--- a/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
+++ b/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="403">
   <si>
     <t xml:space="preserve">PDP Academy · Xadra filiali (1, 2 va 3-qavat): jami xarajatlar — yakuniy</t>
   </si>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">UMUMIY JAMI</t>
   </si>
   <si>
-    <t xml:space="preserve">shundan taxminiy narxlar (mebel, interyer, doskalar, 1-qavat logotiplari) — kutilmagan xarajatsiz</t>
+    <t xml:space="preserve">shundan taxminiy narxlar (mebel, interyer, koworking sahnasi, doskalar, 1-qavat logotiplari) — kutilmagan xarajatsiz</t>
   </si>
   <si>
     <t xml:space="preserve">2. Qavat va bo'limlar bo'yicha</t>
@@ -604,6 +604,30 @@
     <t xml:space="preserve">1-qavat: resepshn stoykasidagi logotip ~1.0 m (yoritilgan)</t>
   </si>
   <si>
+    <t xml:space="preserve">Koworking sahnasi: GKL karkas devor 5.8 × 3.5 m (U4 ustuni bilan tekislanadi) va markazdagi grafit panel 3.9 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna: yog'och reykali panellar (2 × 0.95 × 3.5 m, qora asos ustida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna logotipi ~2.0 m, ichidan yoritilgan (akril harflar, LED)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXMIN — reklama ustasi narxi bilan almashtiring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna yoritishi: 3 ta yo'naltirilgan spot, shift ostida chiziqli LED, yashil LED chiziq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna ekrani: koworkingdagi mavjud ekranni ko'chirish, kronshteyn va kabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXMIN — ekran mavjud deb olingan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minbar (tribuna), ko'chma, logotip bilan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Turniketlar (buyurtmachida mavjud: kirish va chiqish)</t>
   </si>
   <si>
@@ -715,7 +739,7 @@
     <t xml:space="preserve">• 2-qavat koridorlari: 4-xonaning koridor oxiridagi devorlari GKL (avval shisha edi), markazida yorituvchi logotip; e'lonlar va e'tirof doskalari — K1 va K2 qatorlarida.</t>
   </si>
   <si>
-    <t xml:space="preserve">• TAXMINIY narxlar (to'q sariq fon): sotuv va admin xonalari mebeli va interyeri, koridor doskalari, 1-qavat resepshn stoykasi, mehmonlar mebeli va logotiplari — Toshkent bozori bo'yicha dastlabki baho; mebelchi va reklama ustasi narxi bilan almashtiring. «Yakuniy» varag'ida taxminiy qism alohida ko'rsatilgan.</t>
+    <t xml:space="preserve">• TAXMINIY narxlar (to'q sariq fon): sotuv va admin xonalari mebeli va interyeri, koridor doskalari, koworking sahnasi (karkas devor, reyka, logotip, yoritish, minbar), 1-qavat resepshn stoykasi, mehmonlar mebeli va logotiplari — Toshkent bozori bo'yicha dastlabki baho; mebelchi va reklama ustasi narxi bilan almashtiring. «Yakuniy» varag'ida taxminiy qism alohida ko'rsatilgan.</t>
   </si>
   <si>
     <t xml:space="preserve">• Kirmagan: o'quv xonalari, ustozlar xonasi, call-markaz, CEO va koworking mebeli — mavjud; pol (kafel) va internet — mavjud; turniketlar (2 ta) — mavjud (o'rnatish, to'siq va evakuatsiya darvozasi alohida aniqlanadi); eshik furniturasi; shift va bo'yoq; ish haqi (agar narxga kirmagan bo'lsa).</t>
@@ -1076,6 +1100,24 @@
   </si>
   <si>
     <t xml:space="preserve">Offline sotuv (XZ1) bilan orasidagi devor — mavjud devordagi bo'shliqni yopish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna devori: GKL karkas va grafit panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna devori: yog'och reykali yon panellar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna logotipi, ichidan yoritilgan (~2.0 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna yoritishi (spotlar, LED chiziqlar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekranni sahna devoriga ko'chirish (kronshteyn, kabel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minbar (tribuna)</t>
   </si>
   <si>
     <t xml:space="preserve">Jami: Koworking zali</t>
@@ -1907,7 +1949,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>4991.25</v>
       </c>
       <c r="D6" s="8" t="n">
@@ -1916,7 +1958,7 @@
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C6/$C$22)</f>
-        <v>0.0739438415708454</v>
+        <v>0.0714459015278948</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1927,7 +1969,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>5146.8</v>
       </c>
       <c r="D7" s="8" t="n">
@@ -1936,7 +1978,7 @@
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C7/$C$22)</f>
-        <v>0.0762482672270127</v>
+        <v>0.0736724800368182</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1947,7 +1989,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>9404.16</v>
       </c>
       <c r="D8" s="8" t="n">
@@ -1956,7 +1998,7 @@
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C8/$C$22)</f>
-        <v>0.139319752997121</v>
+        <v>0.134613311157038</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1967,7 +2009,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>8256</v>
       </c>
       <c r="D9" s="8" t="n">
@@ -1976,7 +2018,7 @@
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C9/$C$22)</f>
-        <v>0.122310113901107</v>
+        <v>0.118178284600911</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1987,7 +2029,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>2016</v>
       </c>
       <c r="D10" s="8" t="n">
@@ -1996,7 +2038,7 @@
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C10/$C$22)</f>
-        <v>0.0298664231618982</v>
+        <v>0.0288574881002226</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2007,7 +2049,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>3024</v>
       </c>
       <c r="D11" s="8" t="n">
@@ -2016,7 +2058,7 @@
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C11/$C$22)</f>
-        <v>0.0447996347428473</v>
+        <v>0.0432862321503339</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2027,7 +2069,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>2119</v>
       </c>
       <c r="D12" s="8" t="n">
@@ -2036,7 +2078,7 @@
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C12/$C$22)</f>
-        <v>0.0313923366468563</v>
+        <v>0.0303318538116923</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2047,7 +2089,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>3250</v>
       </c>
       <c r="D13" s="8" t="n">
@@ -2056,7 +2098,7 @@
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C13/$C$22)</f>
-        <v>0.0481477555933378</v>
+        <v>0.0465212481774421</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2067,7 +2109,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>537.81512605042</v>
       </c>
       <c r="D14" s="8" t="n">
@@ -2076,7 +2118,7 @@
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C14/$C$22)</f>
-        <v>0.0079675665364541</v>
+        <v>0.0076984095238689</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2087,7 +2129,7 @@
         <v>17</v>
       </c>
       <c r="C15" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>1512.60504201681</v>
       </c>
       <c r="D15" s="8" t="n">
@@ -2096,7 +2138,7 @@
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C15/$C$22)</f>
-        <v>0.0224087808837771</v>
+        <v>0.0216517767858813</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2107,7 +2149,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>451.575630252101</v>
       </c>
       <c r="D16" s="8" t="n">
@@ -2116,7 +2158,7 @@
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C16/$C$22)</f>
-        <v>0.00668995479301097</v>
+        <v>0.00646395752795164</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2127,7 +2169,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>3317.64705882353</v>
       </c>
       <c r="D17" s="8" t="n">
@@ -2136,7 +2178,7 @@
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C17/$C$22)</f>
-        <v>0.0491499260717512</v>
+        <v>0.0474895637503663</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2147,7 +2189,7 @@
         <v>20</v>
       </c>
       <c r="C18" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>1243.6974789916</v>
       </c>
       <c r="D18" s="8" t="n">
@@ -2156,7 +2198,7 @@
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C18/$C$22)</f>
-        <v>0.0184249976155501</v>
+        <v>0.0178025720239468</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2167,7 +2209,7 @@
         <v>21</v>
       </c>
       <c r="C19" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>15000</v>
       </c>
       <c r="D19" s="8" t="n">
@@ -2176,7 +2218,7 @@
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C19/$C$22)</f>
-        <v>0.22222041043079</v>
+        <v>0.214713453126656</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2187,16 +2229,16 @@
         <v>22</v>
       </c>
       <c r="C20" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
-        <v>6490</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <v>8850</v>
       </c>
       <c r="D20" s="8" t="n">
         <f aca="false">C20*Narxlar!$C$19</f>
-        <v>77231000</v>
+        <v>105315000</v>
       </c>
       <c r="E20" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C20/$C$22)</f>
-        <v>0.0961473642463885</v>
+        <v>0.126680937344727</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2207,7 +2249,7 @@
         <v>23</v>
       </c>
       <c r="C21" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>740</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -2216,7 +2258,7 @@
       </c>
       <c r="E21" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C21/$C$22)</f>
-        <v>0.0109628735812523</v>
+        <v>0.0105925303542484</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2226,11 +2268,11 @@
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">SUM(C6:C21)</f>
-        <v>67500.5503361345</v>
+        <v>69860.5503361345</v>
       </c>
       <c r="D22" s="13" t="n">
         <f aca="false">C22*Narxlar!$C$19</f>
-        <v>803256549</v>
+        <v>831340549</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">SUM(E6:E21)</f>
@@ -2240,16 +2282,16 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="str">
-        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$70,"0%")&amp;")"</f>
+        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$76,"0%")&amp;")"</f>
         <v>Kutilmagan xarajatlar (10%)</v>
       </c>
       <c r="C23" s="17" t="n">
-        <f aca="false">C22*Narxlar!$C$70</f>
-        <v>6750.05503361345</v>
+        <f aca="false">C22*Narxlar!$C$76</f>
+        <v>6986.05503361345</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">C23*Narxlar!$C$19</f>
-        <v>80325654.9</v>
+        <v>83134054.9</v>
       </c>
       <c r="E23" s="16"/>
     </row>
@@ -2260,11 +2302,11 @@
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">C22+C23</f>
-        <v>74250.6053697479</v>
+        <v>76846.6053697479</v>
       </c>
       <c r="D24" s="22" t="n">
         <f aca="false">C24*Narxlar!$C$19</f>
-        <v>883582203.9</v>
+        <v>914474603.9</v>
       </c>
       <c r="E24" s="20"/>
     </row>
@@ -2274,12 +2316,12 @@
         <v>26</v>
       </c>
       <c r="C25" s="25" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")+SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")+SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,"1-qavat — kirish zali (resepshn, turniket)",'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
-        <v>7980</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")+SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")+SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,"1-qavat — kirish zali (resepshn, turniket)",'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <v>10340</v>
       </c>
       <c r="D25" s="26" t="n">
         <f aca="false">C25*Narxlar!$C$19</f>
-        <v>94962000</v>
+        <v>123046000</v>
       </c>
       <c r="E25" s="24"/>
     </row>
@@ -2322,7 +2364,7 @@
       </c>
       <c r="E29" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C29/$C$34)</f>
-        <v>0.0508144005185073</v>
+        <v>0.049097809614962</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2342,7 +2384,7 @@
       </c>
       <c r="E30" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C30/$C$34)</f>
-        <v>0.29087910990689</v>
+        <v>0.281052753027689</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2362,7 +2404,7 @@
       </c>
       <c r="E31" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C31/$C$34)</f>
-        <v>0.159724327376757</v>
+        <v>0.154328586707732</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2374,15 +2416,15 @@
       </c>
       <c r="C32" s="7" t="n">
         <f aca="false">'Xonalar bo''yicha'!$W$34</f>
-        <v>26334.8957983193</v>
+        <v>28694.8957983193</v>
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">C32*Narxlar!$C$19</f>
-        <v>313385260</v>
+        <v>341469260</v>
       </c>
       <c r="E32" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C32/$C$34)</f>
-        <v>0.390143423530307</v>
+        <v>0.410745344264448</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2402,7 +2444,7 @@
       </c>
       <c r="E33" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C33/$C$34)</f>
-        <v>0.108438738667539</v>
+        <v>0.10477550638517</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2412,11 +2454,11 @@
       </c>
       <c r="C34" s="12" t="n">
         <f aca="false">SUM(C29:C33)</f>
-        <v>67500.5503361345</v>
+        <v>69860.5503361345</v>
       </c>
       <c r="D34" s="13" t="n">
         <f aca="false">C34*Narxlar!$C$19</f>
-        <v>803256549</v>
+        <v>831340549</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">SUM(E29:E33)</f>
@@ -2578,87 +2620,87 @@
         <v>61</v>
       </c>
       <c r="B6" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D6" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F6" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H6" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J6" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>750</v>
       </c>
       <c r="O6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>2680</v>
       </c>
       <c r="V6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A6,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W6" s="34" t="n">
@@ -2791,87 +2833,87 @@
         <v>63</v>
       </c>
       <c r="B10" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>13.75</v>
       </c>
       <c r="C10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>756.25</v>
       </c>
       <c r="D10" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>7.25</v>
       </c>
       <c r="E10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>87</v>
       </c>
       <c r="F10" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H10" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J10" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A10,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W10" s="34" t="n">
@@ -2884,87 +2926,87 @@
         <v>64</v>
       </c>
       <c r="B11" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>14</v>
       </c>
       <c r="C11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>770</v>
       </c>
       <c r="D11" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>6.3</v>
       </c>
       <c r="E11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>75.6</v>
       </c>
       <c r="F11" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H11" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J11" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A11,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W11" s="34" t="n">
@@ -2977,87 +3019,87 @@
         <v>65</v>
       </c>
       <c r="B12" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>2.25</v>
       </c>
       <c r="C12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>123.75</v>
       </c>
       <c r="D12" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>17.875</v>
       </c>
       <c r="E12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>214.5</v>
       </c>
       <c r="F12" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H12" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J12" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A12,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W12" s="34" t="n">
@@ -3070,87 +3112,87 @@
         <v>66</v>
       </c>
       <c r="B13" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>2.25</v>
       </c>
       <c r="C13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>123.75</v>
       </c>
       <c r="D13" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>52</v>
       </c>
       <c r="E13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>624</v>
       </c>
       <c r="F13" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>50.4</v>
       </c>
       <c r="G13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>781.2</v>
       </c>
       <c r="H13" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J13" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A13,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W13" s="34" t="n">
@@ -3163,87 +3205,87 @@
         <v>67</v>
       </c>
       <c r="B14" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>2.25</v>
       </c>
       <c r="C14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>123.75</v>
       </c>
       <c r="D14" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>27.5</v>
       </c>
       <c r="E14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>330</v>
       </c>
       <c r="F14" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H14" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J14" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A14,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W14" s="34" t="n">
@@ -3256,87 +3298,87 @@
         <v>68</v>
       </c>
       <c r="B15" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>14</v>
       </c>
       <c r="C15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>770</v>
       </c>
       <c r="D15" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>25.55</v>
       </c>
       <c r="E15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>306.6</v>
       </c>
       <c r="F15" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H15" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J15" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A15,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W15" s="34" t="n">
@@ -3349,87 +3391,87 @@
         <v>69</v>
       </c>
       <c r="B16" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>14</v>
       </c>
       <c r="C16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>770</v>
       </c>
       <c r="D16" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>30.45</v>
       </c>
       <c r="E16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>365.4</v>
       </c>
       <c r="F16" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H16" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J16" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A16,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W16" s="34" t="n">
@@ -3562,87 +3604,87 @@
         <v>71</v>
       </c>
       <c r="B20" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>7</v>
       </c>
       <c r="C20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>385</v>
       </c>
       <c r="D20" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>34.3</v>
       </c>
       <c r="E20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>411.6</v>
       </c>
       <c r="F20" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>39.2</v>
       </c>
       <c r="G20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>607.6</v>
       </c>
       <c r="H20" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J20" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>2340</v>
       </c>
       <c r="V20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A20,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W20" s="34" t="n">
@@ -3655,87 +3697,87 @@
         <v>72</v>
       </c>
       <c r="B21" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>7</v>
       </c>
       <c r="C21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>385</v>
       </c>
       <c r="D21" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>35.35</v>
       </c>
       <c r="E21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>424.2</v>
       </c>
       <c r="F21" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>39.2</v>
       </c>
       <c r="G21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>607.6</v>
       </c>
       <c r="H21" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J21" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>1470</v>
       </c>
       <c r="V21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A21,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W21" s="34" t="n">
@@ -3748,87 +3790,87 @@
         <v>73</v>
       </c>
       <c r="B22" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>7.125</v>
       </c>
       <c r="C22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>391.875</v>
       </c>
       <c r="D22" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>35.575</v>
       </c>
       <c r="E22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>426.9</v>
       </c>
       <c r="F22" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>39.2</v>
       </c>
       <c r="G22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>607.6</v>
       </c>
       <c r="H22" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J22" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A22,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W22" s="34" t="n">
@@ -3841,87 +3883,87 @@
         <v>74</v>
       </c>
       <c r="B23" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>7.125</v>
       </c>
       <c r="C23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>391.875</v>
       </c>
       <c r="D23" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>35.925</v>
       </c>
       <c r="E23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>431.1</v>
       </c>
       <c r="F23" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>39.2</v>
       </c>
       <c r="G23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>607.6</v>
       </c>
       <c r="H23" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J23" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A23,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W23" s="34" t="n">
@@ -3934,87 +3976,87 @@
         <v>75</v>
       </c>
       <c r="B24" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D24" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F24" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>29.26</v>
       </c>
       <c r="G24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>453.53</v>
       </c>
       <c r="H24" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J24" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A24,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W24" s="34" t="n">
@@ -4147,87 +4189,87 @@
         <v>77</v>
       </c>
       <c r="B28" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D28" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>52</v>
       </c>
       <c r="E28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>624</v>
       </c>
       <c r="F28" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H28" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J28" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>336</v>
       </c>
       <c r="M28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A28,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>370</v>
       </c>
       <c r="W28" s="34" t="n">
@@ -4240,87 +4282,87 @@
         <v>78</v>
       </c>
       <c r="B29" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D29" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>50.1</v>
       </c>
       <c r="E29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>601.2</v>
       </c>
       <c r="F29" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H29" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J29" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>336</v>
       </c>
       <c r="M29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A29,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>370</v>
       </c>
       <c r="W29" s="34" t="n">
@@ -4333,92 +4375,92 @@
         <v>79</v>
       </c>
       <c r="B30" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D30" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>9.625</v>
       </c>
       <c r="E30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>115.5</v>
       </c>
       <c r="F30" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H30" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J30" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>336</v>
       </c>
       <c r="M30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
-        <v>0</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <v>2360</v>
       </c>
       <c r="V30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A30,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W30" s="34" t="n">
         <f aca="false">C30+E30+G30+I30+K30+L30+M30+N30+O30+P30+Q30+R30+S30+T30+U30+V30</f>
-        <v>451.5</v>
+        <v>2811.5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4426,87 +4468,87 @@
         <v>80</v>
       </c>
       <c r="B31" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D31" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>9.1</v>
       </c>
       <c r="E31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>109.2</v>
       </c>
       <c r="F31" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H31" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J31" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A31,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W31" s="34" t="n">
@@ -4519,87 +4561,87 @@
         <v>81</v>
       </c>
       <c r="B32" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D32" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F32" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H32" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J32" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>24</v>
       </c>
       <c r="K32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>2016</v>
       </c>
       <c r="L32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A32,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W32" s="34" t="n">
@@ -4612,87 +4654,87 @@
         <v>82</v>
       </c>
       <c r="B33" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D33" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F33" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H33" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J33" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>2119</v>
       </c>
       <c r="N33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>2500</v>
       </c>
       <c r="O33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>537.81512605042</v>
       </c>
       <c r="P33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>1512.60504201681</v>
       </c>
       <c r="Q33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>451.575630252101</v>
       </c>
       <c r="R33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>14000</v>
       </c>
       <c r="U33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A33,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W33" s="34" t="n">
@@ -4782,7 +4824,7 @@
       </c>
       <c r="U34" s="36" t="n">
         <f aca="false">SUM(U28:U33)</f>
-        <v>0</v>
+        <v>2360</v>
       </c>
       <c r="V34" s="36" t="n">
         <f aca="false">SUM(V28:V33)</f>
@@ -4790,7 +4832,7 @@
       </c>
       <c r="W34" s="36" t="n">
         <f aca="false">SUM(W28:W33)</f>
-        <v>26334.8957983193</v>
+        <v>28694.8957983193</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4825,87 +4867,87 @@
         <v>84</v>
       </c>
       <c r="B37" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D37" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F37" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>46.86</v>
       </c>
       <c r="G37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>726.33</v>
       </c>
       <c r="H37" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J37" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>1000</v>
       </c>
       <c r="U37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A37,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W37" s="34" t="n">
@@ -4918,87 +4960,87 @@
         <v>85</v>
       </c>
       <c r="B38" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D38" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F38" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H38" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J38" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
         <v>3317.64705882353</v>
       </c>
       <c r="S38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
         <v>1243.6974789916</v>
       </c>
       <c r="T38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$301,'Hisob (batafsil)'!$B$5:$B$301,$A38,'Hisob (batafsil)'!$C$5:$C$301,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W38" s="34" t="n">
@@ -5181,7 +5223,7 @@
       </c>
       <c r="U41" s="39" t="n">
         <f aca="false">U7+U17+U25+U34+U39</f>
-        <v>6490</v>
+        <v>8850</v>
       </c>
       <c r="V41" s="39" t="n">
         <f aca="false">V7+V17+V25+V34+V39</f>
@@ -5189,12 +5231,12 @@
       </c>
       <c r="W41" s="39" t="n">
         <f aca="false">W7+W17+W25+W34+W39</f>
-        <v>67500.5503361345</v>
+        <v>69860.5503361345</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="str">
-        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$70,"0%")&amp;" — «Narxlar» varag'idan)"</f>
+        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$76,"0%")&amp;" — «Narxlar» varag'idan)"</f>
         <v>Kutilmagan xarajatlar (10% — «Narxlar» varag'idan)</v>
       </c>
       <c r="B42" s="16"/>
@@ -5219,8 +5261,8 @@
       <c r="U42" s="16"/>
       <c r="V42" s="16"/>
       <c r="W42" s="41" t="n">
-        <f aca="false">W41*Narxlar!$C$70</f>
-        <v>6750.05503361345</v>
+        <f aca="false">W41*Narxlar!$C$76</f>
+        <v>6986.05503361345</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5250,7 +5292,7 @@
       <c r="V43" s="20"/>
       <c r="W43" s="39" t="n">
         <f aca="false">W41+W42</f>
-        <v>74250.6053697479</v>
+        <v>76846.6053697479</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5280,7 +5322,7 @@
       <c r="V44" s="20"/>
       <c r="W44" s="22" t="n">
         <f aca="false">W43*Narxlar!$C$19</f>
-        <v>883582203.9</v>
+        <v>914474603.9</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5288,7 +5330,7 @@
         <v>89</v>
       </c>
       <c r="W46" s="27" t="n">
-        <f aca="false">W41-'Hisob (batafsil)'!J302</f>
+        <f aca="false">W41-'Hisob (batafsil)'!J308</f>
         <v>0</v>
       </c>
     </row>
@@ -5313,7 +5355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -6445,14 +6487,14 @@
       <c r="B69" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C69" s="44" t="n">
-        <v>2</v>
+      <c r="C69" s="46" t="n">
+        <v>700</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6460,16 +6502,16 @@
         <v>66</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C70" s="47" t="n">
-        <v>0.1</v>
+        <v>194</v>
+      </c>
+      <c r="C70" s="46" t="n">
+        <v>450</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>196</v>
+        <v>117</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6477,16 +6519,16 @@
         <v>67</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C71" s="43" t="n">
-        <v>3.5</v>
+        <v>195</v>
+      </c>
+      <c r="C71" s="46" t="n">
+        <v>600</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6494,16 +6536,16 @@
         <v>68</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C72" s="43" t="n">
-        <v>2.5</v>
+        <v>197</v>
+      </c>
+      <c r="C72" s="46" t="n">
+        <v>250</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6511,17 +6553,16 @@
         <v>69</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C73" s="48" t="n">
-        <f aca="false">C71-C72</f>
-        <v>1</v>
+        <v>198</v>
+      </c>
+      <c r="C73" s="46" t="n">
+        <v>60</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6529,16 +6570,16 @@
         <v>70</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="C74" s="43" t="n">
-        <v>2.1</v>
+        <v>200</v>
+      </c>
+      <c r="C74" s="46" t="n">
+        <v>300</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6546,17 +6587,16 @@
         <v>71</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C75" s="48" t="n">
-        <f aca="false">C71-C74</f>
-        <v>1.4</v>
+        <v>201</v>
+      </c>
+      <c r="C75" s="44" t="n">
+        <v>2</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6564,16 +6604,16 @@
         <v>72</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C76" s="43" t="n">
-        <v>0.9</v>
+        <v>203</v>
+      </c>
+      <c r="C76" s="47" t="n">
+        <v>0.1</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6581,17 +6621,16 @@
         <v>73</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C77" s="49" t="n">
-        <f aca="false">C71</f>
+        <v>206</v>
+      </c>
+      <c r="C77" s="43" t="n">
         <v>3.5</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6599,7 +6638,7 @@
         <v>74</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C78" s="43" t="n">
         <v>2.5</v>
@@ -6611,109 +6650,214 @@
         <v>97</v>
       </c>
     </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C79" s="48" t="n">
+        <f aca="false">C77-C78</f>
+        <v>1</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="3" t="s">
+      <c r="A80" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C80" s="43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E80" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="2" t="s">
+      <c r="A81" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="6" t="s">
         <v>213</v>
       </c>
+      <c r="C81" s="48" t="n">
+        <f aca="false">C77-C80</f>
+        <v>1.4</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="2" t="s">
-        <v>214</v>
+      <c r="A82" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C82" s="43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="2" t="s">
-        <v>215</v>
+      <c r="A83" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C83" s="49" t="n">
+        <f aca="false">C77</f>
+        <v>3.5</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="2" t="s">
-        <v>217</v>
+      <c r="A84" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C84" s="43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="2" t="s">
-        <v>218</v>
+      <c r="B86" s="3" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -6732,7 +6876,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J302"/>
+  <dimension ref="A1:J308"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -6748,12 +6892,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6764,25 +6908,25 @@
         <v>38</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>94</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>5</v>
@@ -6813,7 +6957,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="51"/>
@@ -6843,7 +6987,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E7" s="50"/>
       <c r="F7" s="51"/>
@@ -6873,7 +7017,7 @@
         <v>22</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E8" s="50"/>
       <c r="F8" s="51"/>
@@ -6903,7 +7047,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E9" s="50"/>
       <c r="F9" s="51"/>
@@ -6911,7 +7055,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I9" s="7" t="n">
         <f aca="false">Narxlar!$C$66</f>
@@ -6933,7 +7077,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E10" s="50"/>
       <c r="F10" s="51"/>
@@ -6963,7 +7107,7 @@
         <v>22</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E11" s="50"/>
       <c r="F11" s="51"/>
@@ -7017,7 +7161,7 @@
       <c r="B13" s="54"/>
       <c r="C13" s="54"/>
       <c r="D13" s="11" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E13" s="54"/>
       <c r="F13" s="54"/>
@@ -7054,13 +7198,13 @@
         <v>8</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E16" s="50" t="n">
         <v>4.6</v>
       </c>
       <c r="F16" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G16" s="51" t="n">
@@ -7090,14 +7234,14 @@
         <v>8</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E17" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F17" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G17" s="51" t="n">
@@ -7127,13 +7271,13 @@
         <v>9</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E18" s="50" t="n">
         <v>0.3</v>
       </c>
       <c r="F18" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G18" s="51" t="n">
@@ -7163,13 +7307,13 @@
         <v>9</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E19" s="50" t="n">
         <v>4.6</v>
       </c>
       <c r="F19" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G19" s="51" t="n">
@@ -7199,13 +7343,13 @@
         <v>9</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E20" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F20" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G20" s="51" t="n">
@@ -7235,14 +7379,14 @@
         <v>9</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E21" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F21" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G21" s="51" t="n">
@@ -7272,13 +7416,13 @@
         <v>10</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E22" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F22" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G22" s="51" t="n">
@@ -7308,13 +7452,13 @@
         <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E23" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F23" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G23" s="51" t="n">
@@ -7344,7 +7488,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E24" s="50"/>
       <c r="F24" s="51"/>
@@ -7374,7 +7518,7 @@
         <v>13</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E25" s="50"/>
       <c r="F25" s="51"/>
@@ -7382,7 +7526,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I25" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -7398,7 +7542,7 @@
       <c r="B26" s="54"/>
       <c r="C26" s="54"/>
       <c r="D26" s="11" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E26" s="54"/>
       <c r="F26" s="54"/>
@@ -7435,13 +7579,13 @@
         <v>8</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E29" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F29" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G29" s="51" t="n">
@@ -7471,14 +7615,14 @@
         <v>8</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E30" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F30" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G30" s="51" t="n">
@@ -7508,13 +7652,13 @@
         <v>9</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E31" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F31" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G31" s="51" t="n">
@@ -7544,13 +7688,13 @@
         <v>9</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E32" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F32" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G32" s="51" t="n">
@@ -7580,14 +7724,14 @@
         <v>9</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E33" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F33" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G33" s="51" t="n">
@@ -7617,13 +7761,13 @@
         <v>10</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E34" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F34" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G34" s="51" t="n">
@@ -7653,13 +7797,13 @@
         <v>10</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E35" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F35" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G35" s="51" t="n">
@@ -7689,7 +7833,7 @@
         <v>11</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E36" s="50"/>
       <c r="F36" s="51"/>
@@ -7719,7 +7863,7 @@
         <v>13</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E37" s="50"/>
       <c r="F37" s="51"/>
@@ -7727,7 +7871,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I37" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -7743,7 +7887,7 @@
       <c r="B38" s="54"/>
       <c r="C38" s="54"/>
       <c r="D38" s="11" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="E38" s="54"/>
       <c r="F38" s="54"/>
@@ -7780,14 +7924,14 @@
         <v>8</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E41" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F41" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G41" s="51" t="n">
@@ -7817,13 +7961,13 @@
         <v>9</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E42" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F42" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G42" s="51" t="n">
@@ -7853,13 +7997,13 @@
         <v>9</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E43" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F43" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G43" s="51" t="n">
@@ -7889,14 +8033,14 @@
         <v>9</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E44" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F44" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G44" s="51" t="n">
@@ -7926,13 +8070,13 @@
         <v>10</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E45" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F45" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G45" s="51" t="n">
@@ -7962,13 +8106,13 @@
         <v>10</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E46" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F46" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G46" s="51" t="n">
@@ -7998,7 +8142,7 @@
         <v>11</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E47" s="50"/>
       <c r="F47" s="51"/>
@@ -8028,7 +8172,7 @@
         <v>13</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E48" s="50"/>
       <c r="F48" s="51"/>
@@ -8036,7 +8180,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I48" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -8052,7 +8196,7 @@
       <c r="B49" s="54"/>
       <c r="C49" s="54"/>
       <c r="D49" s="11" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="E49" s="54"/>
       <c r="F49" s="54"/>
@@ -8089,14 +8233,14 @@
         <v>8</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E52" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F52" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G52" s="51" t="n">
@@ -8126,13 +8270,13 @@
         <v>9</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="E53" s="50" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G53" s="51" t="n">
@@ -8162,13 +8306,13 @@
         <v>9</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="E54" s="50" t="n">
         <v>4.5</v>
       </c>
       <c r="F54" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G54" s="51" t="n">
@@ -8198,13 +8342,13 @@
         <v>9</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="E55" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F55" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G55" s="51" t="n">
@@ -8234,13 +8378,13 @@
         <v>9</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E56" s="50" t="n">
         <v>1.15</v>
       </c>
       <c r="F56" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G56" s="51" t="n">
@@ -8270,13 +8414,13 @@
         <v>9</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E57" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F57" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G57" s="51" t="n">
@@ -8306,13 +8450,13 @@
         <v>9</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E58" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F58" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G58" s="51" t="n">
@@ -8342,13 +8486,13 @@
         <v>9</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E59" s="50" t="n">
         <v>0.25</v>
       </c>
       <c r="F59" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G59" s="51" t="n">
@@ -8378,13 +8522,13 @@
         <v>9</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E60" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F60" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G60" s="51" t="n">
@@ -8414,13 +8558,13 @@
         <v>9</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="E61" s="50" t="n">
         <v>4.5</v>
       </c>
       <c r="F61" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G61" s="51" t="n">
@@ -8450,14 +8594,14 @@
         <v>9</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E62" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F62" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G62" s="51" t="n">
@@ -8487,13 +8631,13 @@
         <v>10</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E63" s="50" t="n">
         <v>8.8</v>
       </c>
       <c r="F63" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G63" s="51" t="n">
@@ -8523,13 +8667,13 @@
         <v>10</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="E64" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F64" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G64" s="51" t="n">
@@ -8559,7 +8703,7 @@
         <v>11</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E65" s="50"/>
       <c r="F65" s="51"/>
@@ -8589,7 +8733,7 @@
         <v>13</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E66" s="50"/>
       <c r="F66" s="51"/>
@@ -8597,7 +8741,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I66" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -8613,7 +8757,7 @@
       <c r="B67" s="54"/>
       <c r="C67" s="54"/>
       <c r="D67" s="11" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E67" s="54"/>
       <c r="F67" s="54"/>
@@ -8650,14 +8794,14 @@
         <v>8</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E70" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F70" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G70" s="51" t="n">
@@ -8687,13 +8831,13 @@
         <v>9</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E71" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F71" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G71" s="51" t="n">
@@ -8723,13 +8867,13 @@
         <v>9</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E72" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F72" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G72" s="51" t="n">
@@ -8759,13 +8903,13 @@
         <v>9</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E73" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F73" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G73" s="51" t="n">
@@ -8795,14 +8939,14 @@
         <v>9</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E74" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F74" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G74" s="51" t="n">
@@ -8832,13 +8976,13 @@
         <v>10</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E75" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F75" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G75" s="51" t="n">
@@ -8868,13 +9012,13 @@
         <v>10</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E76" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F76" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G76" s="51" t="n">
@@ -8904,7 +9048,7 @@
         <v>11</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E77" s="50"/>
       <c r="F77" s="51"/>
@@ -8934,7 +9078,7 @@
         <v>13</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E78" s="50"/>
       <c r="F78" s="51"/>
@@ -8942,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I78" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -8958,7 +9102,7 @@
       <c r="B79" s="54"/>
       <c r="C79" s="54"/>
       <c r="D79" s="11" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="E79" s="54"/>
       <c r="F79" s="54"/>
@@ -8995,13 +9139,13 @@
         <v>8</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E82" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F82" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G82" s="51" t="n">
@@ -9031,14 +9175,14 @@
         <v>8</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E83" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F83" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G83" s="51" t="n">
@@ -9068,13 +9212,13 @@
         <v>9</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E84" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F84" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G84" s="51" t="n">
@@ -9104,13 +9248,13 @@
         <v>9</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E85" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F85" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G85" s="51" t="n">
@@ -9140,13 +9284,13 @@
         <v>9</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E86" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F86" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G86" s="51" t="n">
@@ -9176,13 +9320,13 @@
         <v>9</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E87" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F87" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G87" s="51" t="n">
@@ -9212,14 +9356,14 @@
         <v>9</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E88" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F88" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G88" s="51" t="n">
@@ -9249,13 +9393,13 @@
         <v>10</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E89" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F89" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G89" s="51" t="n">
@@ -9285,13 +9429,13 @@
         <v>10</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E90" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F90" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G90" s="51" t="n">
@@ -9321,7 +9465,7 @@
         <v>11</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E91" s="50"/>
       <c r="F91" s="51"/>
@@ -9351,7 +9495,7 @@
         <v>13</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E92" s="50"/>
       <c r="F92" s="51"/>
@@ -9359,7 +9503,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I92" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -9375,7 +9519,7 @@
       <c r="B93" s="54"/>
       <c r="C93" s="54"/>
       <c r="D93" s="11" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="E93" s="54"/>
       <c r="F93" s="54"/>
@@ -9412,13 +9556,13 @@
         <v>8</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E96" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F96" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G96" s="51" t="n">
@@ -9448,14 +9592,14 @@
         <v>8</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E97" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F97" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G97" s="51" t="n">
@@ -9485,13 +9629,13 @@
         <v>9</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E98" s="50" t="n">
         <v>1.55</v>
       </c>
       <c r="F98" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G98" s="51" t="n">
@@ -9521,13 +9665,13 @@
         <v>9</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E99" s="50" t="n">
         <v>2.6</v>
       </c>
       <c r="F99" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G99" s="51" t="n">
@@ -9557,13 +9701,13 @@
         <v>9</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E100" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F100" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G100" s="51" t="n">
@@ -9593,13 +9737,13 @@
         <v>9</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E101" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F101" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G101" s="51" t="n">
@@ -9629,13 +9773,13 @@
         <v>9</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E102" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F102" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G102" s="51" t="n">
@@ -9665,14 +9809,14 @@
         <v>9</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E103" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F103" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G103" s="51" t="n">
@@ -9702,13 +9846,13 @@
         <v>10</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E104" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F104" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G104" s="51" t="n">
@@ -9738,13 +9882,13 @@
         <v>10</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E105" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F105" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G105" s="51" t="n">
@@ -9774,7 +9918,7 @@
         <v>11</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E106" s="50"/>
       <c r="F106" s="51"/>
@@ -9804,7 +9948,7 @@
         <v>13</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E107" s="50"/>
       <c r="F107" s="51"/>
@@ -9812,7 +9956,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I107" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -9828,7 +9972,7 @@
       <c r="B108" s="54"/>
       <c r="C108" s="54"/>
       <c r="D108" s="11" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E108" s="54"/>
       <c r="F108" s="54"/>
@@ -9865,13 +10009,13 @@
         <v>8</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E111" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F111" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G111" s="51" t="n">
@@ -9901,13 +10045,13 @@
         <v>8</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E112" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F112" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G112" s="51" t="n">
@@ -9937,14 +10081,14 @@
         <v>8</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E113" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F113" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G113" s="51" t="n">
@@ -9974,13 +10118,13 @@
         <v>9</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E114" s="50" t="n">
         <v>0.6</v>
       </c>
       <c r="F114" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G114" s="51" t="n">
@@ -10010,13 +10154,13 @@
         <v>9</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E115" s="50" t="n">
         <v>2.8</v>
       </c>
       <c r="F115" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G115" s="51" t="n">
@@ -10046,13 +10190,13 @@
         <v>9</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="E116" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F116" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G116" s="51" t="n">
@@ -10082,13 +10226,13 @@
         <v>9</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E117" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F117" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G117" s="51" t="n">
@@ -10118,13 +10262,13 @@
         <v>9</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E118" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F118" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G118" s="51" t="n">
@@ -10154,14 +10298,14 @@
         <v>9</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E119" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F119" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G119" s="51" t="n">
@@ -10191,13 +10335,13 @@
         <v>10</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E120" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F120" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G120" s="51" t="n">
@@ -10227,13 +10371,13 @@
         <v>10</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="E121" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F121" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G121" s="51" t="n">
@@ -10263,7 +10407,7 @@
         <v>13</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E122" s="50"/>
       <c r="F122" s="51"/>
@@ -10271,7 +10415,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I122" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -10293,7 +10437,7 @@
         <v>22</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="E123" s="50"/>
       <c r="F123" s="51"/>
@@ -10323,7 +10467,7 @@
         <v>22</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="E124" s="50"/>
       <c r="F124" s="51"/>
@@ -10353,7 +10497,7 @@
         <v>22</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="E125" s="50"/>
       <c r="F125" s="51"/>
@@ -10383,7 +10527,7 @@
         <v>22</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="E126" s="50"/>
       <c r="F126" s="51"/>
@@ -10413,7 +10557,7 @@
         <v>22</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E127" s="50"/>
       <c r="F127" s="51"/>
@@ -10443,7 +10587,7 @@
         <v>22</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E128" s="50"/>
       <c r="F128" s="51"/>
@@ -10451,7 +10595,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I128" s="7" t="n">
         <f aca="false">Narxlar!$C$61</f>
@@ -10467,7 +10611,7 @@
       <c r="B129" s="54"/>
       <c r="C129" s="54"/>
       <c r="D129" s="11" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="E129" s="54"/>
       <c r="F129" s="54"/>
@@ -10504,13 +10648,13 @@
         <v>8</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E132" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F132" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G132" s="51" t="n">
@@ -10540,13 +10684,13 @@
         <v>8</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E133" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F133" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G133" s="51" t="n">
@@ -10576,14 +10720,14 @@
         <v>8</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E134" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F134" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G134" s="51" t="n">
@@ -10613,13 +10757,13 @@
         <v>9</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="E135" s="50" t="n">
         <v>0.9</v>
       </c>
       <c r="F135" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G135" s="51" t="n">
@@ -10649,13 +10793,13 @@
         <v>9</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E136" s="50" t="n">
         <v>2.8</v>
       </c>
       <c r="F136" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G136" s="51" t="n">
@@ -10685,13 +10829,13 @@
         <v>9</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E137" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F137" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G137" s="51" t="n">
@@ -10721,13 +10865,13 @@
         <v>9</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E138" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F138" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G138" s="51" t="n">
@@ -10757,13 +10901,13 @@
         <v>9</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E139" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F139" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G139" s="51" t="n">
@@ -10793,14 +10937,14 @@
         <v>9</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E140" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F140" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G140" s="51" t="n">
@@ -10830,13 +10974,13 @@
         <v>10</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E141" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F141" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G141" s="51" t="n">
@@ -10866,13 +11010,13 @@
         <v>10</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E142" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F142" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G142" s="51" t="n">
@@ -10902,7 +11046,7 @@
         <v>13</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E143" s="50"/>
       <c r="F143" s="51"/>
@@ -10910,7 +11054,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I143" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -10932,7 +11076,7 @@
         <v>22</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="E144" s="50"/>
       <c r="F144" s="51"/>
@@ -10962,7 +11106,7 @@
         <v>22</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="E145" s="50"/>
       <c r="F145" s="51"/>
@@ -10992,7 +11136,7 @@
         <v>22</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E146" s="50"/>
       <c r="F146" s="51"/>
@@ -11022,7 +11166,7 @@
         <v>22</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E147" s="50"/>
       <c r="F147" s="51"/>
@@ -11052,7 +11196,7 @@
         <v>22</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E148" s="50"/>
       <c r="F148" s="51"/>
@@ -11060,7 +11204,7 @@
         <v>1</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I148" s="7" t="n">
         <f aca="false">Narxlar!$C$62</f>
@@ -11076,7 +11220,7 @@
       <c r="B149" s="54"/>
       <c r="C149" s="54"/>
       <c r="D149" s="11" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E149" s="54"/>
       <c r="F149" s="54"/>
@@ -11113,13 +11257,13 @@
         <v>8</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E152" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F152" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G152" s="51" t="n">
@@ -11149,13 +11293,13 @@
         <v>8</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E153" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F153" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G153" s="51" t="n">
@@ -11185,14 +11329,14 @@
         <v>8</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E154" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F154" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G154" s="51" t="n">
@@ -11222,13 +11366,13 @@
         <v>9</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="E155" s="50" t="n">
         <v>0.9</v>
       </c>
       <c r="F155" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G155" s="51" t="n">
@@ -11258,13 +11402,13 @@
         <v>9</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E156" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F156" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G156" s="51" t="n">
@@ -11294,13 +11438,13 @@
         <v>9</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E157" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F157" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G157" s="51" t="n">
@@ -11330,13 +11474,13 @@
         <v>9</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="E158" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F158" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G158" s="51" t="n">
@@ -11366,13 +11510,13 @@
         <v>9</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="E159" s="50" t="n">
         <v>2.85</v>
       </c>
       <c r="F159" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G159" s="51" t="n">
@@ -11402,14 +11546,14 @@
         <v>9</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E160" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F160" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G160" s="51" t="n">
@@ -11439,13 +11583,13 @@
         <v>10</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="E161" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F161" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G161" s="51" t="n">
@@ -11475,13 +11619,13 @@
         <v>10</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="E162" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F162" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G162" s="51" t="n">
@@ -11511,7 +11655,7 @@
         <v>13</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E163" s="50"/>
       <c r="F163" s="51"/>
@@ -11519,7 +11663,7 @@
         <v>1</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I163" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -11535,7 +11679,7 @@
       <c r="B164" s="54"/>
       <c r="C164" s="54"/>
       <c r="D164" s="11" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="E164" s="54"/>
       <c r="F164" s="54"/>
@@ -11572,13 +11716,13 @@
         <v>8</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E167" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F167" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G167" s="51" t="n">
@@ -11608,13 +11752,13 @@
         <v>8</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E168" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F168" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G168" s="51" t="n">
@@ -11644,14 +11788,14 @@
         <v>8</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E169" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F169" s="31" t="n">
-        <f aca="false">Narxlar!$C$72</f>
+        <f aca="false">Narxlar!$C$78</f>
         <v>2.5</v>
       </c>
       <c r="G169" s="51" t="n">
@@ -11681,13 +11825,13 @@
         <v>9</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="E170" s="50" t="n">
         <v>1</v>
       </c>
       <c r="F170" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G170" s="51" t="n">
@@ -11717,13 +11861,13 @@
         <v>9</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E171" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F171" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G171" s="51" t="n">
@@ -11753,13 +11897,13 @@
         <v>9</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E172" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F172" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G172" s="51" t="n">
@@ -11789,13 +11933,13 @@
         <v>9</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E173" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F173" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G173" s="51" t="n">
@@ -11825,13 +11969,13 @@
         <v>9</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="E174" s="50" t="n">
         <v>2.85</v>
       </c>
       <c r="F174" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G174" s="51" t="n">
@@ -11861,14 +12005,14 @@
         <v>9</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E175" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F175" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G175" s="51" t="n">
@@ -11898,13 +12042,13 @@
         <v>10</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E176" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F176" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G176" s="51" t="n">
@@ -11934,13 +12078,13 @@
         <v>10</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E177" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F177" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G177" s="51" t="n">
@@ -11970,7 +12114,7 @@
         <v>13</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E178" s="50"/>
       <c r="F178" s="51"/>
@@ -11978,7 +12122,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I178" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -11994,7 +12138,7 @@
       <c r="B179" s="54"/>
       <c r="C179" s="54"/>
       <c r="D179" s="11" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E179" s="54"/>
       <c r="F179" s="54"/>
@@ -12031,13 +12175,13 @@
         <v>10</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="E182" s="50" t="n">
         <v>5.95</v>
       </c>
       <c r="F182" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G182" s="51" t="n">
@@ -12067,14 +12211,14 @@
         <v>10</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="E183" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F183" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>2.1</v>
       </c>
       <c r="G183" s="51" t="n">
@@ -12104,13 +12248,13 @@
         <v>10</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E184" s="50" t="n">
         <v>2.95</v>
       </c>
       <c r="F184" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>3.5</v>
       </c>
       <c r="G184" s="51" t="n">
@@ -12140,7 +12284,7 @@
         <v>13</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E185" s="50"/>
       <c r="F185" s="51"/>
@@ -12148,7 +12292,7 @@
         <v>1</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I185" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -12164,7 +12308,7 @@
       <c r="B186" s="54"/>
       <c r="C186" s="54"/>
       <c r="D186" s="11" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E186" s="54"/>
       <c r="F186" s="54"/>
@@ -12201,13 +12345,13 @@
         <v>9</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E189" s="50" t="n">
         <v>4.6</v>
       </c>
       <c r="F189" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G189" s="51" t="n">
@@ -12237,13 +12381,13 @@
         <v>9</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E190" s="50" t="n">
         <v>0.4</v>
       </c>
       <c r="F190" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G190" s="51" t="n">
@@ -12273,13 +12417,13 @@
         <v>9</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="E191" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F191" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G191" s="51" t="n">
@@ -12309,13 +12453,13 @@
         <v>9</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E192" s="50" t="n">
         <v>0.55</v>
       </c>
       <c r="F192" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G192" s="51" t="n">
@@ -12345,13 +12489,13 @@
         <v>9</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="E193" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F193" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G193" s="51" t="n">
@@ -12381,13 +12525,13 @@
         <v>9</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E194" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F194" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G194" s="51" t="n">
@@ -12417,13 +12561,13 @@
         <v>9</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E195" s="50" t="n">
         <v>5.9</v>
       </c>
       <c r="F195" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G195" s="51" t="n">
@@ -12453,13 +12597,13 @@
         <v>9</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="E196" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F196" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G196" s="51" t="n">
@@ -12489,13 +12633,13 @@
         <v>9</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="E197" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F197" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G197" s="51" t="n">
@@ -12525,13 +12669,13 @@
         <v>9</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="E198" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F198" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G198" s="51" t="n">
@@ -12561,13 +12705,13 @@
         <v>9</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="E199" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F199" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G199" s="51" t="n">
@@ -12597,13 +12741,13 @@
         <v>9</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E200" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F200" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G200" s="51" t="n">
@@ -12633,13 +12777,13 @@
         <v>9</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E201" s="50" t="n">
         <v>1.15</v>
       </c>
       <c r="F201" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G201" s="51" t="n">
@@ -12669,14 +12813,14 @@
         <v>9</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E202" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F202" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G202" s="51" t="n">
@@ -12706,14 +12850,14 @@
         <v>9</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="E203" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F203" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G203" s="51" t="n">
@@ -12743,14 +12887,14 @@
         <v>9</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E204" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F204" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G204" s="51" t="n">
@@ -12780,14 +12924,14 @@
         <v>9</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="E205" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F205" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G205" s="51" t="n">
@@ -12817,14 +12961,14 @@
         <v>9</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="E206" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F206" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G206" s="51" t="n">
@@ -12854,7 +12998,7 @@
         <v>13</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="E207" s="50"/>
       <c r="F207" s="51"/>
@@ -12862,7 +13006,7 @@
         <v>1</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I207" s="7" t="n">
         <f aca="false">Narxlar!$C$11</f>
@@ -12884,7 +13028,7 @@
         <v>23</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="E208" s="50"/>
       <c r="F208" s="51"/>
@@ -12914,7 +13058,7 @@
         <v>23</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="E209" s="50"/>
       <c r="F209" s="51"/>
@@ -12938,7 +13082,7 @@
       <c r="B210" s="54"/>
       <c r="C210" s="54"/>
       <c r="D210" s="11" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="E210" s="54"/>
       <c r="F210" s="54"/>
@@ -12975,13 +13119,13 @@
         <v>9</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="E213" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F213" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G213" s="51" t="n">
@@ -13011,13 +13155,13 @@
         <v>9</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="E214" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F214" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G214" s="51" t="n">
@@ -13047,13 +13191,13 @@
         <v>9</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E215" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F215" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G215" s="51" t="n">
@@ -13083,13 +13227,13 @@
         <v>9</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E216" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F216" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G216" s="51" t="n">
@@ -13119,13 +13263,13 @@
         <v>9</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E217" s="50" t="n">
         <v>6.3</v>
       </c>
       <c r="F217" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G217" s="51" t="n">
@@ -13155,13 +13299,13 @@
         <v>9</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E218" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F218" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G218" s="51" t="n">
@@ -13191,13 +13335,13 @@
         <v>9</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E219" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F219" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G219" s="51" t="n">
@@ -13227,13 +13371,13 @@
         <v>9</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E220" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F220" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G220" s="51" t="n">
@@ -13263,13 +13407,13 @@
         <v>9</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E221" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F221" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G221" s="51" t="n">
@@ -13299,13 +13443,13 @@
         <v>9</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E222" s="50" t="n">
         <v>0.4</v>
       </c>
       <c r="F222" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G222" s="51" t="n">
@@ -13335,13 +13479,13 @@
         <v>9</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="E223" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F223" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G223" s="51" t="n">
@@ -13371,13 +13515,13 @@
         <v>9</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E224" s="50" t="n">
         <v>0.35</v>
       </c>
       <c r="F224" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G224" s="51" t="n">
@@ -13407,13 +13551,13 @@
         <v>9</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E225" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F225" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G225" s="51" t="n">
@@ -13443,14 +13587,14 @@
         <v>9</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E226" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F226" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G226" s="51" t="n">
@@ -13480,14 +13624,14 @@
         <v>9</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="E227" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F227" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G227" s="51" t="n">
@@ -13517,14 +13661,14 @@
         <v>9</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="E228" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F228" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G228" s="51" t="n">
@@ -13554,14 +13698,14 @@
         <v>9</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E229" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F229" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G229" s="51" t="n">
@@ -13591,14 +13735,14 @@
         <v>9</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="E230" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F230" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G230" s="51" t="n">
@@ -13628,14 +13772,14 @@
         <v>9</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E231" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
       <c r="F231" s="31" t="n">
-        <f aca="false">Narxlar!$C$73</f>
+        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G231" s="51" t="n">
@@ -13665,7 +13809,7 @@
         <v>13</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="E232" s="50"/>
       <c r="F232" s="51"/>
@@ -13673,7 +13817,7 @@
         <v>1</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I232" s="7" t="n">
         <f aca="false">Narxlar!$C$11</f>
@@ -13695,7 +13839,7 @@
         <v>23</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E233" s="50"/>
       <c r="F233" s="51"/>
@@ -13725,7 +13869,7 @@
         <v>23</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E234" s="50"/>
       <c r="F234" s="51"/>
@@ -13749,7 +13893,7 @@
       <c r="B235" s="54"/>
       <c r="C235" s="54"/>
       <c r="D235" s="11" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E235" s="54"/>
       <c r="F235" s="54"/>
@@ -13786,13 +13930,13 @@
         <v>9</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E238" s="50" t="n">
         <v>0.4</v>
       </c>
       <c r="F238" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G238" s="51" t="n">
@@ -13822,13 +13966,13 @@
         <v>9</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E239" s="50" t="n">
         <v>0.7</v>
       </c>
       <c r="F239" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G239" s="51" t="n">
@@ -13858,13 +14002,13 @@
         <v>9</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E240" s="50" t="n">
         <v>1.65</v>
       </c>
       <c r="F240" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G240" s="51" t="n">
@@ -13894,7 +14038,7 @@
         <v>13</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="E241" s="50"/>
       <c r="F241" s="51"/>
@@ -13902,7 +14046,7 @@
         <v>1</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I241" s="7" t="n">
         <f aca="false">Narxlar!$C$11</f>
@@ -13914,350 +14058,347 @@
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="54"/>
-      <c r="B242" s="54"/>
-      <c r="C242" s="54"/>
-      <c r="D242" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="E242" s="54"/>
-      <c r="F242" s="54"/>
-      <c r="G242" s="54"/>
-      <c r="H242" s="54"/>
-      <c r="I242" s="54"/>
-      <c r="J242" s="12" t="n">
-        <f aca="false">SUM(J238:J241)</f>
-        <v>451.5</v>
+      <c r="A242" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D242" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E242" s="50"/>
+      <c r="F242" s="51"/>
+      <c r="G242" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I242" s="7" t="n">
+        <f aca="false">Narxlar!$C$69</f>
+        <v>700</v>
+      </c>
+      <c r="J242" s="53" t="n">
+        <f aca="false">G242*I242</f>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="5" t="n">
+        <v>193</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D243" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E243" s="50"/>
+      <c r="F243" s="51"/>
+      <c r="G243" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H243" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I243" s="7" t="n">
+        <f aca="false">Narxlar!$C$70</f>
+        <v>450</v>
+      </c>
+      <c r="J243" s="53" t="n">
+        <f aca="false">G243*I243</f>
+        <v>450</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B244" s="30"/>
-      <c r="C244" s="30"/>
-      <c r="D244" s="30"/>
-      <c r="E244" s="30"/>
-      <c r="F244" s="30"/>
-      <c r="G244" s="30"/>
-      <c r="H244" s="30"/>
-      <c r="I244" s="30"/>
-      <c r="J244" s="30"/>
+      <c r="A244" s="5" t="n">
+        <v>194</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D244" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E244" s="50"/>
+      <c r="F244" s="51"/>
+      <c r="G244" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H244" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I244" s="7" t="n">
+        <f aca="false">Narxlar!$C$71</f>
+        <v>600</v>
+      </c>
+      <c r="J244" s="53" t="n">
+        <f aca="false">G244*I244</f>
+        <v>600</v>
+      </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B245" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D245" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="E245" s="50"/>
+      <c r="F245" s="51"/>
+      <c r="G245" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H245" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I245" s="7" t="n">
+        <f aca="false">Narxlar!$C$72</f>
+        <v>250</v>
+      </c>
+      <c r="J245" s="53" t="n">
+        <f aca="false">G245*I245</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D246" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E246" s="50"/>
+      <c r="F246" s="51"/>
+      <c r="G246" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H246" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I246" s="7" t="n">
+        <f aca="false">Narxlar!$C$73</f>
+        <v>60</v>
+      </c>
+      <c r="J246" s="53" t="n">
+        <f aca="false">G246*I246</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="5" t="n">
+        <v>197</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D247" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E247" s="50"/>
+      <c r="F247" s="51"/>
+      <c r="G247" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I247" s="7" t="n">
+        <f aca="false">Narxlar!$C$74</f>
+        <v>300</v>
+      </c>
+      <c r="J247" s="53" t="n">
+        <f aca="false">G247*I247</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="54"/>
+      <c r="B248" s="54"/>
+      <c r="C248" s="54"/>
+      <c r="D248" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="E248" s="54"/>
+      <c r="F248" s="54"/>
+      <c r="G248" s="54"/>
+      <c r="H248" s="54"/>
+      <c r="I248" s="54"/>
+      <c r="J248" s="12" t="n">
+        <f aca="false">SUM(J238:J247)</f>
+        <v>2811.5</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="C245" s="6" t="s">
+      <c r="B250" s="30"/>
+      <c r="C250" s="30"/>
+      <c r="D250" s="30"/>
+      <c r="E250" s="30"/>
+      <c r="F250" s="30"/>
+      <c r="G250" s="30"/>
+      <c r="H250" s="30"/>
+      <c r="I250" s="30"/>
+      <c r="J250" s="30"/>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C251" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D245" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="E245" s="50" t="n">
+      <c r="D251" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="E251" s="50" t="n">
         <v>2.6</v>
       </c>
-      <c r="F245" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+      <c r="F251" s="31" t="n">
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
-      <c r="G245" s="51" t="n">
-        <f aca="false">E245*F245</f>
+      <c r="G251" s="51" t="n">
+        <f aca="false">E251*F251</f>
         <v>9.1</v>
       </c>
-      <c r="H245" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I245" s="7" t="n">
+      <c r="H251" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I251" s="7" t="n">
         <f aca="false">Narxlar!$C$6</f>
         <v>12</v>
       </c>
-      <c r="J245" s="53" t="n">
-        <f aca="false">G245*I245</f>
+      <c r="J251" s="53" t="n">
+        <f aca="false">G251*I251</f>
         <v>109.2</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="54"/>
-      <c r="B246" s="54"/>
-      <c r="C246" s="54"/>
-      <c r="D246" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="E246" s="54"/>
-      <c r="F246" s="54"/>
-      <c r="G246" s="54"/>
-      <c r="H246" s="54"/>
-      <c r="I246" s="54"/>
-      <c r="J246" s="12" t="n">
-        <f aca="false">SUM(J245:J245)</f>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="54"/>
+      <c r="B252" s="54"/>
+      <c r="C252" s="54"/>
+      <c r="D252" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="E252" s="54"/>
+      <c r="F252" s="54"/>
+      <c r="G252" s="54"/>
+      <c r="H252" s="54"/>
+      <c r="I252" s="54"/>
+      <c r="J252" s="12" t="n">
+        <f aca="false">SUM(J251:J251)</f>
         <v>109.2</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="29" t="s">
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B248" s="30"/>
-      <c r="C248" s="30"/>
-      <c r="D248" s="30"/>
-      <c r="E248" s="30"/>
-      <c r="F248" s="30"/>
-      <c r="G248" s="30"/>
-      <c r="H248" s="30"/>
-      <c r="I248" s="30"/>
-      <c r="J248" s="30"/>
-    </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="5" t="n">
-        <v>193</v>
-      </c>
-      <c r="B249" s="6" t="s">
+      <c r="B254" s="30"/>
+      <c r="C254" s="30"/>
+      <c r="D254" s="30"/>
+      <c r="E254" s="30"/>
+      <c r="F254" s="30"/>
+      <c r="G254" s="30"/>
+      <c r="H254" s="30"/>
+      <c r="I254" s="30"/>
+      <c r="J254" s="30"/>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="B255" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C249" s="6" t="s">
+      <c r="C255" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D249" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="E249" s="31" t="n">
+      <c r="D255" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E255" s="31" t="n">
         <f aca="false">Narxlar!$C$10</f>
         <v>24</v>
       </c>
-      <c r="F249" s="51"/>
-      <c r="G249" s="51" t="n">
-        <f aca="false">E249</f>
+      <c r="F255" s="51"/>
+      <c r="G255" s="51" t="n">
+        <f aca="false">E255</f>
         <v>24</v>
       </c>
-      <c r="H249" s="5" t="s">
+      <c r="H255" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I249" s="7" t="n">
+      <c r="I255" s="7" t="n">
         <f aca="false">Narxlar!$C$9</f>
         <v>84</v>
       </c>
-      <c r="J249" s="53" t="n">
-        <f aca="false">G249*I249</f>
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="54"/>
-      <c r="B250" s="54"/>
-      <c r="C250" s="54"/>
-      <c r="D250" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="E250" s="54"/>
-      <c r="F250" s="54"/>
-      <c r="G250" s="54"/>
-      <c r="H250" s="54"/>
-      <c r="I250" s="54"/>
-      <c r="J250" s="12" t="n">
-        <f aca="false">SUM(J249:J249)</f>
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="B252" s="30"/>
-      <c r="C252" s="30"/>
-      <c r="D252" s="30"/>
-      <c r="E252" s="30"/>
-      <c r="F252" s="30"/>
-      <c r="G252" s="30"/>
-      <c r="H252" s="30"/>
-      <c r="I252" s="30"/>
-      <c r="J252" s="30"/>
-    </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="5" t="n">
-        <v>194</v>
-      </c>
-      <c r="B253" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C253" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D253" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E253" s="50"/>
-      <c r="F253" s="51"/>
-      <c r="G253" s="33" t="n">
-        <f aca="false">Narxlar!$C$14</f>
-        <v>16</v>
-      </c>
-      <c r="H253" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I253" s="7" t="n">
-        <f aca="false">Narxlar!$C$13</f>
-        <v>40</v>
-      </c>
-      <c r="J253" s="53" t="n">
-        <f aca="false">G253*I253</f>
-        <v>640</v>
-      </c>
-    </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="5" t="n">
-        <v>195</v>
-      </c>
-      <c r="B254" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C254" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D254" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="E254" s="50"/>
-      <c r="F254" s="51"/>
-      <c r="G254" s="33" t="n">
-        <f aca="false">Narxlar!$C$14</f>
-        <v>16</v>
-      </c>
-      <c r="H254" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I254" s="7" t="n">
-        <f aca="false">Narxlar!$C$15</f>
-        <v>21</v>
-      </c>
-      <c r="J254" s="53" t="n">
-        <f aca="false">G254*I254</f>
-        <v>336</v>
-      </c>
-    </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="5" t="n">
-        <v>196</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C255" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D255" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E255" s="50"/>
-      <c r="F255" s="51"/>
-      <c r="G255" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H255" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I255" s="7" t="n">
-        <f aca="false">Narxlar!$C$16</f>
-        <v>840</v>
-      </c>
       <c r="J255" s="53" t="n">
         <f aca="false">G255*I255</f>
-        <v>840</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="5" t="n">
-        <v>197</v>
-      </c>
-      <c r="B256" s="6" t="s">
+      <c r="A256" s="54"/>
+      <c r="B256" s="54"/>
+      <c r="C256" s="54"/>
+      <c r="D256" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="E256" s="54"/>
+      <c r="F256" s="54"/>
+      <c r="G256" s="54"/>
+      <c r="H256" s="54"/>
+      <c r="I256" s="54"/>
+      <c r="J256" s="12" t="n">
+        <f aca="false">SUM(J255:J255)</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C256" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D256" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="E256" s="50"/>
-      <c r="F256" s="51"/>
-      <c r="G256" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H256" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I256" s="7" t="n">
-        <f aca="false">Narxlar!$C$17</f>
-        <v>303</v>
-      </c>
-      <c r="J256" s="53" t="n">
-        <f aca="false">G256*I256</f>
-        <v>303</v>
-      </c>
-    </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="5" t="n">
-        <v>198</v>
-      </c>
-      <c r="B257" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C257" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D257" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="E257" s="50"/>
-      <c r="F257" s="51"/>
-      <c r="G257" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H257" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I257" s="7" t="n">
-        <f aca="false">Narxlar!$C$18</f>
-        <v>2500</v>
-      </c>
-      <c r="J257" s="53" t="n">
-        <f aca="false">G257*I257</f>
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="5" t="n">
-        <v>199</v>
-      </c>
-      <c r="B258" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C258" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D258" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E258" s="50"/>
-      <c r="F258" s="51"/>
-      <c r="G258" s="33" t="n">
-        <f aca="false">Narxlar!$C$21</f>
-        <v>8</v>
-      </c>
-      <c r="H258" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I258" s="7" t="n">
-        <f aca="false">Narxlar!$C$20/Narxlar!$C$19</f>
-        <v>67.2268907563025</v>
-      </c>
-      <c r="J258" s="53" t="n">
-        <f aca="false">G258*I258</f>
-        <v>537.81512605042</v>
-      </c>
+      <c r="B258" s="30"/>
+      <c r="C258" s="30"/>
+      <c r="D258" s="30"/>
+      <c r="E258" s="30"/>
+      <c r="F258" s="30"/>
+      <c r="G258" s="30"/>
+      <c r="H258" s="30"/>
+      <c r="I258" s="30"/>
+      <c r="J258" s="30"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="5" t="n">
@@ -14267,26 +14408,27 @@
         <v>82</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>359</v>
+        <v>111</v>
       </c>
       <c r="E259" s="50"/>
       <c r="F259" s="51"/>
-      <c r="G259" s="52" t="n">
-        <v>1</v>
+      <c r="G259" s="33" t="n">
+        <f aca="false">Narxlar!$C$14</f>
+        <v>16</v>
       </c>
       <c r="H259" s="5" t="s">
-        <v>245</v>
+        <v>113</v>
       </c>
       <c r="I259" s="7" t="n">
-        <f aca="false">Narxlar!$C$22/Narxlar!$C$19</f>
-        <v>1512.60504201681</v>
+        <f aca="false">Narxlar!$C$13</f>
+        <v>40</v>
       </c>
       <c r="J259" s="53" t="n">
         <f aca="false">G259*I259</f>
-        <v>1512.60504201681</v>
+        <v>640</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14297,32 +14439,27 @@
         <v>82</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="E260" s="50" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F260" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
-        <v>3.5</v>
-      </c>
-      <c r="G260" s="51" t="n">
-        <f aca="false">E260*F260</f>
-        <v>3.85</v>
+        <v>369</v>
+      </c>
+      <c r="E260" s="50"/>
+      <c r="F260" s="51"/>
+      <c r="G260" s="33" t="n">
+        <f aca="false">Narxlar!$C$14</f>
+        <v>16</v>
       </c>
       <c r="H260" s="5" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="I260" s="7" t="n">
-        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
-        <v>4.20168067226891</v>
+        <f aca="false">Narxlar!$C$15</f>
+        <v>21</v>
       </c>
       <c r="J260" s="53" t="n">
         <f aca="false">G260*I260</f>
-        <v>16.1764705882353</v>
+        <v>336</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14333,32 +14470,26 @@
         <v>82</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E261" s="50" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F261" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
-        <v>3.5</v>
-      </c>
-      <c r="G261" s="51" t="n">
-        <f aca="false">E261*F261</f>
-        <v>19.6</v>
+        <v>115</v>
+      </c>
+      <c r="E261" s="50"/>
+      <c r="F261" s="51"/>
+      <c r="G261" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="H261" s="5" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="I261" s="7" t="n">
-        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
-        <v>4.20168067226891</v>
+        <f aca="false">Narxlar!$C$16</f>
+        <v>840</v>
       </c>
       <c r="J261" s="53" t="n">
         <f aca="false">G261*I261</f>
-        <v>82.3529411764706</v>
+        <v>840</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14369,32 +14500,26 @@
         <v>82</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E262" s="50" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F262" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
-        <v>3.5</v>
-      </c>
-      <c r="G262" s="51" t="n">
-        <f aca="false">E262*F262</f>
-        <v>19.6</v>
+        <v>370</v>
+      </c>
+      <c r="E262" s="50"/>
+      <c r="F262" s="51"/>
+      <c r="G262" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="H262" s="5" t="s">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="I262" s="7" t="n">
-        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
-        <v>4.20168067226891</v>
+        <f aca="false">Narxlar!$C$17</f>
+        <v>303</v>
       </c>
       <c r="J262" s="53" t="n">
         <f aca="false">G262*I262</f>
-        <v>82.3529411764706</v>
+        <v>303</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14405,32 +14530,26 @@
         <v>82</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E263" s="50" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F263" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
-        <v>3.5</v>
-      </c>
-      <c r="G263" s="51" t="n">
-        <f aca="false">E263*F263</f>
-        <v>2.625</v>
+        <v>371</v>
+      </c>
+      <c r="E263" s="50"/>
+      <c r="F263" s="51"/>
+      <c r="G263" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="I263" s="7" t="n">
-        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
-        <v>4.20168067226891</v>
+        <f aca="false">Narxlar!$C$18</f>
+        <v>2500</v>
       </c>
       <c r="J263" s="53" t="n">
         <f aca="false">G263*I263</f>
-        <v>11.0294117647059</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14441,32 +14560,27 @@
         <v>82</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E264" s="50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F264" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
-        <v>3.5</v>
-      </c>
-      <c r="G264" s="51" t="n">
-        <f aca="false">E264*F264</f>
-        <v>11.9</v>
+        <v>372</v>
+      </c>
+      <c r="E264" s="50"/>
+      <c r="F264" s="51"/>
+      <c r="G264" s="33" t="n">
+        <f aca="false">Narxlar!$C$21</f>
+        <v>8</v>
       </c>
       <c r="H264" s="5" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="I264" s="7" t="n">
-        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
-        <v>4.20168067226891</v>
+        <f aca="false">Narxlar!$C$20/Narxlar!$C$19</f>
+        <v>67.2268907563025</v>
       </c>
       <c r="J264" s="53" t="n">
         <f aca="false">G264*I264</f>
-        <v>50</v>
+        <v>537.81512605042</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14477,32 +14591,26 @@
         <v>82</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="E265" s="50" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F265" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
-        <v>3.5</v>
-      </c>
-      <c r="G265" s="51" t="n">
-        <f aca="false">E265*F265</f>
-        <v>14.7</v>
+        <v>373</v>
+      </c>
+      <c r="E265" s="50"/>
+      <c r="F265" s="51"/>
+      <c r="G265" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="H265" s="5" t="s">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="I265" s="7" t="n">
-        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
-        <v>4.20168067226891</v>
+        <f aca="false">Narxlar!$C$22/Narxlar!$C$19</f>
+        <v>1512.60504201681</v>
       </c>
       <c r="J265" s="53" t="n">
         <f aca="false">G265*I265</f>
-        <v>61.764705882353</v>
+        <v>1512.60504201681</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14516,18 +14624,18 @@
         <v>18</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="E266" s="50" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F266" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G266" s="51" t="n">
         <f aca="false">E266*F266</f>
-        <v>5.25</v>
+        <v>3.85</v>
       </c>
       <c r="H266" s="5" t="s">
         <v>157</v>
@@ -14538,7 +14646,7 @@
       </c>
       <c r="J266" s="53" t="n">
         <f aca="false">G266*I266</f>
-        <v>22.0588235294118</v>
+        <v>16.1764705882353</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14552,18 +14660,18 @@
         <v>18</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="E267" s="50" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="F267" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G267" s="51" t="n">
         <f aca="false">E267*F267</f>
-        <v>0.7</v>
+        <v>19.6</v>
       </c>
       <c r="H267" s="5" t="s">
         <v>157</v>
@@ -14574,7 +14682,7 @@
       </c>
       <c r="J267" s="53" t="n">
         <f aca="false">G267*I267</f>
-        <v>2.94117647058824</v>
+        <v>82.3529411764706</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14588,18 +14696,18 @@
         <v>18</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="E268" s="50" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="F268" s="31" t="n">
-        <f aca="false">Narxlar!$C$71</f>
+        <f aca="false">Narxlar!$C$77</f>
         <v>3.5</v>
       </c>
       <c r="G268" s="51" t="n">
         <f aca="false">E268*F268</f>
-        <v>5.25</v>
+        <v>19.6</v>
       </c>
       <c r="H268" s="5" t="s">
         <v>157</v>
@@ -14610,7 +14718,7 @@
       </c>
       <c r="J268" s="53" t="n">
         <f aca="false">G268*I268</f>
-        <v>22.0588235294118</v>
+        <v>82.3529411764706</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14624,23 +14732,29 @@
         <v>18</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="E269" s="50"/>
-      <c r="F269" s="51"/>
-      <c r="G269" s="52" t="n">
-        <v>1</v>
+        <v>375</v>
+      </c>
+      <c r="E269" s="50" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F269" s="31" t="n">
+        <f aca="false">Narxlar!$C$77</f>
+        <v>3.5</v>
+      </c>
+      <c r="G269" s="51" t="n">
+        <f aca="false">E269*F269</f>
+        <v>2.625</v>
       </c>
       <c r="H269" s="5" t="s">
-        <v>245</v>
+        <v>157</v>
       </c>
       <c r="I269" s="7" t="n">
-        <f aca="false">Narxlar!$C$24/Narxlar!$C$19</f>
-        <v>100.840336134454</v>
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
       </c>
       <c r="J269" s="53" t="n">
         <f aca="false">G269*I269</f>
-        <v>100.840336134454</v>
+        <v>11.0294117647059</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14651,26 +14765,32 @@
         <v>82</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="E270" s="50"/>
-      <c r="F270" s="51"/>
-      <c r="G270" s="52" t="n">
-        <v>1</v>
+        <v>375</v>
+      </c>
+      <c r="E270" s="50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F270" s="31" t="n">
+        <f aca="false">Narxlar!$C$77</f>
+        <v>3.5</v>
+      </c>
+      <c r="G270" s="51" t="n">
+        <f aca="false">E270*F270</f>
+        <v>11.9</v>
       </c>
       <c r="H270" s="5" t="s">
-        <v>245</v>
+        <v>157</v>
       </c>
       <c r="I270" s="7" t="n">
-        <f aca="false">Narxlar!$C$52</f>
-        <v>7000</v>
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
       </c>
       <c r="J270" s="53" t="n">
         <f aca="false">G270*I270</f>
-        <v>7000</v>
+        <v>50</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14681,480 +14801,498 @@
         <v>82</v>
       </c>
       <c r="C271" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D271" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E271" s="50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F271" s="31" t="n">
+        <f aca="false">Narxlar!$C$77</f>
+        <v>3.5</v>
+      </c>
+      <c r="G271" s="51" t="n">
+        <f aca="false">E271*F271</f>
+        <v>14.7</v>
+      </c>
+      <c r="H271" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I271" s="7" t="n">
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
+      </c>
+      <c r="J271" s="53" t="n">
+        <f aca="false">G271*I271</f>
+        <v>61.764705882353</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E272" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F272" s="31" t="n">
+        <f aca="false">Narxlar!$C$77</f>
+        <v>3.5</v>
+      </c>
+      <c r="G272" s="51" t="n">
+        <f aca="false">E272*F272</f>
+        <v>5.25</v>
+      </c>
+      <c r="H272" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I272" s="7" t="n">
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
+      </c>
+      <c r="J272" s="53" t="n">
+        <f aca="false">G272*I272</f>
+        <v>22.0588235294118</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D273" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E273" s="50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F273" s="31" t="n">
+        <f aca="false">Narxlar!$C$77</f>
+        <v>3.5</v>
+      </c>
+      <c r="G273" s="51" t="n">
+        <f aca="false">E273*F273</f>
+        <v>0.7</v>
+      </c>
+      <c r="H273" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I273" s="7" t="n">
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
+      </c>
+      <c r="J273" s="53" t="n">
+        <f aca="false">G273*I273</f>
+        <v>2.94117647058824</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D274" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E274" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F274" s="31" t="n">
+        <f aca="false">Narxlar!$C$77</f>
+        <v>3.5</v>
+      </c>
+      <c r="G274" s="51" t="n">
+        <f aca="false">E274*F274</f>
+        <v>5.25</v>
+      </c>
+      <c r="H274" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I274" s="7" t="n">
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
+      </c>
+      <c r="J274" s="53" t="n">
+        <f aca="false">G274*I274</f>
+        <v>22.0588235294118</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E275" s="50"/>
+      <c r="F275" s="51"/>
+      <c r="G275" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H275" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I275" s="7" t="n">
+        <f aca="false">Narxlar!$C$24/Narxlar!$C$19</f>
+        <v>100.840336134454</v>
+      </c>
+      <c r="J275" s="53" t="n">
+        <f aca="false">G275*I275</f>
+        <v>100.840336134454</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C276" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D271" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="E271" s="50"/>
-      <c r="F271" s="51"/>
-      <c r="G271" s="52" t="n">
+      <c r="D276" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E276" s="50"/>
+      <c r="F276" s="51"/>
+      <c r="G276" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="H271" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I271" s="7" t="n">
+      <c r="H276" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I276" s="7" t="n">
+        <f aca="false">Narxlar!$C$52</f>
+        <v>7000</v>
+      </c>
+      <c r="J276" s="53" t="n">
+        <f aca="false">G276*I276</f>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D277" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E277" s="50"/>
+      <c r="F277" s="51"/>
+      <c r="G277" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I277" s="7" t="n">
         <f aca="false">Narxlar!$C$53</f>
         <v>7000</v>
       </c>
-      <c r="J271" s="53" t="n">
-        <f aca="false">G271*I271</f>
+      <c r="J277" s="53" t="n">
+        <f aca="false">G277*I277</f>
         <v>7000</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="54"/>
-      <c r="B272" s="54"/>
-      <c r="C272" s="54"/>
-      <c r="D272" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="E272" s="54"/>
-      <c r="F272" s="54"/>
-      <c r="G272" s="54"/>
-      <c r="H272" s="54"/>
-      <c r="I272" s="54"/>
-      <c r="J272" s="12" t="n">
-        <f aca="false">SUM(J253:J271)</f>
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="54"/>
+      <c r="B278" s="54"/>
+      <c r="C278" s="54"/>
+      <c r="D278" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="E278" s="54"/>
+      <c r="F278" s="54"/>
+      <c r="G278" s="54"/>
+      <c r="H278" s="54"/>
+      <c r="I278" s="54"/>
+      <c r="J278" s="12" t="n">
+        <f aca="false">SUM(J259:J277)</f>
         <v>21120.9957983193</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="29" t="s">
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="B274" s="30"/>
-      <c r="C274" s="30"/>
-      <c r="D274" s="30"/>
-      <c r="E274" s="30"/>
-      <c r="F274" s="30"/>
-      <c r="G274" s="30"/>
-      <c r="H274" s="30"/>
-      <c r="I274" s="30"/>
-      <c r="J274" s="30"/>
-    </row>
-    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="5" t="n">
-        <v>213</v>
-      </c>
-      <c r="B275" s="6" t="s">
+      <c r="B280" s="30"/>
+      <c r="C280" s="30"/>
+      <c r="D280" s="30"/>
+      <c r="E280" s="30"/>
+      <c r="F280" s="30"/>
+      <c r="G280" s="30"/>
+      <c r="H280" s="30"/>
+      <c r="I280" s="30"/>
+      <c r="J280" s="30"/>
+    </row>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="5" t="n">
+        <v>219</v>
+      </c>
+      <c r="B281" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C275" s="6" t="s">
+      <c r="C281" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D275" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="E275" s="50" t="n">
+      <c r="D281" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E281" s="50" t="n">
         <v>5.45</v>
       </c>
-      <c r="F275" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+      <c r="F281" s="31" t="n">
+        <f aca="false">Narxlar!$C$84</f>
         <v>2.5</v>
       </c>
-      <c r="G275" s="51" t="n">
-        <f aca="false">E275*F275</f>
+      <c r="G281" s="51" t="n">
+        <f aca="false">E281*F281</f>
         <v>13.625</v>
       </c>
-      <c r="H275" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I275" s="7" t="n">
+      <c r="H281" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I281" s="7" t="n">
         <f aca="false">Narxlar!$C$7</f>
         <v>15.5</v>
       </c>
-      <c r="J275" s="53" t="n">
-        <f aca="false">G275*I275</f>
+      <c r="J281" s="53" t="n">
+        <f aca="false">G281*I281</f>
         <v>211.1875</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="5" t="n">
-        <v>214</v>
-      </c>
-      <c r="B276" s="6" t="s">
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="B282" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C276" s="6" t="s">
+      <c r="C282" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D276" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="E276" s="50" t="n">
+      <c r="D282" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E282" s="50" t="n">
         <v>5.45</v>
       </c>
-      <c r="F276" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+      <c r="F282" s="31" t="n">
+        <f aca="false">Narxlar!$C$84</f>
         <v>2.5</v>
       </c>
-      <c r="G276" s="51" t="n">
-        <f aca="false">E276*F276</f>
+      <c r="G282" s="51" t="n">
+        <f aca="false">E282*F282</f>
         <v>13.625</v>
       </c>
-      <c r="H276" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I276" s="7" t="n">
+      <c r="H282" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I282" s="7" t="n">
         <f aca="false">Narxlar!$C$7</f>
         <v>15.5</v>
       </c>
-      <c r="J276" s="53" t="n">
-        <f aca="false">G276*I276</f>
+      <c r="J282" s="53" t="n">
+        <f aca="false">G282*I282</f>
         <v>211.1875</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="5" t="n">
-        <v>215</v>
-      </c>
-      <c r="B277" s="6" t="s">
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="B283" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C277" s="6" t="s">
+      <c r="C283" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D277" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="E277" s="50" t="n">
+      <c r="D283" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E283" s="50" t="n">
         <v>8.6</v>
       </c>
-      <c r="F277" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+      <c r="F283" s="31" t="n">
+        <f aca="false">Narxlar!$C$84</f>
         <v>2.5</v>
       </c>
-      <c r="G277" s="51" t="n">
-        <f aca="false">E277*F277</f>
+      <c r="G283" s="51" t="n">
+        <f aca="false">E283*F283</f>
         <v>21.5</v>
       </c>
-      <c r="H277" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I277" s="7" t="n">
+      <c r="H283" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I283" s="7" t="n">
         <f aca="false">Narxlar!$C$7</f>
         <v>15.5</v>
       </c>
-      <c r="J277" s="53" t="n">
-        <f aca="false">G277*I277</f>
+      <c r="J283" s="53" t="n">
+        <f aca="false">G283*I283</f>
         <v>333.25</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="5" t="n">
-        <v>216</v>
-      </c>
-      <c r="B278" s="6" t="s">
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="B284" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C278" s="6" t="s">
+      <c r="C284" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D278" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="E278" s="31" t="n">
-        <f aca="false">Narxlar!$C$76</f>
+      <c r="D284" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="E284" s="31" t="n">
+        <f aca="false">Narxlar!$C$82</f>
         <v>0.9</v>
       </c>
-      <c r="F278" s="31" t="n">
-        <f aca="false">Narxlar!$C$74</f>
+      <c r="F284" s="31" t="n">
+        <f aca="false">Narxlar!$C$80</f>
         <v>2.1</v>
       </c>
-      <c r="G278" s="51" t="n">
-        <f aca="false">-E278*F278</f>
+      <c r="G284" s="51" t="n">
+        <f aca="false">-E284*F284</f>
         <v>-1.89</v>
       </c>
-      <c r="H278" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I278" s="7" t="n">
+      <c r="H284" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I284" s="7" t="n">
         <f aca="false">Narxlar!$C$7</f>
         <v>15.5</v>
       </c>
-      <c r="J278" s="53" t="n">
-        <f aca="false">G278*I278</f>
+      <c r="J284" s="53" t="n">
+        <f aca="false">G284*I284</f>
         <v>-29.295</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="5" t="n">
-        <v>217</v>
-      </c>
-      <c r="B279" s="6" t="s">
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="B285" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C279" s="6" t="s">
+      <c r="C285" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D279" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="E279" s="50"/>
-      <c r="F279" s="51"/>
-      <c r="G279" s="52" t="n">
+      <c r="D285" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E285" s="50"/>
+      <c r="F285" s="51"/>
+      <c r="G285" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="H279" s="5" t="s">
+      <c r="H285" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I279" s="7" t="n">
+      <c r="I285" s="7" t="n">
         <f aca="false">Narxlar!$C$8</f>
         <v>1032</v>
       </c>
-      <c r="J279" s="53" t="n">
-        <f aca="false">G279*I279</f>
+      <c r="J285" s="53" t="n">
+        <f aca="false">G285*I285</f>
         <v>1032</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="5" t="n">
-        <v>218</v>
-      </c>
-      <c r="B280" s="6" t="s">
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="B286" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C280" s="6" t="s">
+      <c r="C286" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D280" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="E280" s="50"/>
-      <c r="F280" s="51"/>
-      <c r="G280" s="52" t="n">
+      <c r="D286" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E286" s="50"/>
+      <c r="F286" s="51"/>
+      <c r="G286" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="H280" s="5" t="s">
+      <c r="H286" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I280" s="7" t="n">
+      <c r="I286" s="7" t="n">
         <f aca="false">Narxlar!$C$54</f>
         <v>1000</v>
       </c>
-      <c r="J280" s="53" t="n">
-        <f aca="false">G280*I280</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="54"/>
-      <c r="B281" s="54"/>
-      <c r="C281" s="54"/>
-      <c r="D281" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="E281" s="54"/>
-      <c r="F281" s="54"/>
-      <c r="G281" s="54"/>
-      <c r="H281" s="54"/>
-      <c r="I281" s="54"/>
-      <c r="J281" s="12" t="n">
-        <f aca="false">SUM(J275:J280)</f>
-        <v>2758.33</v>
-      </c>
-    </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="B283" s="30"/>
-      <c r="C283" s="30"/>
-      <c r="D283" s="30"/>
-      <c r="E283" s="30"/>
-      <c r="F283" s="30"/>
-      <c r="G283" s="30"/>
-      <c r="H283" s="30"/>
-      <c r="I283" s="30"/>
-      <c r="J283" s="30"/>
-    </row>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="5" t="n">
-        <v>219</v>
-      </c>
-      <c r="B284" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C284" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D284" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="E284" s="50"/>
-      <c r="F284" s="51"/>
-      <c r="G284" s="33" t="n">
-        <f aca="false">Narxlar!$C$26</f>
-        <v>3</v>
-      </c>
-      <c r="H284" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I284" s="7" t="n">
-        <f aca="false">Narxlar!$C$25/Narxlar!$C$19</f>
-        <v>58.8235294117647</v>
-      </c>
-      <c r="J284" s="53" t="n">
-        <f aca="false">G284*I284</f>
-        <v>176.470588235294</v>
-      </c>
-    </row>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="5" t="n">
-        <v>220</v>
-      </c>
-      <c r="B285" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C285" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D285" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="E285" s="50"/>
-      <c r="F285" s="51"/>
-      <c r="G285" s="33" t="n">
-        <f aca="false">Narxlar!$C$28</f>
-        <v>3</v>
-      </c>
-      <c r="H285" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I285" s="7" t="n">
-        <f aca="false">Narxlar!$C$27/Narxlar!$C$19</f>
-        <v>100.840336134454</v>
-      </c>
-      <c r="J285" s="53" t="n">
-        <f aca="false">G285*I285</f>
-        <v>302.521008403361</v>
-      </c>
-    </row>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="B286" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C286" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D286" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="E286" s="50"/>
-      <c r="F286" s="51"/>
-      <c r="G286" s="33" t="n">
-        <f aca="false">Narxlar!$C$30</f>
-        <v>4</v>
-      </c>
-      <c r="H286" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I286" s="7" t="n">
-        <f aca="false">Narxlar!$C$29/Narxlar!$C$19</f>
-        <v>54.6218487394958</v>
-      </c>
       <c r="J286" s="53" t="n">
         <f aca="false">G286*I286</f>
-        <v>218.487394957983</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="5" t="n">
-        <v>222</v>
-      </c>
-      <c r="B287" s="6" t="s">
+      <c r="A287" s="54"/>
+      <c r="B287" s="54"/>
+      <c r="C287" s="54"/>
+      <c r="D287" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="E287" s="54"/>
+      <c r="F287" s="54"/>
+      <c r="G287" s="54"/>
+      <c r="H287" s="54"/>
+      <c r="I287" s="54"/>
+      <c r="J287" s="12" t="n">
+        <f aca="false">SUM(J281:J286)</f>
+        <v>2758.33</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="C287" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D287" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E287" s="50"/>
-      <c r="F287" s="51"/>
-      <c r="G287" s="33" t="n">
-        <f aca="false">Narxlar!$C$32</f>
-        <v>6</v>
-      </c>
-      <c r="H287" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I287" s="7" t="n">
-        <f aca="false">Narxlar!$C$31/Narxlar!$C$19</f>
-        <v>16.8067226890756</v>
-      </c>
-      <c r="J287" s="53" t="n">
-        <f aca="false">G287*I287</f>
-        <v>100.840336134454</v>
-      </c>
-    </row>
-    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="5" t="n">
-        <v>223</v>
-      </c>
-      <c r="B288" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C288" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D288" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="E288" s="50"/>
-      <c r="F288" s="51"/>
-      <c r="G288" s="33" t="n">
-        <f aca="false">Narxlar!$C$34</f>
-        <v>4</v>
-      </c>
-      <c r="H288" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I288" s="7" t="n">
-        <f aca="false">Narxlar!$C$33/Narxlar!$C$19</f>
-        <v>33.6134453781513</v>
-      </c>
-      <c r="J288" s="53" t="n">
-        <f aca="false">G288*I288</f>
-        <v>134.453781512605</v>
-      </c>
-    </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="5" t="n">
-        <v>224</v>
-      </c>
-      <c r="B289" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C289" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D289" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="E289" s="50"/>
-      <c r="F289" s="51"/>
-      <c r="G289" s="33" t="n">
-        <f aca="false">Narxlar!$C$36</f>
-        <v>4</v>
-      </c>
-      <c r="H289" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I289" s="7" t="n">
-        <f aca="false">Narxlar!$C$35/Narxlar!$C$19</f>
-        <v>33.6134453781513</v>
-      </c>
-      <c r="J289" s="53" t="n">
-        <f aca="false">G289*I289</f>
-        <v>134.453781512605</v>
-      </c>
+      <c r="B289" s="30"/>
+      <c r="C289" s="30"/>
+      <c r="D289" s="30"/>
+      <c r="E289" s="30"/>
+      <c r="F289" s="30"/>
+      <c r="G289" s="30"/>
+      <c r="H289" s="30"/>
+      <c r="I289" s="30"/>
+      <c r="J289" s="30"/>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="5" t="n">
@@ -15167,24 +15305,24 @@
         <v>19</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="E290" s="50"/>
       <c r="F290" s="51"/>
       <c r="G290" s="33" t="n">
-        <f aca="false">Narxlar!$C$38</f>
-        <v>16</v>
+        <f aca="false">Narxlar!$C$26</f>
+        <v>3</v>
       </c>
       <c r="H290" s="5" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="I290" s="7" t="n">
-        <f aca="false">Narxlar!$C$37/Narxlar!$C$19</f>
-        <v>84.0336134453782</v>
+        <f aca="false">Narxlar!$C$25/Narxlar!$C$19</f>
+        <v>58.8235294117647</v>
       </c>
       <c r="J290" s="53" t="n">
         <f aca="false">G290*I290</f>
-        <v>1344.53781512605</v>
+        <v>176.470588235294</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15198,24 +15336,24 @@
         <v>19</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="E291" s="50"/>
       <c r="F291" s="51"/>
       <c r="G291" s="33" t="n">
-        <f aca="false">Narxlar!$C$44</f>
-        <v>4</v>
+        <f aca="false">Narxlar!$C$28</f>
+        <v>3</v>
       </c>
       <c r="H291" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I291" s="7" t="n">
-        <f aca="false">Narxlar!$C$43/Narxlar!$C$19</f>
+        <f aca="false">Narxlar!$C$27/Narxlar!$C$19</f>
         <v>100.840336134454</v>
       </c>
       <c r="J291" s="53" t="n">
         <f aca="false">G291*I291</f>
-        <v>403.361344537815</v>
+        <v>302.521008403361</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15229,24 +15367,24 @@
         <v>19</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>162</v>
+        <v>390</v>
       </c>
       <c r="E292" s="50"/>
       <c r="F292" s="51"/>
-      <c r="G292" s="31" t="n">
-        <f aca="false">Narxlar!$C$46</f>
-        <v>40</v>
+      <c r="G292" s="33" t="n">
+        <f aca="false">Narxlar!$C$30</f>
+        <v>4</v>
       </c>
       <c r="H292" s="5" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I292" s="7" t="n">
-        <f aca="false">Narxlar!$C$45/Narxlar!$C$19</f>
-        <v>2.10084033613445</v>
+        <f aca="false">Narxlar!$C$29/Narxlar!$C$19</f>
+        <v>54.6218487394958</v>
       </c>
       <c r="J292" s="53" t="n">
         <f aca="false">G292*I292</f>
-        <v>84.0336134453782</v>
+        <v>218.487394957983</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15260,24 +15398,24 @@
         <v>19</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>165</v>
+        <v>391</v>
       </c>
       <c r="E293" s="50"/>
       <c r="F293" s="51"/>
-      <c r="G293" s="31" t="n">
-        <f aca="false">Narxlar!$C$48</f>
-        <v>40</v>
+      <c r="G293" s="33" t="n">
+        <f aca="false">Narxlar!$C$32</f>
+        <v>6</v>
       </c>
       <c r="H293" s="5" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I293" s="7" t="n">
-        <f aca="false">Narxlar!$C$47/Narxlar!$C$19</f>
-        <v>1.00840336134454</v>
+        <f aca="false">Narxlar!$C$31/Narxlar!$C$19</f>
+        <v>16.8067226890756</v>
       </c>
       <c r="J293" s="53" t="n">
         <f aca="false">G293*I293</f>
-        <v>40.3361344537815</v>
+        <v>100.840336134454</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15291,24 +15429,24 @@
         <v>19</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>168</v>
+        <v>392</v>
       </c>
       <c r="E294" s="50"/>
       <c r="F294" s="51"/>
       <c r="G294" s="33" t="n">
-        <f aca="false">Narxlar!$C$50</f>
-        <v>100</v>
+        <f aca="false">Narxlar!$C$34</f>
+        <v>4</v>
       </c>
       <c r="H294" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I294" s="7" t="n">
-        <f aca="false">Narxlar!$C$49/Narxlar!$C$19</f>
-        <v>0.420168067226891</v>
+        <f aca="false">Narxlar!$C$33/Narxlar!$C$19</f>
+        <v>33.6134453781513</v>
       </c>
       <c r="J294" s="53" t="n">
         <f aca="false">G294*I294</f>
-        <v>42.0168067226891</v>
+        <v>134.453781512605</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15322,23 +15460,24 @@
         <v>19</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="E295" s="50"/>
       <c r="F295" s="51"/>
-      <c r="G295" s="52" t="n">
-        <v>1</v>
+      <c r="G295" s="33" t="n">
+        <f aca="false">Narxlar!$C$36</f>
+        <v>4</v>
       </c>
       <c r="H295" s="5" t="s">
-        <v>245</v>
+        <v>113</v>
       </c>
       <c r="I295" s="7" t="n">
-        <f aca="false">Narxlar!$C$51/Narxlar!$C$19</f>
-        <v>336.134453781513</v>
+        <f aca="false">Narxlar!$C$35/Narxlar!$C$19</f>
+        <v>33.6134453781513</v>
       </c>
       <c r="J295" s="53" t="n">
         <f aca="false">G295*I295</f>
-        <v>336.134453781513</v>
+        <v>134.453781512605</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15349,27 +15488,27 @@
         <v>85</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="E296" s="50"/>
       <c r="F296" s="51"/>
-      <c r="G296" s="31" t="n">
-        <f aca="false">Narxlar!$C$41</f>
-        <v>58</v>
+      <c r="G296" s="33" t="n">
+        <f aca="false">Narxlar!$C$38</f>
+        <v>16</v>
       </c>
       <c r="H296" s="5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I296" s="7" t="n">
-        <f aca="false">Narxlar!$C$39/Narxlar!$C$19</f>
-        <v>8.40336134453782</v>
+        <f aca="false">Narxlar!$C$37/Narxlar!$C$19</f>
+        <v>84.0336134453782</v>
       </c>
       <c r="J296" s="53" t="n">
         <f aca="false">G296*I296</f>
-        <v>487.394957983193</v>
+        <v>1344.53781512605</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15380,27 +15519,27 @@
         <v>85</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="E297" s="50"/>
       <c r="F297" s="51"/>
-      <c r="G297" s="31" t="n">
-        <f aca="false">Narxlar!$C$41</f>
-        <v>58</v>
+      <c r="G297" s="33" t="n">
+        <f aca="false">Narxlar!$C$44</f>
+        <v>4</v>
       </c>
       <c r="H297" s="5" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="I297" s="7" t="n">
-        <f aca="false">Narxlar!$C$40/Narxlar!$C$19</f>
-        <v>8.40336134453782</v>
+        <f aca="false">Narxlar!$C$43/Narxlar!$C$19</f>
+        <v>100.840336134454</v>
       </c>
       <c r="J297" s="53" t="n">
         <f aca="false">G297*I297</f>
-        <v>487.394957983193</v>
+        <v>403.361344537815</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15411,27 +15550,27 @@
         <v>85</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>385</v>
+        <v>162</v>
       </c>
       <c r="E298" s="50"/>
       <c r="F298" s="51"/>
       <c r="G298" s="31" t="n">
-        <f aca="false">Narxlar!$C$42</f>
-        <v>16</v>
+        <f aca="false">Narxlar!$C$46</f>
+        <v>40</v>
       </c>
       <c r="H298" s="5" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="I298" s="7" t="n">
-        <f aca="false">Narxlar!$C$39/Narxlar!$C$19</f>
-        <v>8.40336134453782</v>
+        <f aca="false">Narxlar!$C$45/Narxlar!$C$19</f>
+        <v>2.10084033613445</v>
       </c>
       <c r="J298" s="53" t="n">
         <f aca="false">G298*I298</f>
-        <v>134.453781512605</v>
+        <v>84.0336134453782</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15442,61 +15581,246 @@
         <v>85</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>386</v>
+        <v>165</v>
       </c>
       <c r="E299" s="50"/>
       <c r="F299" s="51"/>
       <c r="G299" s="31" t="n">
+        <f aca="false">Narxlar!$C$48</f>
+        <v>40</v>
+      </c>
+      <c r="H299" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I299" s="7" t="n">
+        <f aca="false">Narxlar!$C$47/Narxlar!$C$19</f>
+        <v>1.00840336134454</v>
+      </c>
+      <c r="J299" s="53" t="n">
+        <f aca="false">G299*I299</f>
+        <v>40.3361344537815</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D300" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E300" s="50"/>
+      <c r="F300" s="51"/>
+      <c r="G300" s="33" t="n">
+        <f aca="false">Narxlar!$C$50</f>
+        <v>100</v>
+      </c>
+      <c r="H300" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I300" s="7" t="n">
+        <f aca="false">Narxlar!$C$49/Narxlar!$C$19</f>
+        <v>0.420168067226891</v>
+      </c>
+      <c r="J300" s="53" t="n">
+        <f aca="false">G300*I300</f>
+        <v>42.0168067226891</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="5" t="n">
+        <v>236</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E301" s="50"/>
+      <c r="F301" s="51"/>
+      <c r="G301" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H301" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I301" s="7" t="n">
+        <f aca="false">Narxlar!$C$51/Narxlar!$C$19</f>
+        <v>336.134453781513</v>
+      </c>
+      <c r="J301" s="53" t="n">
+        <f aca="false">G301*I301</f>
+        <v>336.134453781513</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="5" t="n">
+        <v>237</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D302" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="E302" s="50"/>
+      <c r="F302" s="51"/>
+      <c r="G302" s="31" t="n">
+        <f aca="false">Narxlar!$C$41</f>
+        <v>58</v>
+      </c>
+      <c r="H302" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I302" s="7" t="n">
+        <f aca="false">Narxlar!$C$39/Narxlar!$C$19</f>
+        <v>8.40336134453782</v>
+      </c>
+      <c r="J302" s="53" t="n">
+        <f aca="false">G302*I302</f>
+        <v>487.394957983193</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D303" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="E303" s="50"/>
+      <c r="F303" s="51"/>
+      <c r="G303" s="31" t="n">
+        <f aca="false">Narxlar!$C$41</f>
+        <v>58</v>
+      </c>
+      <c r="H303" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I303" s="7" t="n">
+        <f aca="false">Narxlar!$C$40/Narxlar!$C$19</f>
+        <v>8.40336134453782</v>
+      </c>
+      <c r="J303" s="53" t="n">
+        <f aca="false">G303*I303</f>
+        <v>487.394957983193</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="5" t="n">
+        <v>239</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D304" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="E304" s="50"/>
+      <c r="F304" s="51"/>
+      <c r="G304" s="31" t="n">
         <f aca="false">Narxlar!$C$42</f>
         <v>16</v>
       </c>
-      <c r="H299" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I299" s="7" t="n">
+      <c r="H304" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I304" s="7" t="n">
+        <f aca="false">Narxlar!$C$39/Narxlar!$C$19</f>
+        <v>8.40336134453782</v>
+      </c>
+      <c r="J304" s="53" t="n">
+        <f aca="false">G304*I304</f>
+        <v>134.453781512605</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D305" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E305" s="50"/>
+      <c r="F305" s="51"/>
+      <c r="G305" s="31" t="n">
+        <f aca="false">Narxlar!$C$42</f>
+        <v>16</v>
+      </c>
+      <c r="H305" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I305" s="7" t="n">
         <f aca="false">Narxlar!$C$40/Narxlar!$C$19</f>
         <v>8.40336134453782</v>
       </c>
-      <c r="J299" s="53" t="n">
-        <f aca="false">G299*I299</f>
+      <c r="J305" s="53" t="n">
+        <f aca="false">G305*I305</f>
         <v>134.453781512605</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="54"/>
-      <c r="B300" s="54"/>
-      <c r="C300" s="54"/>
-      <c r="D300" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="E300" s="54"/>
-      <c r="F300" s="54"/>
-      <c r="G300" s="54"/>
-      <c r="H300" s="54"/>
-      <c r="I300" s="54"/>
-      <c r="J300" s="12" t="n">
-        <f aca="false">SUM(J284:J299)</f>
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="54"/>
+      <c r="B306" s="54"/>
+      <c r="C306" s="54"/>
+      <c r="D306" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="E306" s="54"/>
+      <c r="F306" s="54"/>
+      <c r="G306" s="54"/>
+      <c r="H306" s="54"/>
+      <c r="I306" s="54"/>
+      <c r="J306" s="12" t="n">
+        <f aca="false">SUM(J290:J305)</f>
         <v>4561.34453781513</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="54"/>
-      <c r="B302" s="54"/>
-      <c r="C302" s="54"/>
-      <c r="D302" s="11" t="s">
-        <v>388</v>
-      </c>
-      <c r="E302" s="54"/>
-      <c r="F302" s="54"/>
-      <c r="G302" s="54"/>
-      <c r="H302" s="54"/>
-      <c r="I302" s="54"/>
-      <c r="J302" s="12" t="n">
-        <f aca="false">J13+J26+J38+J49+J67+J79+J93+J108+J129+J149+J164+J179+J186+J210+J235+J242+J246+J250+J272+J281+J300</f>
-        <v>67500.5503361345</v>
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="54"/>
+      <c r="B308" s="54"/>
+      <c r="C308" s="54"/>
+      <c r="D308" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="E308" s="54"/>
+      <c r="F308" s="54"/>
+      <c r="G308" s="54"/>
+      <c r="H308" s="54"/>
+      <c r="I308" s="54"/>
+      <c r="J308" s="12" t="n">
+        <f aca="false">J13+J26+J38+J49+J67+J79+J93+J108+J129+J149+J164+J179+J186+J210+J235+J248+J252+J256+J278+J287+J306</f>
+        <v>69860.5503361345</v>
       </c>
     </row>
   </sheetData>

--- a/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
+++ b/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="409">
   <si>
     <t xml:space="preserve">PDP Academy · Xadra filiali (1, 2 va 3-qavat): jami xarajatlar — yakuniy</t>
   </si>
@@ -610,24 +610,33 @@
     <t xml:space="preserve">Sahna: yog'och reykali panellar (2 × 0.95 × 3.5 m, qora asos ustida)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sahna logotipi ~2.0 m, ichidan yoritilgan (akril harflar, LED)</t>
+    <t xml:space="preserve">Sahna logotipi ~1.7 m, ichidan yoritilgan (akril harflar, LED)</t>
   </si>
   <si>
     <t xml:space="preserve">TAXMIN — reklama ustasi narxi bilan almashtiring</t>
   </si>
   <si>
-    <t xml:space="preserve">Sahna yoritishi: 3 ta yo'naltirilgan spot, shift ostida chiziqli LED, yashil LED chiziq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahna ekrani: koworkingdagi mavjud ekranni ko'chirish, kronshteyn va kabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAXMIN — ekran mavjud deb olingan</t>
+    <t xml:space="preserve">Sahna yoritishi: trek shina 5.2 m va 7 ta spot, tik va yuqori yashil LED chiziqlar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna ekrani 86": koworkingdagi mavjud ekranni ko'chirish, kronshteyn va kabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXMIN — ekran mavjud deb olingan; yangi 86" ekran ~$1 300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ovoz: 2 ta faol kolonka (devorga osiladi), simsiz mikrofon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna maydoni poli: yog'och ko'rinishli vinil ~9 m², pol bilan bir sathda (o'tish profili bilan)</t>
   </si>
   <si>
     <t xml:space="preserve">Minbar (tribuna), ko'chma, logotip bilan</t>
   </si>
   <si>
+    <t xml:space="preserve">Katta o'simlik tuvakda (sahna yonida)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Turniketlar (buyurtmachida mavjud: kirish va chiqish)</t>
   </si>
   <si>
@@ -739,7 +748,7 @@
     <t xml:space="preserve">• 2-qavat koridorlari: 4-xonaning koridor oxiridagi devorlari GKL (avval shisha edi), markazida yorituvchi logotip; e'lonlar va e'tirof doskalari — K1 va K2 qatorlarida.</t>
   </si>
   <si>
-    <t xml:space="preserve">• TAXMINIY narxlar (to'q sariq fon): sotuv va admin xonalari mebeli va interyeri, koridor doskalari, koworking sahnasi (karkas devor, reyka, logotip, yoritish, minbar), 1-qavat resepshn stoykasi, mehmonlar mebeli va logotiplari — Toshkent bozori bo'yicha dastlabki baho; mebelchi va reklama ustasi narxi bilan almashtiring. «Yakuniy» varag'ida taxminiy qism alohida ko'rsatilgan.</t>
+    <t xml:space="preserve">• TAXMINIY narxlar (to'q sariq fon): sotuv va admin xonalari mebeli va interyeri, koridor doskalari, koworking sahnasi (karkas devor, reyka, logotip, trek yoritish, ovoz, pol, minbar), 1-qavat resepshn stoykasi, mehmonlar mebeli va logotiplari — Toshkent bozori bo'yicha dastlabki baho; mebelchi va reklama ustasi narxi bilan almashtiring. «Yakuniy» varag'ida taxminiy qism alohida ko'rsatilgan.</t>
   </si>
   <si>
     <t xml:space="preserve">• Kirmagan: o'quv xonalari, ustozlar xonasi, call-markaz, CEO va koworking mebeli — mavjud; pol (kafel) va internet — mavjud; turniketlar (2 ta) — mavjud (o'rnatish, to'siq va evakuatsiya darvozasi alohida aniqlanadi); eshik furniturasi; shift va bo'yoq; ish haqi (agar narxga kirmagan bo'lsa).</t>
@@ -1111,13 +1120,22 @@
     <t xml:space="preserve">Sahna logotipi, ichidan yoritilgan (~2.0 m)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sahna yoritishi (spotlar, LED chiziqlar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ekranni sahna devoriga ko'chirish (kronshteyn, kabel)</t>
+    <t xml:space="preserve">Sahna yoritishi (trek shina, 7 ta spot, yashil LED chiziqlar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86" ekranni sahna devoriga ko'chirish (kronshteyn, kabel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ovoz tizimi: 2 ta kolonka (devorga), mikrofon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahna maydoni poli (vinil, pol bilan bir sathda)</t>
   </si>
   <si>
     <t xml:space="preserve">Minbar (tribuna)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'simlik (sahna yonida)</t>
   </si>
   <si>
     <t xml:space="preserve">Jami: Koworking zali</t>
@@ -1949,7 +1967,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>4991.25</v>
       </c>
       <c r="D6" s="8" t="n">
@@ -1958,7 +1976,7 @@
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C6/$C$22)</f>
-        <v>0.0714459015278948</v>
+        <v>0.0703879743753246</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1969,7 +1987,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>5146.8</v>
       </c>
       <c r="D7" s="8" t="n">
@@ -1978,7 +1996,7 @@
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C7/$C$22)</f>
-        <v>0.0736724800368182</v>
+        <v>0.0725815830733626</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1989,7 +2007,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>9404.16</v>
       </c>
       <c r="D8" s="8" t="n">
@@ -1998,7 +2016,7 @@
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C8/$C$22)</f>
-        <v>0.134613311157038</v>
+        <v>0.132620039689748</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2009,7 +2027,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>8256</v>
       </c>
       <c r="D9" s="8" t="n">
@@ -2018,7 +2036,7 @@
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C9/$C$22)</f>
-        <v>0.118178284600911</v>
+        <v>0.116428372941183</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2029,7 +2047,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>2016</v>
       </c>
       <c r="D10" s="8" t="n">
@@ -2038,7 +2056,7 @@
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C10/$C$22)</f>
-        <v>0.0288574881002226</v>
+        <v>0.0284301840902889</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2049,7 +2067,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>3024</v>
       </c>
       <c r="D11" s="8" t="n">
@@ -2058,7 +2076,7 @@
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C11/$C$22)</f>
-        <v>0.0432862321503339</v>
+        <v>0.0426452761354334</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2069,7 +2087,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>2119</v>
       </c>
       <c r="D12" s="8" t="n">
@@ -2078,7 +2096,7 @@
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C12/$C$22)</f>
-        <v>0.0303318538116923</v>
+        <v>0.0298827182972828</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,7 +2107,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>3250</v>
       </c>
       <c r="D13" s="8" t="n">
@@ -2098,7 +2116,7 @@
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C13/$C$22)</f>
-        <v>0.0465212481774421</v>
+        <v>0.0458323900265074</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2109,7 +2127,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>537.81512605042</v>
       </c>
       <c r="D14" s="8" t="n">
@@ -2118,7 +2136,7 @@
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C14/$C$22)</f>
-        <v>0.0076984095238689</v>
+        <v>0.00758441619055326</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2129,7 +2147,7 @@
         <v>17</v>
       </c>
       <c r="C15" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>1512.60504201681</v>
       </c>
       <c r="D15" s="8" t="n">
@@ -2138,7 +2156,7 @@
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C15/$C$22)</f>
-        <v>0.0216517767858813</v>
+        <v>0.021331170535931</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2149,7 +2167,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>451.575630252101</v>
       </c>
       <c r="D16" s="8" t="n">
@@ -2158,7 +2176,7 @@
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C16/$C$22)</f>
-        <v>0.00646395752795164</v>
+        <v>0.00636824320374775</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2169,7 +2187,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>3317.64705882353</v>
       </c>
       <c r="D17" s="8" t="n">
@@ -2178,7 +2196,7 @@
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C17/$C$22)</f>
-        <v>0.0474895637503663</v>
+        <v>0.0467863673754754</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2189,7 +2207,7 @@
         <v>20</v>
       </c>
       <c r="C18" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>1243.6974789916</v>
       </c>
       <c r="D18" s="8" t="n">
@@ -2198,7 +2216,7 @@
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C18/$C$22)</f>
-        <v>0.0178025720239468</v>
+        <v>0.0175389624406544</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2209,7 +2227,7 @@
         <v>21</v>
       </c>
       <c r="C19" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>15000</v>
       </c>
       <c r="D19" s="8" t="n">
@@ -2218,7 +2236,7 @@
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C19/$C$22)</f>
-        <v>0.214713453126656</v>
+        <v>0.21153410781465</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,16 +2247,16 @@
         <v>22</v>
       </c>
       <c r="C20" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
-        <v>8850</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <v>9900</v>
       </c>
       <c r="D20" s="8" t="n">
         <f aca="false">C20*Narxlar!$C$19</f>
-        <v>105315000</v>
+        <v>117810000</v>
       </c>
       <c r="E20" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C20/$C$22)</f>
-        <v>0.126680937344727</v>
+        <v>0.139612511157669</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2249,7 +2267,7 @@
         <v>23</v>
       </c>
       <c r="C21" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>740</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -2258,7 +2276,7 @@
       </c>
       <c r="E21" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C21/$C$22)</f>
-        <v>0.0105925303542484</v>
+        <v>0.0104356826521894</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2268,11 +2286,11 @@
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">SUM(C6:C21)</f>
-        <v>69860.5503361345</v>
+        <v>70910.5503361345</v>
       </c>
       <c r="D22" s="13" t="n">
         <f aca="false">C22*Narxlar!$C$19</f>
-        <v>831340549</v>
+        <v>843835549</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">SUM(E6:E21)</f>
@@ -2282,16 +2300,16 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="str">
-        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$76,"0%")&amp;")"</f>
+        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$79,"0%")&amp;")"</f>
         <v>Kutilmagan xarajatlar (10%)</v>
       </c>
       <c r="C23" s="17" t="n">
-        <f aca="false">C22*Narxlar!$C$76</f>
-        <v>6986.05503361345</v>
+        <f aca="false">C22*Narxlar!$C$79</f>
+        <v>7091.05503361345</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">C23*Narxlar!$C$19</f>
-        <v>83134054.9</v>
+        <v>84383554.9</v>
       </c>
       <c r="E23" s="16"/>
     </row>
@@ -2302,11 +2320,11 @@
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">C22+C23</f>
-        <v>76846.6053697479</v>
+        <v>78001.6053697479</v>
       </c>
       <c r="D24" s="22" t="n">
         <f aca="false">C24*Narxlar!$C$19</f>
-        <v>914474603.9</v>
+        <v>928219103.9</v>
       </c>
       <c r="E24" s="20"/>
     </row>
@@ -2316,12 +2334,12 @@
         <v>26</v>
       </c>
       <c r="C25" s="25" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")+SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")+SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,"1-qavat — kirish zali (resepshn, turniket)",'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
-        <v>10340</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")+SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")+SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,"1-qavat — kirish zali (resepshn, turniket)",'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <v>11390</v>
       </c>
       <c r="D25" s="26" t="n">
         <f aca="false">C25*Narxlar!$C$19</f>
-        <v>123046000</v>
+        <v>135541000</v>
       </c>
       <c r="E25" s="24"/>
     </row>
@@ -2364,7 +2382,7 @@
       </c>
       <c r="E29" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C29/$C$34)</f>
-        <v>0.049097809614962</v>
+        <v>0.0483707993202832</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2384,7 +2402,7 @@
       </c>
       <c r="E30" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C30/$C$34)</f>
-        <v>0.281052753027689</v>
+        <v>0.276891095992449</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2404,7 +2422,7 @@
       </c>
       <c r="E31" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C31/$C$34)</f>
-        <v>0.154328586707732</v>
+        <v>0.152043383514766</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2416,15 +2434,15 @@
       </c>
       <c r="C32" s="7" t="n">
         <f aca="false">'Xonalar bo''yicha'!$W$34</f>
-        <v>28694.8957983193</v>
+        <v>29744.8957983193</v>
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">C32*Narxlar!$C$19</f>
-        <v>341469260</v>
+        <v>353964260</v>
       </c>
       <c r="E32" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C32/$C$34)</f>
-        <v>0.410745344264448</v>
+        <v>0.419470666315813</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2444,7 +2462,7 @@
       </c>
       <c r="E33" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C33/$C$34)</f>
-        <v>0.10477550638517</v>
+        <v>0.103224054856689</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2454,11 +2472,11 @@
       </c>
       <c r="C34" s="12" t="n">
         <f aca="false">SUM(C29:C33)</f>
-        <v>69860.5503361345</v>
+        <v>70910.5503361345</v>
       </c>
       <c r="D34" s="13" t="n">
         <f aca="false">C34*Narxlar!$C$19</f>
-        <v>831340549</v>
+        <v>843835549</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">SUM(E29:E33)</f>
@@ -2620,87 +2638,87 @@
         <v>61</v>
       </c>
       <c r="B6" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D6" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F6" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H6" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J6" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>750</v>
       </c>
       <c r="O6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>2680</v>
       </c>
       <c r="V6" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A6,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W6" s="34" t="n">
@@ -2833,87 +2851,87 @@
         <v>63</v>
       </c>
       <c r="B10" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>13.75</v>
       </c>
       <c r="C10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>756.25</v>
       </c>
       <c r="D10" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>7.25</v>
       </c>
       <c r="E10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>87</v>
       </c>
       <c r="F10" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H10" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J10" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V10" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A10,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W10" s="34" t="n">
@@ -2926,87 +2944,87 @@
         <v>64</v>
       </c>
       <c r="B11" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>14</v>
       </c>
       <c r="C11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>770</v>
       </c>
       <c r="D11" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>6.3</v>
       </c>
       <c r="E11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>75.6</v>
       </c>
       <c r="F11" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H11" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J11" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V11" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A11,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W11" s="34" t="n">
@@ -3019,87 +3037,87 @@
         <v>65</v>
       </c>
       <c r="B12" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>2.25</v>
       </c>
       <c r="C12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>123.75</v>
       </c>
       <c r="D12" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>17.875</v>
       </c>
       <c r="E12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>214.5</v>
       </c>
       <c r="F12" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H12" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J12" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V12" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A12,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W12" s="34" t="n">
@@ -3112,87 +3130,87 @@
         <v>66</v>
       </c>
       <c r="B13" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>2.25</v>
       </c>
       <c r="C13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>123.75</v>
       </c>
       <c r="D13" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>52</v>
       </c>
       <c r="E13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>624</v>
       </c>
       <c r="F13" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>50.4</v>
       </c>
       <c r="G13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>781.2</v>
       </c>
       <c r="H13" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J13" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V13" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A13,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W13" s="34" t="n">
@@ -3205,87 +3223,87 @@
         <v>67</v>
       </c>
       <c r="B14" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>2.25</v>
       </c>
       <c r="C14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>123.75</v>
       </c>
       <c r="D14" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>27.5</v>
       </c>
       <c r="E14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>330</v>
       </c>
       <c r="F14" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H14" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J14" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V14" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A14,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W14" s="34" t="n">
@@ -3298,87 +3316,87 @@
         <v>68</v>
       </c>
       <c r="B15" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>14</v>
       </c>
       <c r="C15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>770</v>
       </c>
       <c r="D15" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>25.55</v>
       </c>
       <c r="E15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>306.6</v>
       </c>
       <c r="F15" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H15" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J15" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V15" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A15,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W15" s="34" t="n">
@@ -3391,87 +3409,87 @@
         <v>69</v>
       </c>
       <c r="B16" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>14</v>
       </c>
       <c r="C16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>770</v>
       </c>
       <c r="D16" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>30.45</v>
       </c>
       <c r="E16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>365.4</v>
       </c>
       <c r="F16" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H16" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J16" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V16" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A16,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W16" s="34" t="n">
@@ -3604,87 +3622,87 @@
         <v>71</v>
       </c>
       <c r="B20" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>7</v>
       </c>
       <c r="C20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>385</v>
       </c>
       <c r="D20" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>34.3</v>
       </c>
       <c r="E20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>411.6</v>
       </c>
       <c r="F20" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>39.2</v>
       </c>
       <c r="G20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>607.6</v>
       </c>
       <c r="H20" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J20" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>2340</v>
       </c>
       <c r="V20" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A20,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W20" s="34" t="n">
@@ -3697,87 +3715,87 @@
         <v>72</v>
       </c>
       <c r="B21" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>7</v>
       </c>
       <c r="C21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>385</v>
       </c>
       <c r="D21" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>35.35</v>
       </c>
       <c r="E21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>424.2</v>
       </c>
       <c r="F21" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>39.2</v>
       </c>
       <c r="G21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>607.6</v>
       </c>
       <c r="H21" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J21" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>1470</v>
       </c>
       <c r="V21" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A21,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W21" s="34" t="n">
@@ -3790,87 +3808,87 @@
         <v>73</v>
       </c>
       <c r="B22" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>7.125</v>
       </c>
       <c r="C22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>391.875</v>
       </c>
       <c r="D22" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>35.575</v>
       </c>
       <c r="E22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>426.9</v>
       </c>
       <c r="F22" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>39.2</v>
       </c>
       <c r="G22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>607.6</v>
       </c>
       <c r="H22" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J22" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V22" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A22,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W22" s="34" t="n">
@@ -3883,87 +3901,87 @@
         <v>74</v>
       </c>
       <c r="B23" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>7.125</v>
       </c>
       <c r="C23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>391.875</v>
       </c>
       <c r="D23" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>35.925</v>
       </c>
       <c r="E23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>431.1</v>
       </c>
       <c r="F23" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>39.2</v>
       </c>
       <c r="G23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>607.6</v>
       </c>
       <c r="H23" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J23" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V23" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A23,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W23" s="34" t="n">
@@ -3976,87 +3994,87 @@
         <v>75</v>
       </c>
       <c r="B24" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D24" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F24" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>29.26</v>
       </c>
       <c r="G24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>453.53</v>
       </c>
       <c r="H24" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J24" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V24" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A24,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W24" s="34" t="n">
@@ -4189,87 +4207,87 @@
         <v>77</v>
       </c>
       <c r="B28" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D28" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>52</v>
       </c>
       <c r="E28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>624</v>
       </c>
       <c r="F28" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H28" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J28" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>336</v>
       </c>
       <c r="M28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V28" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A28,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>370</v>
       </c>
       <c r="W28" s="34" t="n">
@@ -4282,87 +4300,87 @@
         <v>78</v>
       </c>
       <c r="B29" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D29" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>50.1</v>
       </c>
       <c r="E29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>601.2</v>
       </c>
       <c r="F29" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H29" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J29" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>336</v>
       </c>
       <c r="M29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V29" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A29,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>370</v>
       </c>
       <c r="W29" s="34" t="n">
@@ -4375,92 +4393,92 @@
         <v>79</v>
       </c>
       <c r="B30" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D30" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>9.625</v>
       </c>
       <c r="E30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>115.5</v>
       </c>
       <c r="F30" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H30" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J30" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>336</v>
       </c>
       <c r="M30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
-        <v>2360</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <v>3410</v>
       </c>
       <c r="V30" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A30,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W30" s="34" t="n">
         <f aca="false">C30+E30+G30+I30+K30+L30+M30+N30+O30+P30+Q30+R30+S30+T30+U30+V30</f>
-        <v>2811.5</v>
+        <v>3861.5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4468,87 +4486,87 @@
         <v>80</v>
       </c>
       <c r="B31" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D31" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>9.1</v>
       </c>
       <c r="E31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>109.2</v>
       </c>
       <c r="F31" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H31" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J31" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V31" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A31,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W31" s="34" t="n">
@@ -4561,87 +4579,87 @@
         <v>81</v>
       </c>
       <c r="B32" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D32" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F32" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H32" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J32" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>24</v>
       </c>
       <c r="K32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>2016</v>
       </c>
       <c r="L32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V32" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A32,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W32" s="34" t="n">
@@ -4654,87 +4672,87 @@
         <v>82</v>
       </c>
       <c r="B33" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D33" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F33" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H33" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J33" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>2119</v>
       </c>
       <c r="N33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>2500</v>
       </c>
       <c r="O33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>537.81512605042</v>
       </c>
       <c r="P33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>1512.60504201681</v>
       </c>
       <c r="Q33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>451.575630252101</v>
       </c>
       <c r="R33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>14000</v>
       </c>
       <c r="U33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V33" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A33,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W33" s="34" t="n">
@@ -4824,7 +4842,7 @@
       </c>
       <c r="U34" s="36" t="n">
         <f aca="false">SUM(U28:U33)</f>
-        <v>2360</v>
+        <v>3410</v>
       </c>
       <c r="V34" s="36" t="n">
         <f aca="false">SUM(V28:V33)</f>
@@ -4832,7 +4850,7 @@
       </c>
       <c r="W34" s="36" t="n">
         <f aca="false">SUM(W28:W33)</f>
-        <v>28694.8957983193</v>
+        <v>29744.8957983193</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4867,87 +4885,87 @@
         <v>84</v>
       </c>
       <c r="B37" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D37" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F37" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>46.86</v>
       </c>
       <c r="G37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>726.33</v>
       </c>
       <c r="H37" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J37" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>1000</v>
       </c>
       <c r="U37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V37" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A37,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W37" s="34" t="n">
@@ -4960,87 +4978,87 @@
         <v>85</v>
       </c>
       <c r="B38" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D38" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F38" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H38" s="33" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J38" s="31" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
         <v>3317.64705882353</v>
       </c>
       <c r="S38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
         <v>1243.6974789916</v>
       </c>
       <c r="T38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V38" s="32" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$307,'Hisob (batafsil)'!$B$5:$B$307,$A38,'Hisob (batafsil)'!$C$5:$C$307,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W38" s="34" t="n">
@@ -5223,7 +5241,7 @@
       </c>
       <c r="U41" s="39" t="n">
         <f aca="false">U7+U17+U25+U34+U39</f>
-        <v>8850</v>
+        <v>9900</v>
       </c>
       <c r="V41" s="39" t="n">
         <f aca="false">V7+V17+V25+V34+V39</f>
@@ -5231,12 +5249,12 @@
       </c>
       <c r="W41" s="39" t="n">
         <f aca="false">W7+W17+W25+W34+W39</f>
-        <v>69860.5503361345</v>
+        <v>70910.5503361345</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="str">
-        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$76,"0%")&amp;" — «Narxlar» varag'idan)"</f>
+        <f aca="false">"Kutilmagan xarajatlar ("&amp;TEXT(Narxlar!$C$79,"0%")&amp;" — «Narxlar» varag'idan)"</f>
         <v>Kutilmagan xarajatlar (10% — «Narxlar» varag'idan)</v>
       </c>
       <c r="B42" s="16"/>
@@ -5261,8 +5279,8 @@
       <c r="U42" s="16"/>
       <c r="V42" s="16"/>
       <c r="W42" s="41" t="n">
-        <f aca="false">W41*Narxlar!$C$76</f>
-        <v>6986.05503361345</v>
+        <f aca="false">W41*Narxlar!$C$79</f>
+        <v>7091.05503361345</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5292,7 +5310,7 @@
       <c r="V43" s="20"/>
       <c r="W43" s="39" t="n">
         <f aca="false">W41+W42</f>
-        <v>76846.6053697479</v>
+        <v>78001.6053697479</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5322,7 +5340,7 @@
       <c r="V44" s="20"/>
       <c r="W44" s="22" t="n">
         <f aca="false">W43*Narxlar!$C$19</f>
-        <v>914474603.9</v>
+        <v>928219103.9</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5330,7 +5348,7 @@
         <v>89</v>
       </c>
       <c r="W46" s="27" t="n">
-        <f aca="false">W41-'Hisob (batafsil)'!J308</f>
+        <f aca="false">W41-'Hisob (batafsil)'!J311</f>
         <v>0</v>
       </c>
     </row>
@@ -5355,7 +5373,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -6539,7 +6557,7 @@
         <v>197</v>
       </c>
       <c r="C72" s="46" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>117</v>
@@ -6573,10 +6591,10 @@
         <v>200</v>
       </c>
       <c r="C74" s="46" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>179</v>
@@ -6589,14 +6607,14 @@
       <c r="B75" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C75" s="44" t="n">
-        <v>2</v>
+      <c r="C75" s="46" t="n">
+        <v>250</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6604,16 +6622,16 @@
         <v>72</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="C76" s="47" t="n">
-        <v>0.1</v>
+        <v>202</v>
+      </c>
+      <c r="C76" s="46" t="n">
+        <v>300</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6621,16 +6639,16 @@
         <v>73</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C77" s="43" t="n">
-        <v>3.5</v>
+        <v>203</v>
+      </c>
+      <c r="C77" s="46" t="n">
+        <v>100</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6638,16 +6656,16 @@
         <v>74</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C78" s="43" t="n">
-        <v>2.5</v>
+        <v>204</v>
+      </c>
+      <c r="C78" s="44" t="n">
+        <v>2</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>97</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6655,17 +6673,16 @@
         <v>75</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C79" s="48" t="n">
-        <f aca="false">C77-C78</f>
-        <v>1</v>
+        <v>206</v>
+      </c>
+      <c r="C79" s="47" t="n">
+        <v>0.1</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6673,16 +6690,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C80" s="43" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6690,17 +6707,16 @@
         <v>77</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C81" s="48" t="n">
-        <f aca="false">C77-C80</f>
-        <v>1.4</v>
+        <v>211</v>
+      </c>
+      <c r="C81" s="43" t="n">
+        <v>2.5</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>214</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6708,16 +6724,17 @@
         <v>78</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C82" s="43" t="n">
-        <v>0.9</v>
+        <v>212</v>
+      </c>
+      <c r="C82" s="48" t="n">
+        <f aca="false">C80-C81</f>
+        <v>1</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6725,17 +6742,16 @@
         <v>79</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C83" s="49" t="n">
-        <f aca="false">C77</f>
-        <v>3.5</v>
+        <v>214</v>
+      </c>
+      <c r="C83" s="43" t="n">
+        <v>2.1</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6743,35 +6759,73 @@
         <v>80</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C84" s="43" t="n">
-        <v>2.5</v>
+        <v>216</v>
+      </c>
+      <c r="C84" s="48" t="n">
+        <f aca="false">C80-C83</f>
+        <v>1.4</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E84" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C85" s="43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C86" s="49" t="n">
+        <f aca="false">C80</f>
+        <v>3.5</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C87" s="43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E87" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="3" t="s">
         <v>223</v>
       </c>
     </row>
@@ -6858,6 +6912,21 @@
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="2" t="s">
         <v>240</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -6876,7 +6945,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J308"/>
+  <dimension ref="A1:J311"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -6892,12 +6961,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6908,25 +6977,25 @@
         <v>38</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>94</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>5</v>
@@ -6957,7 +7026,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="51"/>
@@ -6987,7 +7056,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E7" s="50"/>
       <c r="F7" s="51"/>
@@ -7017,7 +7086,7 @@
         <v>22</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E8" s="50"/>
       <c r="F8" s="51"/>
@@ -7047,7 +7116,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E9" s="50"/>
       <c r="F9" s="51"/>
@@ -7055,7 +7124,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I9" s="7" t="n">
         <f aca="false">Narxlar!$C$66</f>
@@ -7077,7 +7146,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E10" s="50"/>
       <c r="F10" s="51"/>
@@ -7107,7 +7176,7 @@
         <v>22</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E11" s="50"/>
       <c r="F11" s="51"/>
@@ -7161,7 +7230,7 @@
       <c r="B13" s="54"/>
       <c r="C13" s="54"/>
       <c r="D13" s="11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E13" s="54"/>
       <c r="F13" s="54"/>
@@ -7198,13 +7267,13 @@
         <v>8</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E16" s="50" t="n">
         <v>4.6</v>
       </c>
       <c r="F16" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G16" s="51" t="n">
@@ -7234,14 +7303,14 @@
         <v>8</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E17" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F17" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G17" s="51" t="n">
@@ -7271,13 +7340,13 @@
         <v>9</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E18" s="50" t="n">
         <v>0.3</v>
       </c>
       <c r="F18" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G18" s="51" t="n">
@@ -7307,13 +7376,13 @@
         <v>9</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E19" s="50" t="n">
         <v>4.6</v>
       </c>
       <c r="F19" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G19" s="51" t="n">
@@ -7343,13 +7412,13 @@
         <v>9</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E20" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F20" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G20" s="51" t="n">
@@ -7379,14 +7448,14 @@
         <v>9</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E21" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F21" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F21" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G21" s="51" t="n">
@@ -7416,13 +7485,13 @@
         <v>10</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E22" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F22" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G22" s="51" t="n">
@@ -7452,13 +7521,13 @@
         <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E23" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F23" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G23" s="51" t="n">
@@ -7488,7 +7557,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E24" s="50"/>
       <c r="F24" s="51"/>
@@ -7518,7 +7587,7 @@
         <v>13</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E25" s="50"/>
       <c r="F25" s="51"/>
@@ -7526,7 +7595,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I25" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -7542,7 +7611,7 @@
       <c r="B26" s="54"/>
       <c r="C26" s="54"/>
       <c r="D26" s="11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E26" s="54"/>
       <c r="F26" s="54"/>
@@ -7579,13 +7648,13 @@
         <v>8</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E29" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F29" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G29" s="51" t="n">
@@ -7615,14 +7684,14 @@
         <v>8</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E30" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F30" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G30" s="51" t="n">
@@ -7652,13 +7721,13 @@
         <v>9</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E31" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F31" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G31" s="51" t="n">
@@ -7688,13 +7757,13 @@
         <v>9</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E32" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F32" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G32" s="51" t="n">
@@ -7724,14 +7793,14 @@
         <v>9</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E33" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F33" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F33" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G33" s="51" t="n">
@@ -7761,13 +7830,13 @@
         <v>10</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E34" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F34" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G34" s="51" t="n">
@@ -7797,13 +7866,13 @@
         <v>10</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E35" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F35" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G35" s="51" t="n">
@@ -7833,7 +7902,7 @@
         <v>11</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E36" s="50"/>
       <c r="F36" s="51"/>
@@ -7863,7 +7932,7 @@
         <v>13</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E37" s="50"/>
       <c r="F37" s="51"/>
@@ -7871,7 +7940,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I37" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -7887,7 +7956,7 @@
       <c r="B38" s="54"/>
       <c r="C38" s="54"/>
       <c r="D38" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E38" s="54"/>
       <c r="F38" s="54"/>
@@ -7924,14 +7993,14 @@
         <v>8</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E41" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F41" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G41" s="51" t="n">
@@ -7961,13 +8030,13 @@
         <v>9</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E42" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F42" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G42" s="51" t="n">
@@ -7997,13 +8066,13 @@
         <v>9</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E43" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F43" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G43" s="51" t="n">
@@ -8033,14 +8102,14 @@
         <v>9</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E44" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F44" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F44" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G44" s="51" t="n">
@@ -8070,13 +8139,13 @@
         <v>10</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E45" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F45" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G45" s="51" t="n">
@@ -8106,13 +8175,13 @@
         <v>10</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E46" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F46" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G46" s="51" t="n">
@@ -8142,7 +8211,7 @@
         <v>11</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E47" s="50"/>
       <c r="F47" s="51"/>
@@ -8172,7 +8241,7 @@
         <v>13</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E48" s="50"/>
       <c r="F48" s="51"/>
@@ -8180,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I48" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -8196,7 +8265,7 @@
       <c r="B49" s="54"/>
       <c r="C49" s="54"/>
       <c r="D49" s="11" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E49" s="54"/>
       <c r="F49" s="54"/>
@@ -8233,14 +8302,14 @@
         <v>8</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E52" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F52" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G52" s="51" t="n">
@@ -8270,13 +8339,13 @@
         <v>9</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E53" s="50" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G53" s="51" t="n">
@@ -8306,13 +8375,13 @@
         <v>9</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E54" s="50" t="n">
         <v>4.5</v>
       </c>
       <c r="F54" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G54" s="51" t="n">
@@ -8342,13 +8411,13 @@
         <v>9</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E55" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F55" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G55" s="51" t="n">
@@ -8378,13 +8447,13 @@
         <v>9</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E56" s="50" t="n">
         <v>1.15</v>
       </c>
       <c r="F56" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G56" s="51" t="n">
@@ -8414,13 +8483,13 @@
         <v>9</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E57" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F57" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G57" s="51" t="n">
@@ -8450,13 +8519,13 @@
         <v>9</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E58" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F58" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G58" s="51" t="n">
@@ -8486,13 +8555,13 @@
         <v>9</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E59" s="50" t="n">
         <v>0.25</v>
       </c>
       <c r="F59" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G59" s="51" t="n">
@@ -8522,13 +8591,13 @@
         <v>9</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E60" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F60" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G60" s="51" t="n">
@@ -8558,13 +8627,13 @@
         <v>9</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E61" s="50" t="n">
         <v>4.5</v>
       </c>
       <c r="F61" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G61" s="51" t="n">
@@ -8594,14 +8663,14 @@
         <v>9</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E62" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F62" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F62" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G62" s="51" t="n">
@@ -8631,13 +8700,13 @@
         <v>10</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E63" s="50" t="n">
         <v>8.8</v>
       </c>
       <c r="F63" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G63" s="51" t="n">
@@ -8667,13 +8736,13 @@
         <v>10</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E64" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F64" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G64" s="51" t="n">
@@ -8703,7 +8772,7 @@
         <v>11</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E65" s="50"/>
       <c r="F65" s="51"/>
@@ -8733,7 +8802,7 @@
         <v>13</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E66" s="50"/>
       <c r="F66" s="51"/>
@@ -8741,7 +8810,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I66" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -8757,7 +8826,7 @@
       <c r="B67" s="54"/>
       <c r="C67" s="54"/>
       <c r="D67" s="11" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E67" s="54"/>
       <c r="F67" s="54"/>
@@ -8794,14 +8863,14 @@
         <v>8</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E70" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F70" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G70" s="51" t="n">
@@ -8831,13 +8900,13 @@
         <v>9</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E71" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F71" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G71" s="51" t="n">
@@ -8867,13 +8936,13 @@
         <v>9</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E72" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F72" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G72" s="51" t="n">
@@ -8903,13 +8972,13 @@
         <v>9</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E73" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F73" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G73" s="51" t="n">
@@ -8939,14 +9008,14 @@
         <v>9</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E74" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F74" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G74" s="51" t="n">
@@ -8976,13 +9045,13 @@
         <v>10</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E75" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F75" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G75" s="51" t="n">
@@ -9012,13 +9081,13 @@
         <v>10</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E76" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F76" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G76" s="51" t="n">
@@ -9048,7 +9117,7 @@
         <v>11</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E77" s="50"/>
       <c r="F77" s="51"/>
@@ -9078,7 +9147,7 @@
         <v>13</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E78" s="50"/>
       <c r="F78" s="51"/>
@@ -9086,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I78" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -9102,7 +9171,7 @@
       <c r="B79" s="54"/>
       <c r="C79" s="54"/>
       <c r="D79" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E79" s="54"/>
       <c r="F79" s="54"/>
@@ -9139,13 +9208,13 @@
         <v>8</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E82" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F82" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G82" s="51" t="n">
@@ -9175,14 +9244,14 @@
         <v>8</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E83" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F83" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G83" s="51" t="n">
@@ -9212,13 +9281,13 @@
         <v>9</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E84" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F84" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G84" s="51" t="n">
@@ -9248,13 +9317,13 @@
         <v>9</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E85" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F85" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G85" s="51" t="n">
@@ -9284,13 +9353,13 @@
         <v>9</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E86" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F86" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G86" s="51" t="n">
@@ -9320,13 +9389,13 @@
         <v>9</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E87" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F87" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G87" s="51" t="n">
@@ -9356,14 +9425,14 @@
         <v>9</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E88" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F88" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F88" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G88" s="51" t="n">
@@ -9393,13 +9462,13 @@
         <v>10</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E89" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F89" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G89" s="51" t="n">
@@ -9429,13 +9498,13 @@
         <v>10</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E90" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F90" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G90" s="51" t="n">
@@ -9465,7 +9534,7 @@
         <v>11</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E91" s="50"/>
       <c r="F91" s="51"/>
@@ -9495,7 +9564,7 @@
         <v>13</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E92" s="50"/>
       <c r="F92" s="51"/>
@@ -9503,7 +9572,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I92" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -9519,7 +9588,7 @@
       <c r="B93" s="54"/>
       <c r="C93" s="54"/>
       <c r="D93" s="11" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E93" s="54"/>
       <c r="F93" s="54"/>
@@ -9556,13 +9625,13 @@
         <v>8</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E96" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F96" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G96" s="51" t="n">
@@ -9592,14 +9661,14 @@
         <v>8</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E97" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F97" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G97" s="51" t="n">
@@ -9629,13 +9698,13 @@
         <v>9</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E98" s="50" t="n">
         <v>1.55</v>
       </c>
       <c r="F98" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G98" s="51" t="n">
@@ -9665,13 +9734,13 @@
         <v>9</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E99" s="50" t="n">
         <v>2.6</v>
       </c>
       <c r="F99" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G99" s="51" t="n">
@@ -9701,13 +9770,13 @@
         <v>9</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E100" s="50" t="n">
         <v>2.75</v>
       </c>
       <c r="F100" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G100" s="51" t="n">
@@ -9737,13 +9806,13 @@
         <v>9</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E101" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F101" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G101" s="51" t="n">
@@ -9773,13 +9842,13 @@
         <v>9</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E102" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F102" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G102" s="51" t="n">
@@ -9809,14 +9878,14 @@
         <v>9</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E103" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F103" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F103" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G103" s="51" t="n">
@@ -9846,13 +9915,13 @@
         <v>10</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E104" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F104" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G104" s="51" t="n">
@@ -9882,13 +9951,13 @@
         <v>10</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E105" s="50" t="n">
         <v>7.7</v>
       </c>
       <c r="F105" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G105" s="51" t="n">
@@ -9918,7 +9987,7 @@
         <v>11</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E106" s="50"/>
       <c r="F106" s="51"/>
@@ -9948,7 +10017,7 @@
         <v>13</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E107" s="50"/>
       <c r="F107" s="51"/>
@@ -9956,7 +10025,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I107" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -9972,7 +10041,7 @@
       <c r="B108" s="54"/>
       <c r="C108" s="54"/>
       <c r="D108" s="11" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E108" s="54"/>
       <c r="F108" s="54"/>
@@ -10009,13 +10078,13 @@
         <v>8</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E111" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F111" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G111" s="51" t="n">
@@ -10045,13 +10114,13 @@
         <v>8</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E112" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F112" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G112" s="51" t="n">
@@ -10081,14 +10150,14 @@
         <v>8</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E113" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F113" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G113" s="51" t="n">
@@ -10118,13 +10187,13 @@
         <v>9</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E114" s="50" t="n">
         <v>0.6</v>
       </c>
       <c r="F114" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G114" s="51" t="n">
@@ -10154,13 +10223,13 @@
         <v>9</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E115" s="50" t="n">
         <v>2.8</v>
       </c>
       <c r="F115" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G115" s="51" t="n">
@@ -10190,13 +10259,13 @@
         <v>9</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E116" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F116" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G116" s="51" t="n">
@@ -10226,13 +10295,13 @@
         <v>9</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E117" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F117" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G117" s="51" t="n">
@@ -10262,13 +10331,13 @@
         <v>9</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E118" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F118" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G118" s="51" t="n">
@@ -10298,14 +10367,14 @@
         <v>9</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E119" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F119" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F119" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G119" s="51" t="n">
@@ -10335,13 +10404,13 @@
         <v>10</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E120" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F120" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G120" s="51" t="n">
@@ -10371,13 +10440,13 @@
         <v>10</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E121" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F121" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G121" s="51" t="n">
@@ -10407,7 +10476,7 @@
         <v>13</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E122" s="50"/>
       <c r="F122" s="51"/>
@@ -10415,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I122" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -10437,7 +10506,7 @@
         <v>22</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E123" s="50"/>
       <c r="F123" s="51"/>
@@ -10467,7 +10536,7 @@
         <v>22</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E124" s="50"/>
       <c r="F124" s="51"/>
@@ -10497,7 +10566,7 @@
         <v>22</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E125" s="50"/>
       <c r="F125" s="51"/>
@@ -10527,7 +10596,7 @@
         <v>22</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E126" s="50"/>
       <c r="F126" s="51"/>
@@ -10557,7 +10626,7 @@
         <v>22</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E127" s="50"/>
       <c r="F127" s="51"/>
@@ -10587,7 +10656,7 @@
         <v>22</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E128" s="50"/>
       <c r="F128" s="51"/>
@@ -10595,7 +10664,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I128" s="7" t="n">
         <f aca="false">Narxlar!$C$61</f>
@@ -10611,7 +10680,7 @@
       <c r="B129" s="54"/>
       <c r="C129" s="54"/>
       <c r="D129" s="11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E129" s="54"/>
       <c r="F129" s="54"/>
@@ -10648,13 +10717,13 @@
         <v>8</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E132" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F132" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G132" s="51" t="n">
@@ -10684,13 +10753,13 @@
         <v>8</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E133" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F133" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G133" s="51" t="n">
@@ -10720,14 +10789,14 @@
         <v>8</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E134" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F134" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G134" s="51" t="n">
@@ -10757,13 +10826,13 @@
         <v>9</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E135" s="50" t="n">
         <v>0.9</v>
       </c>
       <c r="F135" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G135" s="51" t="n">
@@ -10793,13 +10862,13 @@
         <v>9</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E136" s="50" t="n">
         <v>2.8</v>
       </c>
       <c r="F136" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G136" s="51" t="n">
@@ -10829,13 +10898,13 @@
         <v>9</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E137" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F137" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G137" s="51" t="n">
@@ -10865,13 +10934,13 @@
         <v>9</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E138" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F138" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G138" s="51" t="n">
@@ -10901,13 +10970,13 @@
         <v>9</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E139" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F139" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G139" s="51" t="n">
@@ -10937,14 +11006,14 @@
         <v>9</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E140" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F140" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F140" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G140" s="51" t="n">
@@ -10974,13 +11043,13 @@
         <v>10</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E141" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F141" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G141" s="51" t="n">
@@ -11010,13 +11079,13 @@
         <v>10</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E142" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F142" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G142" s="51" t="n">
@@ -11046,7 +11115,7 @@
         <v>13</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E143" s="50"/>
       <c r="F143" s="51"/>
@@ -11054,7 +11123,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I143" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -11076,7 +11145,7 @@
         <v>22</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E144" s="50"/>
       <c r="F144" s="51"/>
@@ -11106,7 +11175,7 @@
         <v>22</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E145" s="50"/>
       <c r="F145" s="51"/>
@@ -11136,7 +11205,7 @@
         <v>22</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E146" s="50"/>
       <c r="F146" s="51"/>
@@ -11166,7 +11235,7 @@
         <v>22</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E147" s="50"/>
       <c r="F147" s="51"/>
@@ -11196,7 +11265,7 @@
         <v>22</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E148" s="50"/>
       <c r="F148" s="51"/>
@@ -11204,7 +11273,7 @@
         <v>1</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I148" s="7" t="n">
         <f aca="false">Narxlar!$C$62</f>
@@ -11220,7 +11289,7 @@
       <c r="B149" s="54"/>
       <c r="C149" s="54"/>
       <c r="D149" s="11" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E149" s="54"/>
       <c r="F149" s="54"/>
@@ -11257,13 +11326,13 @@
         <v>8</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E152" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F152" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G152" s="51" t="n">
@@ -11293,13 +11362,13 @@
         <v>8</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E153" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F153" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G153" s="51" t="n">
@@ -11329,14 +11398,14 @@
         <v>8</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E154" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F154" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G154" s="51" t="n">
@@ -11366,13 +11435,13 @@
         <v>9</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E155" s="50" t="n">
         <v>0.9</v>
       </c>
       <c r="F155" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G155" s="51" t="n">
@@ -11402,13 +11471,13 @@
         <v>9</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E156" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F156" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G156" s="51" t="n">
@@ -11438,13 +11507,13 @@
         <v>9</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E157" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F157" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G157" s="51" t="n">
@@ -11474,13 +11543,13 @@
         <v>9</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E158" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F158" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G158" s="51" t="n">
@@ -11510,13 +11579,13 @@
         <v>9</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E159" s="50" t="n">
         <v>2.85</v>
       </c>
       <c r="F159" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G159" s="51" t="n">
@@ -11546,14 +11615,14 @@
         <v>9</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E160" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F160" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F160" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G160" s="51" t="n">
@@ -11583,13 +11652,13 @@
         <v>10</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E161" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F161" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G161" s="51" t="n">
@@ -11619,13 +11688,13 @@
         <v>10</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E162" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F162" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G162" s="51" t="n">
@@ -11655,7 +11724,7 @@
         <v>13</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E163" s="50"/>
       <c r="F163" s="51"/>
@@ -11663,7 +11732,7 @@
         <v>1</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I163" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -11679,7 +11748,7 @@
       <c r="B164" s="54"/>
       <c r="C164" s="54"/>
       <c r="D164" s="11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E164" s="54"/>
       <c r="F164" s="54"/>
@@ -11716,13 +11785,13 @@
         <v>8</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E167" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F167" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G167" s="51" t="n">
@@ -11752,13 +11821,13 @@
         <v>8</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E168" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F168" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G168" s="51" t="n">
@@ -11788,14 +11857,14 @@
         <v>8</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E169" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F169" s="31" t="n">
-        <f aca="false">Narxlar!$C$78</f>
+        <f aca="false">Narxlar!$C$81</f>
         <v>2.5</v>
       </c>
       <c r="G169" s="51" t="n">
@@ -11825,13 +11894,13 @@
         <v>9</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E170" s="50" t="n">
         <v>1</v>
       </c>
       <c r="F170" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G170" s="51" t="n">
@@ -11861,13 +11930,13 @@
         <v>9</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E171" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F171" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G171" s="51" t="n">
@@ -11897,13 +11966,13 @@
         <v>9</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E172" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F172" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G172" s="51" t="n">
@@ -11933,13 +12002,13 @@
         <v>9</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E173" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F173" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G173" s="51" t="n">
@@ -11969,13 +12038,13 @@
         <v>9</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E174" s="50" t="n">
         <v>2.85</v>
       </c>
       <c r="F174" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G174" s="51" t="n">
@@ -12005,14 +12074,14 @@
         <v>9</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E175" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F175" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F175" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G175" s="51" t="n">
@@ -12042,13 +12111,13 @@
         <v>10</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E176" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F176" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G176" s="51" t="n">
@@ -12078,13 +12147,13 @@
         <v>10</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E177" s="50" t="n">
         <v>5.6</v>
       </c>
       <c r="F177" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G177" s="51" t="n">
@@ -12114,7 +12183,7 @@
         <v>13</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E178" s="50"/>
       <c r="F178" s="51"/>
@@ -12122,7 +12191,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I178" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -12138,7 +12207,7 @@
       <c r="B179" s="54"/>
       <c r="C179" s="54"/>
       <c r="D179" s="11" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E179" s="54"/>
       <c r="F179" s="54"/>
@@ -12175,13 +12244,13 @@
         <v>10</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E182" s="50" t="n">
         <v>5.95</v>
       </c>
       <c r="F182" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G182" s="51" t="n">
@@ -12211,14 +12280,14 @@
         <v>10</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E183" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
+        <f aca="false">Narxlar!$C$85</f>
         <v>0.9</v>
       </c>
       <c r="F183" s="31" t="n">
-        <f aca="false">Narxlar!$C$80</f>
+        <f aca="false">Narxlar!$C$83</f>
         <v>2.1</v>
       </c>
       <c r="G183" s="51" t="n">
@@ -12248,13 +12317,13 @@
         <v>10</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E184" s="50" t="n">
         <v>2.95</v>
       </c>
       <c r="F184" s="31" t="n">
-        <f aca="false">Narxlar!$C$83</f>
+        <f aca="false">Narxlar!$C$86</f>
         <v>3.5</v>
       </c>
       <c r="G184" s="51" t="n">
@@ -12284,7 +12353,7 @@
         <v>13</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E185" s="50"/>
       <c r="F185" s="51"/>
@@ -12292,7 +12361,7 @@
         <v>1</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I185" s="7" t="n">
         <f aca="false">Narxlar!$C$12</f>
@@ -12308,7 +12377,7 @@
       <c r="B186" s="54"/>
       <c r="C186" s="54"/>
       <c r="D186" s="11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E186" s="54"/>
       <c r="F186" s="54"/>
@@ -12345,13 +12414,13 @@
         <v>9</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E189" s="50" t="n">
         <v>4.6</v>
       </c>
       <c r="F189" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G189" s="51" t="n">
@@ -12381,13 +12450,13 @@
         <v>9</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E190" s="50" t="n">
         <v>0.4</v>
       </c>
       <c r="F190" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G190" s="51" t="n">
@@ -12417,13 +12486,13 @@
         <v>9</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E191" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F191" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G191" s="51" t="n">
@@ -12453,13 +12522,13 @@
         <v>9</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E192" s="50" t="n">
         <v>0.55</v>
       </c>
       <c r="F192" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G192" s="51" t="n">
@@ -12489,13 +12558,13 @@
         <v>9</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E193" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F193" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G193" s="51" t="n">
@@ -12525,13 +12594,13 @@
         <v>9</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E194" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F194" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G194" s="51" t="n">
@@ -12561,13 +12630,13 @@
         <v>9</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E195" s="50" t="n">
         <v>5.9</v>
       </c>
       <c r="F195" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G195" s="51" t="n">
@@ -12597,13 +12666,13 @@
         <v>9</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E196" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F196" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G196" s="51" t="n">
@@ -12633,13 +12702,13 @@
         <v>9</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E197" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F197" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G197" s="51" t="n">
@@ -12669,13 +12738,13 @@
         <v>9</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E198" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F198" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G198" s="51" t="n">
@@ -12705,13 +12774,13 @@
         <v>9</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E199" s="50" t="n">
         <v>1.8</v>
       </c>
       <c r="F199" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G199" s="51" t="n">
@@ -12741,13 +12810,13 @@
         <v>9</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E200" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F200" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G200" s="51" t="n">
@@ -12777,13 +12846,13 @@
         <v>9</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E201" s="50" t="n">
         <v>1.15</v>
       </c>
       <c r="F201" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G201" s="51" t="n">
@@ -12813,14 +12882,14 @@
         <v>9</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E202" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F202" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F202" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G202" s="51" t="n">
@@ -12850,14 +12919,14 @@
         <v>9</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E203" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F203" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F203" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G203" s="51" t="n">
@@ -12887,14 +12956,14 @@
         <v>9</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E204" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F204" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F204" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G204" s="51" t="n">
@@ -12924,14 +12993,14 @@
         <v>9</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E205" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F205" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F205" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G205" s="51" t="n">
@@ -12961,14 +13030,14 @@
         <v>9</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E206" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F206" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F206" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G206" s="51" t="n">
@@ -12998,7 +13067,7 @@
         <v>13</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E207" s="50"/>
       <c r="F207" s="51"/>
@@ -13006,7 +13075,7 @@
         <v>1</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I207" s="7" t="n">
         <f aca="false">Narxlar!$C$11</f>
@@ -13028,7 +13097,7 @@
         <v>23</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E208" s="50"/>
       <c r="F208" s="51"/>
@@ -13058,7 +13127,7 @@
         <v>23</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E209" s="50"/>
       <c r="F209" s="51"/>
@@ -13082,7 +13151,7 @@
       <c r="B210" s="54"/>
       <c r="C210" s="54"/>
       <c r="D210" s="11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E210" s="54"/>
       <c r="F210" s="54"/>
@@ -13119,13 +13188,13 @@
         <v>9</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E213" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F213" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G213" s="51" t="n">
@@ -13155,13 +13224,13 @@
         <v>9</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E214" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F214" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G214" s="51" t="n">
@@ -13191,13 +13260,13 @@
         <v>9</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E215" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F215" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G215" s="51" t="n">
@@ -13227,13 +13296,13 @@
         <v>9</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E216" s="50" t="n">
         <v>1.75</v>
       </c>
       <c r="F216" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G216" s="51" t="n">
@@ -13263,13 +13332,13 @@
         <v>9</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E217" s="50" t="n">
         <v>6.3</v>
       </c>
       <c r="F217" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G217" s="51" t="n">
@@ -13299,13 +13368,13 @@
         <v>9</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E218" s="50" t="n">
         <v>0.15</v>
       </c>
       <c r="F218" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G218" s="51" t="n">
@@ -13335,13 +13404,13 @@
         <v>9</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E219" s="50" t="n">
         <v>1.5</v>
       </c>
       <c r="F219" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G219" s="51" t="n">
@@ -13371,13 +13440,13 @@
         <v>9</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E220" s="50" t="n">
         <v>0.2</v>
       </c>
       <c r="F220" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G220" s="51" t="n">
@@ -13407,13 +13476,13 @@
         <v>9</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E221" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F221" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G221" s="51" t="n">
@@ -13443,13 +13512,13 @@
         <v>9</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E222" s="50" t="n">
         <v>0.4</v>
       </c>
       <c r="F222" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G222" s="51" t="n">
@@ -13479,13 +13548,13 @@
         <v>9</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E223" s="50" t="n">
         <v>4.7</v>
       </c>
       <c r="F223" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
+        <f aca="false">Narxlar!$C$82</f>
         <v>1</v>
       </c>
       <c r="G223" s="51" t="n">
@@ -13515,13 +13584,13 @@
         <v>9</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E224" s="50" t="n">
         <v>0.35</v>
       </c>
       <c r="F224" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G224" s="51" t="n">
@@ -13551,13 +13620,13 @@
         <v>9</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E225" s="50" t="n">
         <v>0.1</v>
       </c>
       <c r="F225" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G225" s="51" t="n">
@@ -13587,14 +13656,14 @@
         <v>9</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E226" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F226" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F226" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G226" s="51" t="n">
@@ -13624,14 +13693,14 @@
         <v>9</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E227" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F227" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F227" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G227" s="51" t="n">
@@ -13661,14 +13730,14 @@
         <v>9</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E228" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F228" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F228" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G228" s="51" t="n">
@@ -13698,14 +13767,14 @@
         <v>9</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E229" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F229" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F229" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G229" s="51" t="n">
@@ -13735,14 +13804,14 @@
         <v>9</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E230" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F230" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F230" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G230" s="51" t="n">
@@ -13772,14 +13841,14 @@
         <v>9</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E231" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F231" s="31" t="n">
         <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
-      </c>
-      <c r="F231" s="31" t="n">
-        <f aca="false">Narxlar!$C$79</f>
         <v>1</v>
       </c>
       <c r="G231" s="51" t="n">
@@ -13809,7 +13878,7 @@
         <v>13</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E232" s="50"/>
       <c r="F232" s="51"/>
@@ -13817,7 +13886,7 @@
         <v>1</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I232" s="7" t="n">
         <f aca="false">Narxlar!$C$11</f>
@@ -13839,7 +13908,7 @@
         <v>23</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E233" s="50"/>
       <c r="F233" s="51"/>
@@ -13869,7 +13938,7 @@
         <v>23</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E234" s="50"/>
       <c r="F234" s="51"/>
@@ -13893,7 +13962,7 @@
       <c r="B235" s="54"/>
       <c r="C235" s="54"/>
       <c r="D235" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E235" s="54"/>
       <c r="F235" s="54"/>
@@ -13930,13 +13999,13 @@
         <v>9</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E238" s="50" t="n">
         <v>0.4</v>
       </c>
       <c r="F238" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G238" s="51" t="n">
@@ -13966,13 +14035,13 @@
         <v>9</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E239" s="50" t="n">
         <v>0.7</v>
       </c>
       <c r="F239" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G239" s="51" t="n">
@@ -14002,13 +14071,13 @@
         <v>9</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E240" s="50" t="n">
         <v>1.65</v>
       </c>
       <c r="F240" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G240" s="51" t="n">
@@ -14038,7 +14107,7 @@
         <v>13</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E241" s="50"/>
       <c r="F241" s="51"/>
@@ -14046,7 +14115,7 @@
         <v>1</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I241" s="7" t="n">
         <f aca="false">Narxlar!$C$11</f>
@@ -14068,7 +14137,7 @@
         <v>22</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E242" s="50"/>
       <c r="F242" s="51"/>
@@ -14076,7 +14145,7 @@
         <v>1</v>
       </c>
       <c r="H242" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I242" s="7" t="n">
         <f aca="false">Narxlar!$C$69</f>
@@ -14098,7 +14167,7 @@
         <v>22</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E243" s="50"/>
       <c r="F243" s="51"/>
@@ -14106,7 +14175,7 @@
         <v>1</v>
       </c>
       <c r="H243" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I243" s="7" t="n">
         <f aca="false">Narxlar!$C$70</f>
@@ -14128,7 +14197,7 @@
         <v>22</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E244" s="50"/>
       <c r="F244" s="51"/>
@@ -14158,7 +14227,7 @@
         <v>22</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E245" s="50"/>
       <c r="F245" s="51"/>
@@ -14166,15 +14235,15 @@
         <v>1</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I245" s="7" t="n">
         <f aca="false">Narxlar!$C$72</f>
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="J245" s="53" t="n">
         <f aca="false">G245*I245</f>
-        <v>250</v>
+        <v>450</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14188,7 +14257,7 @@
         <v>22</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E246" s="50"/>
       <c r="F246" s="51"/>
@@ -14196,7 +14265,7 @@
         <v>1</v>
       </c>
       <c r="H246" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I246" s="7" t="n">
         <f aca="false">Narxlar!$C$73</f>
@@ -14218,7 +14287,7 @@
         <v>22</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E247" s="50"/>
       <c r="F247" s="51"/>
@@ -14226,271 +14295,269 @@
         <v>1</v>
       </c>
       <c r="H247" s="5" t="s">
-        <v>113</v>
+        <v>256</v>
       </c>
       <c r="I247" s="7" t="n">
         <f aca="false">Narxlar!$C$74</f>
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="J247" s="53" t="n">
         <f aca="false">G247*I247</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D248" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E248" s="50"/>
+      <c r="F248" s="51"/>
+      <c r="G248" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H248" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="I248" s="7" t="n">
+        <f aca="false">Narxlar!$C$75</f>
+        <v>250</v>
+      </c>
+      <c r="J248" s="53" t="n">
+        <f aca="false">G248*I248</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D249" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E249" s="50"/>
+      <c r="F249" s="51"/>
+      <c r="G249" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I249" s="7" t="n">
+        <f aca="false">Narxlar!$C$76</f>
         <v>300</v>
       </c>
-    </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="54"/>
-      <c r="B248" s="54"/>
-      <c r="C248" s="54"/>
-      <c r="D248" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="E248" s="54"/>
-      <c r="F248" s="54"/>
-      <c r="G248" s="54"/>
-      <c r="H248" s="54"/>
-      <c r="I248" s="54"/>
-      <c r="J248" s="12" t="n">
-        <f aca="false">SUM(J238:J247)</f>
-        <v>2811.5</v>
+      <c r="J249" s="53" t="n">
+        <f aca="false">G249*I249</f>
+        <v>300</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="29" t="s">
+      <c r="A250" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D250" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E250" s="50"/>
+      <c r="F250" s="51"/>
+      <c r="G250" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H250" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I250" s="7" t="n">
+        <f aca="false">Narxlar!$C$77</f>
+        <v>100</v>
+      </c>
+      <c r="J250" s="53" t="n">
+        <f aca="false">G250*I250</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="54"/>
+      <c r="B251" s="54"/>
+      <c r="C251" s="54"/>
+      <c r="D251" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="E251" s="54"/>
+      <c r="F251" s="54"/>
+      <c r="G251" s="54"/>
+      <c r="H251" s="54"/>
+      <c r="I251" s="54"/>
+      <c r="J251" s="12" t="n">
+        <f aca="false">SUM(J238:J250)</f>
+        <v>3861.5</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="B250" s="30"/>
-      <c r="C250" s="30"/>
-      <c r="D250" s="30"/>
-      <c r="E250" s="30"/>
-      <c r="F250" s="30"/>
-      <c r="G250" s="30"/>
-      <c r="H250" s="30"/>
-      <c r="I250" s="30"/>
-      <c r="J250" s="30"/>
-    </row>
-    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="5" t="n">
-        <v>198</v>
-      </c>
-      <c r="B251" s="6" t="s">
+      <c r="B253" s="30"/>
+      <c r="C253" s="30"/>
+      <c r="D253" s="30"/>
+      <c r="E253" s="30"/>
+      <c r="F253" s="30"/>
+      <c r="G253" s="30"/>
+      <c r="H253" s="30"/>
+      <c r="I253" s="30"/>
+      <c r="J253" s="30"/>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="5" t="n">
+        <v>201</v>
+      </c>
+      <c r="B254" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C251" s="6" t="s">
+      <c r="C254" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D251" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="E251" s="50" t="n">
+      <c r="D254" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E254" s="50" t="n">
         <v>2.6</v>
       </c>
-      <c r="F251" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+      <c r="F254" s="31" t="n">
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
-      <c r="G251" s="51" t="n">
-        <f aca="false">E251*F251</f>
+      <c r="G254" s="51" t="n">
+        <f aca="false">E254*F254</f>
         <v>9.1</v>
       </c>
-      <c r="H251" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I251" s="7" t="n">
+      <c r="H254" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I254" s="7" t="n">
         <f aca="false">Narxlar!$C$6</f>
         <v>12</v>
       </c>
-      <c r="J251" s="53" t="n">
-        <f aca="false">G251*I251</f>
+      <c r="J254" s="53" t="n">
+        <f aca="false">G254*I254</f>
         <v>109.2</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="54"/>
-      <c r="B252" s="54"/>
-      <c r="C252" s="54"/>
-      <c r="D252" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="E252" s="54"/>
-      <c r="F252" s="54"/>
-      <c r="G252" s="54"/>
-      <c r="H252" s="54"/>
-      <c r="I252" s="54"/>
-      <c r="J252" s="12" t="n">
-        <f aca="false">SUM(J251:J251)</f>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="54"/>
+      <c r="B255" s="54"/>
+      <c r="C255" s="54"/>
+      <c r="D255" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="E255" s="54"/>
+      <c r="F255" s="54"/>
+      <c r="G255" s="54"/>
+      <c r="H255" s="54"/>
+      <c r="I255" s="54"/>
+      <c r="J255" s="12" t="n">
+        <f aca="false">SUM(J254:J254)</f>
         <v>109.2</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="29" t="s">
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B254" s="30"/>
-      <c r="C254" s="30"/>
-      <c r="D254" s="30"/>
-      <c r="E254" s="30"/>
-      <c r="F254" s="30"/>
-      <c r="G254" s="30"/>
-      <c r="H254" s="30"/>
-      <c r="I254" s="30"/>
-      <c r="J254" s="30"/>
-    </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="5" t="n">
-        <v>199</v>
-      </c>
-      <c r="B255" s="6" t="s">
+      <c r="B257" s="30"/>
+      <c r="C257" s="30"/>
+      <c r="D257" s="30"/>
+      <c r="E257" s="30"/>
+      <c r="F257" s="30"/>
+      <c r="G257" s="30"/>
+      <c r="H257" s="30"/>
+      <c r="I257" s="30"/>
+      <c r="J257" s="30"/>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="5" t="n">
+        <v>202</v>
+      </c>
+      <c r="B258" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C255" s="6" t="s">
+      <c r="C258" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D255" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E255" s="31" t="n">
+      <c r="D258" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E258" s="31" t="n">
         <f aca="false">Narxlar!$C$10</f>
         <v>24</v>
       </c>
-      <c r="F255" s="51"/>
-      <c r="G255" s="51" t="n">
-        <f aca="false">E255</f>
+      <c r="F258" s="51"/>
+      <c r="G258" s="51" t="n">
+        <f aca="false">E258</f>
         <v>24</v>
       </c>
-      <c r="H255" s="5" t="s">
+      <c r="H258" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I255" s="7" t="n">
+      <c r="I258" s="7" t="n">
         <f aca="false">Narxlar!$C$9</f>
         <v>84</v>
       </c>
-      <c r="J255" s="53" t="n">
-        <f aca="false">G255*I255</f>
+      <c r="J258" s="53" t="n">
+        <f aca="false">G258*I258</f>
         <v>2016</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="54"/>
-      <c r="B256" s="54"/>
-      <c r="C256" s="54"/>
-      <c r="D256" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="E256" s="54"/>
-      <c r="F256" s="54"/>
-      <c r="G256" s="54"/>
-      <c r="H256" s="54"/>
-      <c r="I256" s="54"/>
-      <c r="J256" s="12" t="n">
-        <f aca="false">SUM(J255:J255)</f>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="54"/>
+      <c r="B259" s="54"/>
+      <c r="C259" s="54"/>
+      <c r="D259" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="E259" s="54"/>
+      <c r="F259" s="54"/>
+      <c r="G259" s="54"/>
+      <c r="H259" s="54"/>
+      <c r="I259" s="54"/>
+      <c r="J259" s="12" t="n">
+        <f aca="false">SUM(J258:J258)</f>
         <v>2016</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="29" t="s">
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="B258" s="30"/>
-      <c r="C258" s="30"/>
-      <c r="D258" s="30"/>
-      <c r="E258" s="30"/>
-      <c r="F258" s="30"/>
-      <c r="G258" s="30"/>
-      <c r="H258" s="30"/>
-      <c r="I258" s="30"/>
-      <c r="J258" s="30"/>
-    </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="B259" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C259" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D259" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E259" s="50"/>
-      <c r="F259" s="51"/>
-      <c r="G259" s="33" t="n">
-        <f aca="false">Narxlar!$C$14</f>
-        <v>16</v>
-      </c>
-      <c r="H259" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I259" s="7" t="n">
-        <f aca="false">Narxlar!$C$13</f>
-        <v>40</v>
-      </c>
-      <c r="J259" s="53" t="n">
-        <f aca="false">G259*I259</f>
-        <v>640</v>
-      </c>
-    </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="5" t="n">
-        <v>201</v>
-      </c>
-      <c r="B260" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C260" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D260" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="E260" s="50"/>
-      <c r="F260" s="51"/>
-      <c r="G260" s="33" t="n">
-        <f aca="false">Narxlar!$C$14</f>
-        <v>16</v>
-      </c>
-      <c r="H260" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I260" s="7" t="n">
-        <f aca="false">Narxlar!$C$15</f>
-        <v>21</v>
-      </c>
-      <c r="J260" s="53" t="n">
-        <f aca="false">G260*I260</f>
-        <v>336</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="5" t="n">
-        <v>202</v>
-      </c>
-      <c r="B261" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C261" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D261" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E261" s="50"/>
-      <c r="F261" s="51"/>
-      <c r="G261" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H261" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I261" s="7" t="n">
-        <f aca="false">Narxlar!$C$16</f>
-        <v>840</v>
-      </c>
-      <c r="J261" s="53" t="n">
-        <f aca="false">G261*I261</f>
-        <v>840</v>
-      </c>
+      <c r="B261" s="30"/>
+      <c r="C261" s="30"/>
+      <c r="D261" s="30"/>
+      <c r="E261" s="30"/>
+      <c r="F261" s="30"/>
+      <c r="G261" s="30"/>
+      <c r="H261" s="30"/>
+      <c r="I261" s="30"/>
+      <c r="J261" s="30"/>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="5" t="n">
@@ -14503,23 +14570,24 @@
         <v>14</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>370</v>
+        <v>111</v>
       </c>
       <c r="E262" s="50"/>
       <c r="F262" s="51"/>
-      <c r="G262" s="52" t="n">
-        <v>1</v>
+      <c r="G262" s="33" t="n">
+        <f aca="false">Narxlar!$C$14</f>
+        <v>16</v>
       </c>
       <c r="H262" s="5" t="s">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="I262" s="7" t="n">
-        <f aca="false">Narxlar!$C$17</f>
-        <v>303</v>
+        <f aca="false">Narxlar!$C$13</f>
+        <v>40</v>
       </c>
       <c r="J262" s="53" t="n">
         <f aca="false">G262*I262</f>
-        <v>303</v>
+        <v>640</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14530,26 +14598,27 @@
         <v>82</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E263" s="50"/>
       <c r="F263" s="51"/>
-      <c r="G263" s="52" t="n">
-        <v>1</v>
+      <c r="G263" s="33" t="n">
+        <f aca="false">Narxlar!$C$14</f>
+        <v>16</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="I263" s="7" t="n">
-        <f aca="false">Narxlar!$C$18</f>
-        <v>2500</v>
+        <f aca="false">Narxlar!$C$15</f>
+        <v>21</v>
       </c>
       <c r="J263" s="53" t="n">
         <f aca="false">G263*I263</f>
-        <v>2500</v>
+        <v>336</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14560,27 +14629,26 @@
         <v>82</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>372</v>
+        <v>115</v>
       </c>
       <c r="E264" s="50"/>
       <c r="F264" s="51"/>
-      <c r="G264" s="33" t="n">
-        <f aca="false">Narxlar!$C$21</f>
-        <v>8</v>
+      <c r="G264" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="H264" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I264" s="7" t="n">
-        <f aca="false">Narxlar!$C$20/Narxlar!$C$19</f>
-        <v>67.2268907563025</v>
+        <f aca="false">Narxlar!$C$16</f>
+        <v>840</v>
       </c>
       <c r="J264" s="53" t="n">
         <f aca="false">G264*I264</f>
-        <v>537.81512605042</v>
+        <v>840</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14591,10 +14659,10 @@
         <v>82</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E265" s="50"/>
       <c r="F265" s="51"/>
@@ -14602,15 +14670,15 @@
         <v>1</v>
       </c>
       <c r="H265" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I265" s="7" t="n">
-        <f aca="false">Narxlar!$C$22/Narxlar!$C$19</f>
-        <v>1512.60504201681</v>
+        <f aca="false">Narxlar!$C$17</f>
+        <v>303</v>
       </c>
       <c r="J265" s="53" t="n">
         <f aca="false">G265*I265</f>
-        <v>1512.60504201681</v>
+        <v>303</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14621,32 +14689,26 @@
         <v>82</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="E266" s="50" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F266" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
-        <v>3.5</v>
-      </c>
-      <c r="G266" s="51" t="n">
-        <f aca="false">E266*F266</f>
-        <v>3.85</v>
+        <v>377</v>
+      </c>
+      <c r="E266" s="50"/>
+      <c r="F266" s="51"/>
+      <c r="G266" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="H266" s="5" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="I266" s="7" t="n">
-        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
-        <v>4.20168067226891</v>
+        <f aca="false">Narxlar!$C$18</f>
+        <v>2500</v>
       </c>
       <c r="J266" s="53" t="n">
         <f aca="false">G266*I266</f>
-        <v>16.1764705882353</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14657,32 +14719,27 @@
         <v>82</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="E267" s="50" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F267" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
-        <v>3.5</v>
-      </c>
-      <c r="G267" s="51" t="n">
-        <f aca="false">E267*F267</f>
-        <v>19.6</v>
+        <v>378</v>
+      </c>
+      <c r="E267" s="50"/>
+      <c r="F267" s="51"/>
+      <c r="G267" s="33" t="n">
+        <f aca="false">Narxlar!$C$21</f>
+        <v>8</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="I267" s="7" t="n">
-        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
-        <v>4.20168067226891</v>
+        <f aca="false">Narxlar!$C$20/Narxlar!$C$19</f>
+        <v>67.2268907563025</v>
       </c>
       <c r="J267" s="53" t="n">
         <f aca="false">G267*I267</f>
-        <v>82.3529411764706</v>
+        <v>537.81512605042</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14693,32 +14750,26 @@
         <v>82</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="E268" s="50" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F268" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
-        <v>3.5</v>
-      </c>
-      <c r="G268" s="51" t="n">
-        <f aca="false">E268*F268</f>
-        <v>19.6</v>
+        <v>379</v>
+      </c>
+      <c r="E268" s="50"/>
+      <c r="F268" s="51"/>
+      <c r="G268" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="H268" s="5" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="I268" s="7" t="n">
-        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
-        <v>4.20168067226891</v>
+        <f aca="false">Narxlar!$C$22/Narxlar!$C$19</f>
+        <v>1512.60504201681</v>
       </c>
       <c r="J268" s="53" t="n">
         <f aca="false">G268*I268</f>
-        <v>82.3529411764706</v>
+        <v>1512.60504201681</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14732,18 +14783,18 @@
         <v>18</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E269" s="50" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="F269" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G269" s="51" t="n">
         <f aca="false">E269*F269</f>
-        <v>2.625</v>
+        <v>3.85</v>
       </c>
       <c r="H269" s="5" t="s">
         <v>157</v>
@@ -14754,7 +14805,7 @@
       </c>
       <c r="J269" s="53" t="n">
         <f aca="false">G269*I269</f>
-        <v>11.0294117647059</v>
+        <v>16.1764705882353</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14768,18 +14819,18 @@
         <v>18</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E270" s="50" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="F270" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G270" s="51" t="n">
         <f aca="false">E270*F270</f>
-        <v>11.9</v>
+        <v>19.6</v>
       </c>
       <c r="H270" s="5" t="s">
         <v>157</v>
@@ -14790,7 +14841,7 @@
       </c>
       <c r="J270" s="53" t="n">
         <f aca="false">G270*I270</f>
-        <v>50</v>
+        <v>82.3529411764706</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14804,18 +14855,18 @@
         <v>18</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E271" s="50" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="F271" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G271" s="51" t="n">
         <f aca="false">E271*F271</f>
-        <v>14.7</v>
+        <v>19.6</v>
       </c>
       <c r="H271" s="5" t="s">
         <v>157</v>
@@ -14826,7 +14877,7 @@
       </c>
       <c r="J271" s="53" t="n">
         <f aca="false">G271*I271</f>
-        <v>61.764705882353</v>
+        <v>82.3529411764706</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14840,18 +14891,18 @@
         <v>18</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E272" s="50" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="F272" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G272" s="51" t="n">
         <f aca="false">E272*F272</f>
-        <v>5.25</v>
+        <v>2.625</v>
       </c>
       <c r="H272" s="5" t="s">
         <v>157</v>
@@ -14862,7 +14913,7 @@
       </c>
       <c r="J272" s="53" t="n">
         <f aca="false">G272*I272</f>
-        <v>22.0588235294118</v>
+        <v>11.0294117647059</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14876,18 +14927,18 @@
         <v>18</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E273" s="50" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="F273" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G273" s="51" t="n">
         <f aca="false">E273*F273</f>
-        <v>0.7</v>
+        <v>11.9</v>
       </c>
       <c r="H273" s="5" t="s">
         <v>157</v>
@@ -14898,7 +14949,7 @@
       </c>
       <c r="J273" s="53" t="n">
         <f aca="false">G273*I273</f>
-        <v>2.94117647058824</v>
+        <v>50</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14912,18 +14963,18 @@
         <v>18</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="E274" s="50" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="F274" s="31" t="n">
-        <f aca="false">Narxlar!$C$77</f>
+        <f aca="false">Narxlar!$C$80</f>
         <v>3.5</v>
       </c>
       <c r="G274" s="51" t="n">
         <f aca="false">E274*F274</f>
-        <v>5.25</v>
+        <v>14.7</v>
       </c>
       <c r="H274" s="5" t="s">
         <v>157</v>
@@ -14934,7 +14985,7 @@
       </c>
       <c r="J274" s="53" t="n">
         <f aca="false">G274*I274</f>
-        <v>22.0588235294118</v>
+        <v>61.764705882353</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14948,23 +14999,29 @@
         <v>18</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="E275" s="50"/>
-      <c r="F275" s="51"/>
-      <c r="G275" s="52" t="n">
-        <v>1</v>
+        <v>380</v>
+      </c>
+      <c r="E275" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F275" s="31" t="n">
+        <f aca="false">Narxlar!$C$80</f>
+        <v>3.5</v>
+      </c>
+      <c r="G275" s="51" t="n">
+        <f aca="false">E275*F275</f>
+        <v>5.25</v>
       </c>
       <c r="H275" s="5" t="s">
-        <v>253</v>
+        <v>157</v>
       </c>
       <c r="I275" s="7" t="n">
-        <f aca="false">Narxlar!$C$24/Narxlar!$C$19</f>
-        <v>100.840336134454</v>
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
       </c>
       <c r="J275" s="53" t="n">
         <f aca="false">G275*I275</f>
-        <v>100.840336134454</v>
+        <v>22.0588235294118</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14975,26 +15032,32 @@
         <v>82</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="E276" s="50"/>
-      <c r="F276" s="51"/>
-      <c r="G276" s="52" t="n">
-        <v>1</v>
+        <v>383</v>
+      </c>
+      <c r="E276" s="50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F276" s="31" t="n">
+        <f aca="false">Narxlar!$C$80</f>
+        <v>3.5</v>
+      </c>
+      <c r="G276" s="51" t="n">
+        <f aca="false">E276*F276</f>
+        <v>0.7</v>
       </c>
       <c r="H276" s="5" t="s">
-        <v>253</v>
+        <v>157</v>
       </c>
       <c r="I276" s="7" t="n">
-        <f aca="false">Narxlar!$C$52</f>
-        <v>7000</v>
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
       </c>
       <c r="J276" s="53" t="n">
         <f aca="false">G276*I276</f>
-        <v>7000</v>
+        <v>2.94117647058824</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15005,166 +15068,154 @@
         <v>82</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D277" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="E277" s="50"/>
-      <c r="F277" s="51"/>
-      <c r="G277" s="52" t="n">
+      <c r="E277" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F277" s="31" t="n">
+        <f aca="false">Narxlar!$C$80</f>
+        <v>3.5</v>
+      </c>
+      <c r="G277" s="51" t="n">
+        <f aca="false">E277*F277</f>
+        <v>5.25</v>
+      </c>
+      <c r="H277" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I277" s="7" t="n">
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
+      </c>
+      <c r="J277" s="53" t="n">
+        <f aca="false">G277*I277</f>
+        <v>22.0588235294118</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="5" t="n">
+        <v>219</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D278" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E278" s="50"/>
+      <c r="F278" s="51"/>
+      <c r="G278" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="H277" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="I277" s="7" t="n">
+      <c r="H278" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="I278" s="7" t="n">
+        <f aca="false">Narxlar!$C$24/Narxlar!$C$19</f>
+        <v>100.840336134454</v>
+      </c>
+      <c r="J278" s="53" t="n">
+        <f aca="false">G278*I278</f>
+        <v>100.840336134454</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D279" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E279" s="50"/>
+      <c r="F279" s="51"/>
+      <c r="G279" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H279" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="I279" s="7" t="n">
+        <f aca="false">Narxlar!$C$52</f>
+        <v>7000</v>
+      </c>
+      <c r="J279" s="53" t="n">
+        <f aca="false">G279*I279</f>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D280" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E280" s="50"/>
+      <c r="F280" s="51"/>
+      <c r="G280" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H280" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="I280" s="7" t="n">
         <f aca="false">Narxlar!$C$53</f>
         <v>7000</v>
       </c>
-      <c r="J277" s="53" t="n">
-        <f aca="false">G277*I277</f>
+      <c r="J280" s="53" t="n">
+        <f aca="false">G280*I280</f>
         <v>7000</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="54"/>
-      <c r="B278" s="54"/>
-      <c r="C278" s="54"/>
-      <c r="D278" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="E278" s="54"/>
-      <c r="F278" s="54"/>
-      <c r="G278" s="54"/>
-      <c r="H278" s="54"/>
-      <c r="I278" s="54"/>
-      <c r="J278" s="12" t="n">
-        <f aca="false">SUM(J259:J277)</f>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="54"/>
+      <c r="B281" s="54"/>
+      <c r="C281" s="54"/>
+      <c r="D281" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="E281" s="54"/>
+      <c r="F281" s="54"/>
+      <c r="G281" s="54"/>
+      <c r="H281" s="54"/>
+      <c r="I281" s="54"/>
+      <c r="J281" s="12" t="n">
+        <f aca="false">SUM(J262:J280)</f>
         <v>21120.9957983193</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="29" t="s">
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="B280" s="30"/>
-      <c r="C280" s="30"/>
-      <c r="D280" s="30"/>
-      <c r="E280" s="30"/>
-      <c r="F280" s="30"/>
-      <c r="G280" s="30"/>
-      <c r="H280" s="30"/>
-      <c r="I280" s="30"/>
-      <c r="J280" s="30"/>
-    </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="5" t="n">
-        <v>219</v>
-      </c>
-      <c r="B281" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C281" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D281" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="E281" s="50" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="F281" s="31" t="n">
-        <f aca="false">Narxlar!$C$84</f>
-        <v>2.5</v>
-      </c>
-      <c r="G281" s="51" t="n">
-        <f aca="false">E281*F281</f>
-        <v>13.625</v>
-      </c>
-      <c r="H281" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I281" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
-      </c>
-      <c r="J281" s="53" t="n">
-        <f aca="false">G281*I281</f>
-        <v>211.1875</v>
-      </c>
-    </row>
-    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="5" t="n">
-        <v>220</v>
-      </c>
-      <c r="B282" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C282" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D282" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="E282" s="50" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="F282" s="31" t="n">
-        <f aca="false">Narxlar!$C$84</f>
-        <v>2.5</v>
-      </c>
-      <c r="G282" s="51" t="n">
-        <f aca="false">E282*F282</f>
-        <v>13.625</v>
-      </c>
-      <c r="H282" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I282" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
-      </c>
-      <c r="J282" s="53" t="n">
-        <f aca="false">G282*I282</f>
-        <v>211.1875</v>
-      </c>
-    </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C283" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D283" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="E283" s="50" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F283" s="31" t="n">
-        <f aca="false">Narxlar!$C$84</f>
-        <v>2.5</v>
-      </c>
-      <c r="G283" s="51" t="n">
-        <f aca="false">E283*F283</f>
-        <v>21.5</v>
-      </c>
-      <c r="H283" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I283" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
-      </c>
-      <c r="J283" s="53" t="n">
-        <f aca="false">G283*I283</f>
-        <v>333.25</v>
-      </c>
+      <c r="B283" s="30"/>
+      <c r="C283" s="30"/>
+      <c r="D283" s="30"/>
+      <c r="E283" s="30"/>
+      <c r="F283" s="30"/>
+      <c r="G283" s="30"/>
+      <c r="H283" s="30"/>
+      <c r="I283" s="30"/>
+      <c r="J283" s="30"/>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="5" t="n">
@@ -15177,19 +15228,18 @@
         <v>10</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="E284" s="31" t="n">
-        <f aca="false">Narxlar!$C$82</f>
-        <v>0.9</v>
+        <v>388</v>
+      </c>
+      <c r="E284" s="50" t="n">
+        <v>5.45</v>
       </c>
       <c r="F284" s="31" t="n">
-        <f aca="false">Narxlar!$C$80</f>
-        <v>2.1</v>
+        <f aca="false">Narxlar!$C$87</f>
+        <v>2.5</v>
       </c>
       <c r="G284" s="51" t="n">
-        <f aca="false">-E284*F284</f>
-        <v>-1.89</v>
+        <f aca="false">E284*F284</f>
+        <v>13.625</v>
       </c>
       <c r="H284" s="5" t="s">
         <v>157</v>
@@ -15200,7 +15250,7 @@
       </c>
       <c r="J284" s="53" t="n">
         <f aca="false">G284*I284</f>
-        <v>-29.295</v>
+        <v>211.1875</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15211,26 +15261,32 @@
         <v>84</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="E285" s="50"/>
-      <c r="F285" s="51"/>
-      <c r="G285" s="52" t="n">
-        <v>1</v>
+        <v>389</v>
+      </c>
+      <c r="E285" s="50" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="F285" s="31" t="n">
+        <f aca="false">Narxlar!$C$87</f>
+        <v>2.5</v>
+      </c>
+      <c r="G285" s="51" t="n">
+        <f aca="false">E285*F285</f>
+        <v>13.625</v>
       </c>
       <c r="H285" s="5" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="I285" s="7" t="n">
-        <f aca="false">Narxlar!$C$8</f>
-        <v>1032</v>
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
       </c>
       <c r="J285" s="53" t="n">
         <f aca="false">G285*I285</f>
-        <v>1032</v>
+        <v>211.1875</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15241,151 +15297,161 @@
         <v>84</v>
       </c>
       <c r="C286" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E286" s="50" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F286" s="31" t="n">
+        <f aca="false">Narxlar!$C$87</f>
+        <v>2.5</v>
+      </c>
+      <c r="G286" s="51" t="n">
+        <f aca="false">E286*F286</f>
+        <v>21.5</v>
+      </c>
+      <c r="H286" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I286" s="7" t="n">
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
+      </c>
+      <c r="J286" s="53" t="n">
+        <f aca="false">G286*I286</f>
+        <v>333.25</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E287" s="31" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>0.9</v>
+      </c>
+      <c r="F287" s="31" t="n">
+        <f aca="false">Narxlar!$C$83</f>
+        <v>2.1</v>
+      </c>
+      <c r="G287" s="51" t="n">
+        <f aca="false">-E287*F287</f>
+        <v>-1.89</v>
+      </c>
+      <c r="H287" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I287" s="7" t="n">
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
+      </c>
+      <c r="J287" s="53" t="n">
+        <f aca="false">G287*I287</f>
+        <v>-29.295</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="E288" s="50"/>
+      <c r="F288" s="51"/>
+      <c r="G288" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I288" s="7" t="n">
+        <f aca="false">Narxlar!$C$8</f>
+        <v>1032</v>
+      </c>
+      <c r="J288" s="53" t="n">
+        <f aca="false">G288*I288</f>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C289" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D286" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="E286" s="50"/>
-      <c r="F286" s="51"/>
-      <c r="G286" s="52" t="n">
+      <c r="D289" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="E289" s="50"/>
+      <c r="F289" s="51"/>
+      <c r="G289" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="H286" s="5" t="s">
+      <c r="H289" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I286" s="7" t="n">
+      <c r="I289" s="7" t="n">
         <f aca="false">Narxlar!$C$54</f>
         <v>1000</v>
       </c>
-      <c r="J286" s="53" t="n">
-        <f aca="false">G286*I286</f>
+      <c r="J289" s="53" t="n">
+        <f aca="false">G289*I289</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="54"/>
-      <c r="B287" s="54"/>
-      <c r="C287" s="54"/>
-      <c r="D287" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="E287" s="54"/>
-      <c r="F287" s="54"/>
-      <c r="G287" s="54"/>
-      <c r="H287" s="54"/>
-      <c r="I287" s="54"/>
-      <c r="J287" s="12" t="n">
-        <f aca="false">SUM(J281:J286)</f>
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="54"/>
+      <c r="B290" s="54"/>
+      <c r="C290" s="54"/>
+      <c r="D290" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E290" s="54"/>
+      <c r="F290" s="54"/>
+      <c r="G290" s="54"/>
+      <c r="H290" s="54"/>
+      <c r="I290" s="54"/>
+      <c r="J290" s="12" t="n">
+        <f aca="false">SUM(J284:J289)</f>
         <v>2758.33</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="29" t="s">
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="B289" s="30"/>
-      <c r="C289" s="30"/>
-      <c r="D289" s="30"/>
-      <c r="E289" s="30"/>
-      <c r="F289" s="30"/>
-      <c r="G289" s="30"/>
-      <c r="H289" s="30"/>
-      <c r="I289" s="30"/>
-      <c r="J289" s="30"/>
-    </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="5" t="n">
-        <v>225</v>
-      </c>
-      <c r="B290" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C290" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D290" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="E290" s="50"/>
-      <c r="F290" s="51"/>
-      <c r="G290" s="33" t="n">
-        <f aca="false">Narxlar!$C$26</f>
-        <v>3</v>
-      </c>
-      <c r="H290" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I290" s="7" t="n">
-        <f aca="false">Narxlar!$C$25/Narxlar!$C$19</f>
-        <v>58.8235294117647</v>
-      </c>
-      <c r="J290" s="53" t="n">
-        <f aca="false">G290*I290</f>
-        <v>176.470588235294</v>
-      </c>
-    </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="5" t="n">
-        <v>226</v>
-      </c>
-      <c r="B291" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C291" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D291" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="E291" s="50"/>
-      <c r="F291" s="51"/>
-      <c r="G291" s="33" t="n">
-        <f aca="false">Narxlar!$C$28</f>
-        <v>3</v>
-      </c>
-      <c r="H291" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I291" s="7" t="n">
-        <f aca="false">Narxlar!$C$27/Narxlar!$C$19</f>
-        <v>100.840336134454</v>
-      </c>
-      <c r="J291" s="53" t="n">
-        <f aca="false">G291*I291</f>
-        <v>302.521008403361</v>
-      </c>
-    </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="5" t="n">
-        <v>227</v>
-      </c>
-      <c r="B292" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C292" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D292" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="E292" s="50"/>
-      <c r="F292" s="51"/>
-      <c r="G292" s="33" t="n">
-        <f aca="false">Narxlar!$C$30</f>
-        <v>4</v>
-      </c>
-      <c r="H292" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I292" s="7" t="n">
-        <f aca="false">Narxlar!$C$29/Narxlar!$C$19</f>
-        <v>54.6218487394958</v>
-      </c>
-      <c r="J292" s="53" t="n">
-        <f aca="false">G292*I292</f>
-        <v>218.487394957983</v>
-      </c>
+      <c r="B292" s="30"/>
+      <c r="C292" s="30"/>
+      <c r="D292" s="30"/>
+      <c r="E292" s="30"/>
+      <c r="F292" s="30"/>
+      <c r="G292" s="30"/>
+      <c r="H292" s="30"/>
+      <c r="I292" s="30"/>
+      <c r="J292" s="30"/>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="5" t="n">
@@ -15398,24 +15464,24 @@
         <v>19</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E293" s="50"/>
       <c r="F293" s="51"/>
       <c r="G293" s="33" t="n">
-        <f aca="false">Narxlar!$C$32</f>
-        <v>6</v>
+        <f aca="false">Narxlar!$C$26</f>
+        <v>3</v>
       </c>
       <c r="H293" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I293" s="7" t="n">
-        <f aca="false">Narxlar!$C$31/Narxlar!$C$19</f>
-        <v>16.8067226890756</v>
+        <f aca="false">Narxlar!$C$25/Narxlar!$C$19</f>
+        <v>58.8235294117647</v>
       </c>
       <c r="J293" s="53" t="n">
         <f aca="false">G293*I293</f>
-        <v>100.840336134454</v>
+        <v>176.470588235294</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15429,24 +15495,24 @@
         <v>19</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E294" s="50"/>
       <c r="F294" s="51"/>
       <c r="G294" s="33" t="n">
-        <f aca="false">Narxlar!$C$34</f>
-        <v>4</v>
+        <f aca="false">Narxlar!$C$28</f>
+        <v>3</v>
       </c>
       <c r="H294" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I294" s="7" t="n">
-        <f aca="false">Narxlar!$C$33/Narxlar!$C$19</f>
-        <v>33.6134453781513</v>
+        <f aca="false">Narxlar!$C$27/Narxlar!$C$19</f>
+        <v>100.840336134454</v>
       </c>
       <c r="J294" s="53" t="n">
         <f aca="false">G294*I294</f>
-        <v>134.453781512605</v>
+        <v>302.521008403361</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15460,24 +15526,24 @@
         <v>19</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E295" s="50"/>
       <c r="F295" s="51"/>
       <c r="G295" s="33" t="n">
-        <f aca="false">Narxlar!$C$36</f>
+        <f aca="false">Narxlar!$C$30</f>
         <v>4</v>
       </c>
       <c r="H295" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I295" s="7" t="n">
-        <f aca="false">Narxlar!$C$35/Narxlar!$C$19</f>
-        <v>33.6134453781513</v>
+        <f aca="false">Narxlar!$C$29/Narxlar!$C$19</f>
+        <v>54.6218487394958</v>
       </c>
       <c r="J295" s="53" t="n">
         <f aca="false">G295*I295</f>
-        <v>134.453781512605</v>
+        <v>218.487394957983</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15491,24 +15557,24 @@
         <v>19</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E296" s="50"/>
       <c r="F296" s="51"/>
       <c r="G296" s="33" t="n">
-        <f aca="false">Narxlar!$C$38</f>
-        <v>16</v>
+        <f aca="false">Narxlar!$C$32</f>
+        <v>6</v>
       </c>
       <c r="H296" s="5" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="I296" s="7" t="n">
-        <f aca="false">Narxlar!$C$37/Narxlar!$C$19</f>
-        <v>84.0336134453782</v>
+        <f aca="false">Narxlar!$C$31/Narxlar!$C$19</f>
+        <v>16.8067226890756</v>
       </c>
       <c r="J296" s="53" t="n">
         <f aca="false">G296*I296</f>
-        <v>1344.53781512605</v>
+        <v>100.840336134454</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15522,24 +15588,24 @@
         <v>19</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E297" s="50"/>
       <c r="F297" s="51"/>
       <c r="G297" s="33" t="n">
-        <f aca="false">Narxlar!$C$44</f>
+        <f aca="false">Narxlar!$C$34</f>
         <v>4</v>
       </c>
       <c r="H297" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I297" s="7" t="n">
-        <f aca="false">Narxlar!$C$43/Narxlar!$C$19</f>
-        <v>100.840336134454</v>
+        <f aca="false">Narxlar!$C$33/Narxlar!$C$19</f>
+        <v>33.6134453781513</v>
       </c>
       <c r="J297" s="53" t="n">
         <f aca="false">G297*I297</f>
-        <v>403.361344537815</v>
+        <v>134.453781512605</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15553,24 +15619,24 @@
         <v>19</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>162</v>
+        <v>399</v>
       </c>
       <c r="E298" s="50"/>
       <c r="F298" s="51"/>
-      <c r="G298" s="31" t="n">
-        <f aca="false">Narxlar!$C$46</f>
-        <v>40</v>
+      <c r="G298" s="33" t="n">
+        <f aca="false">Narxlar!$C$36</f>
+        <v>4</v>
       </c>
       <c r="H298" s="5" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I298" s="7" t="n">
-        <f aca="false">Narxlar!$C$45/Narxlar!$C$19</f>
-        <v>2.10084033613445</v>
+        <f aca="false">Narxlar!$C$35/Narxlar!$C$19</f>
+        <v>33.6134453781513</v>
       </c>
       <c r="J298" s="53" t="n">
         <f aca="false">G298*I298</f>
-        <v>84.0336134453782</v>
+        <v>134.453781512605</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15584,24 +15650,24 @@
         <v>19</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>165</v>
+        <v>400</v>
       </c>
       <c r="E299" s="50"/>
       <c r="F299" s="51"/>
-      <c r="G299" s="31" t="n">
-        <f aca="false">Narxlar!$C$48</f>
-        <v>40</v>
+      <c r="G299" s="33" t="n">
+        <f aca="false">Narxlar!$C$38</f>
+        <v>16</v>
       </c>
       <c r="H299" s="5" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="I299" s="7" t="n">
-        <f aca="false">Narxlar!$C$47/Narxlar!$C$19</f>
-        <v>1.00840336134454</v>
+        <f aca="false">Narxlar!$C$37/Narxlar!$C$19</f>
+        <v>84.0336134453782</v>
       </c>
       <c r="J299" s="53" t="n">
         <f aca="false">G299*I299</f>
-        <v>40.3361344537815</v>
+        <v>1344.53781512605</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15615,24 +15681,24 @@
         <v>19</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>168</v>
+        <v>401</v>
       </c>
       <c r="E300" s="50"/>
       <c r="F300" s="51"/>
       <c r="G300" s="33" t="n">
-        <f aca="false">Narxlar!$C$50</f>
-        <v>100</v>
+        <f aca="false">Narxlar!$C$44</f>
+        <v>4</v>
       </c>
       <c r="H300" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I300" s="7" t="n">
-        <f aca="false">Narxlar!$C$49/Narxlar!$C$19</f>
-        <v>0.420168067226891</v>
+        <f aca="false">Narxlar!$C$43/Narxlar!$C$19</f>
+        <v>100.840336134454</v>
       </c>
       <c r="J300" s="53" t="n">
         <f aca="false">G300*I300</f>
-        <v>42.0168067226891</v>
+        <v>403.361344537815</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15646,23 +15712,24 @@
         <v>19</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>396</v>
+        <v>162</v>
       </c>
       <c r="E301" s="50"/>
       <c r="F301" s="51"/>
-      <c r="G301" s="52" t="n">
-        <v>1</v>
+      <c r="G301" s="31" t="n">
+        <f aca="false">Narxlar!$C$46</f>
+        <v>40</v>
       </c>
       <c r="H301" s="5" t="s">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="I301" s="7" t="n">
-        <f aca="false">Narxlar!$C$51/Narxlar!$C$19</f>
-        <v>336.134453781513</v>
+        <f aca="false">Narxlar!$C$45/Narxlar!$C$19</f>
+        <v>2.10084033613445</v>
       </c>
       <c r="J301" s="53" t="n">
         <f aca="false">G301*I301</f>
-        <v>336.134453781513</v>
+        <v>84.0336134453782</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15673,27 +15740,27 @@
         <v>85</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>397</v>
+        <v>165</v>
       </c>
       <c r="E302" s="50"/>
       <c r="F302" s="51"/>
       <c r="G302" s="31" t="n">
-        <f aca="false">Narxlar!$C$41</f>
-        <v>58</v>
+        <f aca="false">Narxlar!$C$48</f>
+        <v>40</v>
       </c>
       <c r="H302" s="5" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="I302" s="7" t="n">
-        <f aca="false">Narxlar!$C$39/Narxlar!$C$19</f>
-        <v>8.40336134453782</v>
+        <f aca="false">Narxlar!$C$47/Narxlar!$C$19</f>
+        <v>1.00840336134454</v>
       </c>
       <c r="J302" s="53" t="n">
         <f aca="false">G302*I302</f>
-        <v>487.394957983193</v>
+        <v>40.3361344537815</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15704,27 +15771,27 @@
         <v>85</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>398</v>
+        <v>168</v>
       </c>
       <c r="E303" s="50"/>
       <c r="F303" s="51"/>
-      <c r="G303" s="31" t="n">
-        <f aca="false">Narxlar!$C$41</f>
-        <v>58</v>
+      <c r="G303" s="33" t="n">
+        <f aca="false">Narxlar!$C$50</f>
+        <v>100</v>
       </c>
       <c r="H303" s="5" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="I303" s="7" t="n">
-        <f aca="false">Narxlar!$C$40/Narxlar!$C$19</f>
-        <v>8.40336134453782</v>
+        <f aca="false">Narxlar!$C$49/Narxlar!$C$19</f>
+        <v>0.420168067226891</v>
       </c>
       <c r="J303" s="53" t="n">
         <f aca="false">G303*I303</f>
-        <v>487.394957983193</v>
+        <v>42.0168067226891</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15735,27 +15802,26 @@
         <v>85</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E304" s="50"/>
       <c r="F304" s="51"/>
-      <c r="G304" s="31" t="n">
-        <f aca="false">Narxlar!$C$42</f>
-        <v>16</v>
+      <c r="G304" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="H304" s="5" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="I304" s="7" t="n">
-        <f aca="false">Narxlar!$C$39/Narxlar!$C$19</f>
-        <v>8.40336134453782</v>
+        <f aca="false">Narxlar!$C$51/Narxlar!$C$19</f>
+        <v>336.134453781513</v>
       </c>
       <c r="J304" s="53" t="n">
         <f aca="false">G304*I304</f>
-        <v>134.453781512605</v>
+        <v>336.134453781513</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15769,58 +15835,151 @@
         <v>20</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E305" s="50"/>
       <c r="F305" s="51"/>
       <c r="G305" s="31" t="n">
+        <f aca="false">Narxlar!$C$41</f>
+        <v>58</v>
+      </c>
+      <c r="H305" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I305" s="7" t="n">
+        <f aca="false">Narxlar!$C$39/Narxlar!$C$19</f>
+        <v>8.40336134453782</v>
+      </c>
+      <c r="J305" s="53" t="n">
+        <f aca="false">G305*I305</f>
+        <v>487.394957983193</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="5" t="n">
+        <v>241</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D306" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="E306" s="50"/>
+      <c r="F306" s="51"/>
+      <c r="G306" s="31" t="n">
+        <f aca="false">Narxlar!$C$41</f>
+        <v>58</v>
+      </c>
+      <c r="H306" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I306" s="7" t="n">
+        <f aca="false">Narxlar!$C$40/Narxlar!$C$19</f>
+        <v>8.40336134453782</v>
+      </c>
+      <c r="J306" s="53" t="n">
+        <f aca="false">G306*I306</f>
+        <v>487.394957983193</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="E307" s="50"/>
+      <c r="F307" s="51"/>
+      <c r="G307" s="31" t="n">
         <f aca="false">Narxlar!$C$42</f>
         <v>16</v>
       </c>
-      <c r="H305" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I305" s="7" t="n">
+      <c r="H307" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I307" s="7" t="n">
+        <f aca="false">Narxlar!$C$39/Narxlar!$C$19</f>
+        <v>8.40336134453782</v>
+      </c>
+      <c r="J307" s="53" t="n">
+        <f aca="false">G307*I307</f>
+        <v>134.453781512605</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="5" t="n">
+        <v>243</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="E308" s="50"/>
+      <c r="F308" s="51"/>
+      <c r="G308" s="31" t="n">
+        <f aca="false">Narxlar!$C$42</f>
+        <v>16</v>
+      </c>
+      <c r="H308" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I308" s="7" t="n">
         <f aca="false">Narxlar!$C$40/Narxlar!$C$19</f>
         <v>8.40336134453782</v>
       </c>
-      <c r="J305" s="53" t="n">
-        <f aca="false">G305*I305</f>
+      <c r="J308" s="53" t="n">
+        <f aca="false">G308*I308</f>
         <v>134.453781512605</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="54"/>
-      <c r="B306" s="54"/>
-      <c r="C306" s="54"/>
-      <c r="D306" s="11" t="s">
-        <v>401</v>
-      </c>
-      <c r="E306" s="54"/>
-      <c r="F306" s="54"/>
-      <c r="G306" s="54"/>
-      <c r="H306" s="54"/>
-      <c r="I306" s="54"/>
-      <c r="J306" s="12" t="n">
-        <f aca="false">SUM(J290:J305)</f>
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="54"/>
+      <c r="B309" s="54"/>
+      <c r="C309" s="54"/>
+      <c r="D309" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="E309" s="54"/>
+      <c r="F309" s="54"/>
+      <c r="G309" s="54"/>
+      <c r="H309" s="54"/>
+      <c r="I309" s="54"/>
+      <c r="J309" s="12" t="n">
+        <f aca="false">SUM(J293:J308)</f>
         <v>4561.34453781513</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="54"/>
-      <c r="B308" s="54"/>
-      <c r="C308" s="54"/>
-      <c r="D308" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="E308" s="54"/>
-      <c r="F308" s="54"/>
-      <c r="G308" s="54"/>
-      <c r="H308" s="54"/>
-      <c r="I308" s="54"/>
-      <c r="J308" s="12" t="n">
-        <f aca="false">J13+J26+J38+J49+J67+J79+J93+J108+J129+J149+J164+J179+J186+J210+J235+J248+J252+J256+J278+J287+J306</f>
-        <v>69860.5503361345</v>
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="54"/>
+      <c r="B311" s="54"/>
+      <c r="C311" s="54"/>
+      <c r="D311" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="E311" s="54"/>
+      <c r="F311" s="54"/>
+      <c r="G311" s="54"/>
+      <c r="H311" s="54"/>
+      <c r="I311" s="54"/>
+      <c r="J311" s="12" t="n">
+        <f aca="false">J13+J26+J38+J49+J67+J79+J93+J108+J129+J149+J164+J179+J186+J210+J235+J251+J255+J259+J281+J290+J309</f>
+        <v>70910.5503361345</v>
       </c>
     </row>
   </sheetData>

--- a/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
+++ b/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
@@ -622,7 +622,7 @@
     <t xml:space="preserve">Sahna ekrani 86": koworkingdagi mavjud ekranni ko'chirish, kronshteyn va kabel</t>
   </si>
   <si>
-    <t xml:space="preserve">TAXMIN — ekran mavjud deb olingan; yangi 86" ekran ~$1 300</t>
+    <t xml:space="preserve">TAXMIN — ekran buyurtmachida mavjud (09.10); faqat kronshteyn va kabel</t>
   </si>
   <si>
     <t xml:space="preserve">Ovoz: 2 ta faol kolonka (devorga osiladi), simsiz mikrofon</t>

--- a/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
+++ b/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
@@ -541,10 +541,10 @@
     <t xml:space="preserve">Kanalizatsiya quvuri (40 m) va otvodlar</t>
   </si>
   <si>
-    <t xml:space="preserve">Konditsioner — 2-qavat (2 ta, 100 mingtalik, o'rnatish bilan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buyurtmachi: 2 ta uchun jami, o'rnatish bilan</t>
+    <t xml:space="preserve">Konditsioner — 2-qavat (2 ta «96-ka», 96 000 BTU/soat ≈ 28 kW, o'rnatish bilan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyurtmachi: 2 ta uchun jami, o'rnatish bilan; «100-lik» = 96-ka (09.10)</t>
   </si>
   <si>
     <t xml:space="preserve">Havo kanallari (vozduxovod), 200 m²</t>
@@ -739,7 +739,7 @@
     <t xml:space="preserve">• 3-qavat: 5-xona — o'quv xonasi (24 o'rin, bambuk panel va interaktiv doska); 2-xona — erkaklar hojatxonasi. Santexnika soni ikkala hojatxona uchun jami (2-qavatdagisi — ayollar: 2 kabina, unitazli, eng ichkarida; oldida rakovinali tambur — 6-xona 3-qavatga o'tish yo'lagi bo'lgani uchun ikki eshik orqali kiriladi); kafel faqat erkaklar hojatxonasi uchun (devor 58 m², pol 16 m²).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Konditsioner va ventilyatsiya (buyurtmachi summalari, o'rnatish bilan): 2-qavatga 2 ta 100 mingtalik konditsioner va 200 m² havo kanali — «Butun qavat» qatorida; 3-qavat o'quv xonasiga 1 ta konditsioner.</t>
+    <t xml:space="preserve">• Konditsioner va ventilyatsiya (buyurtmachi summalari, o'rnatish bilan): 2-qavatga 2 ta «96-ka» (96 000 BTU/soat) konditsioner va 200 m² havo kanali — «Butun qavat» qatorida; 3-qavat o'quv xonasiga 1 ta konditsioner.</t>
   </si>
   <si>
     <t xml:space="preserve">• Santexnika: 4 ta kabina, issiq va sovuq suv quvurlari (40 m dan), 100 ta aksessuar, kanalizatsiya quvuri va otvodlar — «Hojatxonalar» qatorida.</t>
@@ -1180,7 +1180,7 @@
     <t xml:space="preserve">Qurilish chiqindisini olib chiqish (jami)</t>
   </si>
   <si>
-    <t xml:space="preserve">Konditsioner — 2 ta, 100 mingtalik, o'rnatish bilan (jami)</t>
+    <t xml:space="preserve">Konditsioner — 2 ta «96-ka» (96 000 BTU/soat), o'rnatish bilan (jami)</t>
   </si>
   <si>
     <t xml:space="preserve">Havo kanallari (vozduxovod), 200 m² (jami)</t>

--- a/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
+++ b/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
@@ -766,7 +766,7 @@
     <t xml:space="preserve">• 3-qavat: 5-xona — o'quv xonasi (24 o'rin, bambuk panel va interaktiv doska); 2-xona — erkaklar hojatxonasi. Santexnika soni ikkala hojatxona uchun jami (2-qavatdagisi — ayollar: 2 kabina, unitazli, eng ichkarida; oldida rakovinali tambur — 6-xona 3-qavatga o'tish yo'lagi bo'lgani uchun ikki eshik orqali kiriladi); kafel faqat erkaklar hojatxonasi uchun (devor 58 m², pol 16 m²).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Ventilyatsiya va konditsionerlash (buyurtmachi, 12.10): 2 ta Welkin rekuperatori (28 mln so'm dan) va havo kanallari (HVAC sxemasidagi uzunlik × 300 000 so'm/m) — «Butun qavat» qatorida; split konditsionerlar: SR1–SR7 ga bittadan 24 000 BTU ($1 120), XZ1–XZ4 ga bittadan 12 000 BTU ($380) — xonalar qatorida; CEO xonasi va koworkingda konditsioner mavjud (koworkingdagisi koridorlarni ham sovutadi); 3-qavat o'quv xonasiga 1 ta konditsioner. Kirmagan: montaj (narxga kirmagan bo'lsa), diffuzor va panjaralar, shovqin so'ndirgichlar, kanal izolyatsiyasi, freon trassalari.</t>
+    <t xml:space="preserve">• Ventilyatsiya va konditsionerlash (buyurtmachi, 12.10): 2 ta Welkin rekuperatori (28 mln so'm dan) va havo kanallari (HVAC sxemasidagi uzunlik × 300 000 so'm/m) — «Butun qavat» qatorida; split konditsionerlar: SR1–SR7 ga bittadan 24 000 BTU ($1 120), XZ1–XZ4 ga bittadan 12 000 BTU ($380) — xonalar qatorida; CEO xonasi va koworkingda konditsioner mavjud (koworkingdagisi koridorlarni ham sovutadi); 3-qavat o'quv xonasiga 1 ta konditsioner. Sinflarning ko'cha tomoni to'liq oynali (buyurtmachi, 12.10) — tashqi bloklar tomda, trassa ~5–13 m. Kirmagan: montaj (narxga kirmagan bo'lsa), diffuzor va panjaralar, shovqin so'ndirgichlar, kanal izolyatsiyasi, freon trassalari, tomdagi tayanch ramalar, drenaj nasoslari (kerak bo'lsa).</t>
   </si>
   <si>
     <t xml:space="preserve">• Santexnika: 4 ta kabina, issiq va sovuq suv quvurlari (40 m dan), 100 ta aksessuar, kanalizatsiya quvuri va otvodlar — «Hojatxonalar» qatorida.</t>

--- a/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
+++ b/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="535">
   <si>
     <t xml:space="preserve">PDP Academy · Xadra filiali (1, 2 va 3-qavat): jami xarajatlar — yakuniy</t>
   </si>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">Havo kanallari uzunligi</t>
   </si>
   <si>
-    <t xml:space="preserve">HVAC sxemasidan: 197 m (taklif yo'nalish) + 10% burilish va ulanishlar</t>
+    <t xml:space="preserve">HVAC sxemasidan: 191 m (taklif yo'nalish) + 10% burilish va ulanishlar</t>
   </si>
   <si>
     <t xml:space="preserve">Buyurtmachi (12.10): SR1–SR7 ga bittadan</t>
@@ -1307,67 +1307,67 @@
     <t xml:space="preserve">Koworking (sahna) bilan orasidagi devor</t>
   </si>
   <si>
+    <t xml:space="preserve">Admin (XZ2) bilan orasidagi devor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsultant stoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsultant kreslosi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mijoz stuli (har konsultantga 2 ta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kutish divani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hujjat shkafi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interyer: brend devor, o'simliklar, dekor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jami: Offline sotuv (XZ1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offline sotuv (XZ1) bilan orasidagi devor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-xona bilan orasidagi devor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ish stoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ofis kreslosi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mehmon stuli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interyer: dekor, o'simliklar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jami: Admin (XZ2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call-markaz (XZ4) bilan orasidagi devor — mavjud devordagi bo'shliqni yopish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-xona bilan orasidagi devor — mavjud devordagi bo'shliqni yopish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eski o'rta devor (admin bilan orasida)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Call-markaz (XZ4) bilan orasidagi devor</t>
   </si>
   <si>
-    <t xml:space="preserve">Konsultant stoli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konsultant kreslosi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mijoz stuli (har konsultantga 2 ta)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kutish divani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hujjat shkafi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interyer: brend devor, o'simliklar, dekor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jami: Offline sotuv (XZ1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ustozlar xonasi (XZ3) bilan orasidagi devor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ish stoli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ofis kreslosi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mehmon stuli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interyer: dekor, o'simliklar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jami: Admin (XZ2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin (XZ2) bilan orasidagi devor — mavjud devordagi bo'shliqni yopish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-xona bilan orasidagi devor — mavjud devordagi bo'shliqni yopish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eski o'rta devor (call-markaz bilan orasida)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin (XZ2) bilan orasidagi devor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jami: Ustozlar xonasi (XZ3)</t>
   </si>
   <si>
-    <t xml:space="preserve">Eski o'rta devor (ustozlar xonasi bilan orasida)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offline sotuv (XZ1) bilan orasidagi devor</t>
+    <t xml:space="preserve">Eski o'rta devor (sotuv bilan orasida)</t>
   </si>
   <si>
     <t xml:space="preserve">Jami: Call-markaz (XZ4)</t>
@@ -1403,78 +1403,75 @@
     <t xml:space="preserve">Koridor oxiridagi logotip devori (4-xona bilan orasida)</t>
   </si>
   <si>
+    <t xml:space="preserve">Shisha ustidagi GKL (Call-markaz (XZ4) bilan orasida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shisha ustidagi GKL (Ustozlar xonasi (XZ3) bilan orasida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik ustidagi GKL (1-xona eshigi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik ustidagi GKL (2-xona eshigi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik ustidagi GKL (3-xona eshigi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik ustidagi GKL (Ustozlar xonasi (XZ3) eshigi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik ustidagi GKL (Call-markaz (XZ4) eshigi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampalar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jami: K1 koridori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shisha ustidagi GKL (Offline sotuv (XZ1) bilan orasida)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Shisha ustidagi GKL (Admin (XZ2) bilan orasida)</t>
   </si>
   <si>
-    <t xml:space="preserve">Shisha ustidagi GKL (Ustozlar xonasi (XZ3) bilan orasida)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-xona bilan orasidagi devor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik ustidagi GKL (1-xona eshigi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik ustidagi GKL (2-xona eshigi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik ustidagi GKL (3-xona eshigi)</t>
+    <t xml:space="preserve">Eshik yonidagi kesak (4-xona tomoni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik yonidagi kesak (7-xona tomoni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shisha ustidagi GKL (7-xona bilan orasida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik yonidagi kesak (6-xona tomoni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shisha ustidagi GKL (6-xona bilan orasida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik yonidagi kesak (5-xona tomoni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik ustidagi GKL (4-xona eshigi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik ustidagi GKL (5-xona eshigi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik ustidagi GKL (6-xona eshigi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik ustidagi GKL (7-xona eshigi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshik ustidagi GKL (Offline sotuv (XZ1) eshigi)</t>
   </si>
   <si>
     <t xml:space="preserve">Eshik ustidagi GKL (Admin (XZ2) eshigi)</t>
   </si>
   <si>
-    <t xml:space="preserve">Eshik ustidagi GKL (Ustozlar xonasi (XZ3) eshigi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lampalar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jami: K1 koridori</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shisha ustidagi GKL (Offline sotuv (XZ1) bilan orasida)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shisha ustidagi GKL (Call-markaz (XZ4) bilan orasida)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik yonidagi kesak (4-xona tomoni)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik yonidagi kesak (7-xona tomoni)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shisha ustidagi GKL (7-xona bilan orasida)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik yonidagi kesak (6-xona tomoni)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shisha ustidagi GKL (6-xona bilan orasida)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik yonidagi kesak (5-xona tomoni)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik ustidagi GKL (4-xona eshigi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik ustidagi GKL (5-xona eshigi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik ustidagi GKL (6-xona eshigi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik ustidagi GKL (7-xona eshigi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik ustidagi GKL (Offline sotuv (XZ1) eshigi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eshik ustidagi GKL (Call-markaz (XZ4) eshigi)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jami: K2 koridori</t>
   </si>
   <si>
@@ -1523,6 +1520,9 @@
     <t xml:space="preserve">Perila (buyurtmachi bergan uzunlik)</t>
   </si>
   <si>
+    <t xml:space="preserve">Zina panjarasi — ZN2 zinasi — koworking tomoni (devor o'rniga)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jami: Zinapoya</t>
   </si>
   <si>
@@ -1539,6 +1539,9 @@
   </si>
   <si>
     <t xml:space="preserve">Signalizatsiya, o't o'chirgichlar, evakuatsiya belgilari, avariya chiroqlari (jami)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devorni buzish — ZN2 to'sig'i — o'rniga zina panjarasi</t>
   </si>
   <si>
     <t xml:space="preserve">Devorni buzish — K2 koridori o'rnidagi bo'lak</t>
@@ -2470,7 +2473,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>6600</v>
       </c>
       <c r="D6" s="8" t="n">
@@ -2479,7 +2482,7 @@
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C6/$C$22)</f>
-        <v>0.0880220465392778</v>
+        <v>0.0877963639330384</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2490,7 +2493,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>3529.2</v>
       </c>
       <c r="D7" s="8" t="n">
@@ -2499,7 +2502,7 @@
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C7/$C$22)</f>
-        <v>0.0470677888858211</v>
+        <v>0.0469471102412847</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2510,16 +2513,16 @@
         <v>10</v>
       </c>
       <c r="C8" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
-        <v>8481.91</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
+        <v>8465.635</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">C8*Narxlar!$C$19</f>
-        <v>100934729</v>
+        <v>100741056.5</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C8/$C$22)</f>
-        <v>0.113120466176055</v>
+        <v>0.112613935058222</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2530,7 +2533,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>8256</v>
       </c>
       <c r="D9" s="8" t="n">
@@ -2539,7 +2542,7 @@
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C9/$C$22)</f>
-        <v>0.110107578216406</v>
+        <v>0.109825269792601</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2550,16 +2553,16 @@
         <v>12</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
-        <v>2016</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
+        <v>2322.6</v>
       </c>
       <c r="D10" s="8" t="n">
         <f aca="false">C10*Narxlar!$C$19</f>
-        <v>23990400</v>
+        <v>27638940</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C10/$C$22)</f>
-        <v>0.0268867342156339</v>
+        <v>0.0308963386167992</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2570,7 +2573,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>3024</v>
       </c>
       <c r="D11" s="8" t="n">
@@ -2579,7 +2582,7 @@
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C11/$C$22)</f>
-        <v>0.0403301013234509</v>
+        <v>0.0402266976565921</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2590,7 +2593,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>2119</v>
       </c>
       <c r="D12" s="8" t="n">
@@ -2599,7 +2602,7 @@
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C12/$C$22)</f>
-        <v>0.0282604116085954</v>
+        <v>0.0281879538142588</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2610,7 +2613,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>3250</v>
       </c>
       <c r="D13" s="8" t="n">
@@ -2619,7 +2622,7 @@
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C13/$C$22)</f>
-        <v>0.0433441895837353</v>
+        <v>0.0432330579973295</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2630,7 +2633,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>537.81512605042</v>
       </c>
       <c r="D14" s="8" t="n">
@@ -2639,7 +2642,7 @@
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C14/$C$22)</f>
-        <v>0.00717266485677843</v>
+        <v>0.00715427462657812</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2650,7 +2653,7 @@
         <v>17</v>
       </c>
       <c r="C15" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>1512.60504201681</v>
       </c>
       <c r="D15" s="8" t="n">
@@ -2659,7 +2662,7 @@
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C15/$C$22)</f>
-        <v>0.0201731199096893</v>
+        <v>0.020121397387251</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2670,16 +2673,16 @@
         <v>18</v>
       </c>
       <c r="C16" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
-        <v>286.86974789916</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
+        <v>340.546218487395</v>
       </c>
       <c r="D16" s="8" t="n">
         <f aca="false">C16*Narxlar!$C$19</f>
-        <v>3413750</v>
+        <v>4052500</v>
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C16/$C$22)</f>
-        <v>0.00382588822731678</v>
+        <v>0.00453010905065748</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2690,7 +2693,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>3317.64705882353</v>
       </c>
       <c r="D17" s="8" t="n">
@@ -2699,7 +2702,7 @@
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C17/$C$22)</f>
-        <v>0.0442463763352519</v>
+        <v>0.0441329316027038</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2710,7 +2713,7 @@
         <v>20</v>
       </c>
       <c r="C18" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>1243.6974789916</v>
       </c>
       <c r="D18" s="8" t="n">
@@ -2719,7 +2722,7 @@
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C18/$C$22)</f>
-        <v>0.0165867874813001</v>
+        <v>0.0165442600739619</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2730,16 +2733,16 @@
         <v>21</v>
       </c>
       <c r="C19" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
-        <v>20536.4705882353</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
+        <v>20385.2100840336</v>
       </c>
       <c r="D19" s="8" t="n">
         <f aca="false">C19*Narxlar!$C$19</f>
-        <v>244384000</v>
+        <v>242584000</v>
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C19/$C$22)</f>
-        <v>0.273888207556084</v>
+        <v>0.271173836877161</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2750,7 +2753,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>9900</v>
       </c>
       <c r="D20" s="8" t="n">
@@ -2759,7 +2762,7 @@
       </c>
       <c r="E20" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C20/$C$22)</f>
-        <v>0.132033069808917</v>
+        <v>0.131694545899558</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2770,7 +2773,7 @@
         <v>23</v>
       </c>
       <c r="C21" s="7" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>370</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -2779,7 +2782,7 @@
       </c>
       <c r="E21" s="9" t="n">
         <f aca="false">IF($C$22=0,0,C21/$C$22)</f>
-        <v>0.00493456927568679</v>
+        <v>0.00492191737200367</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2789,11 +2792,11 @@
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">SUM(C6:C21)</f>
-        <v>74981.2150420168</v>
+        <v>75173.9560084034</v>
       </c>
       <c r="D22" s="13" t="n">
         <f aca="false">C22*Narxlar!$C$19</f>
-        <v>892276459</v>
+        <v>894570076.5</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">SUM(E6:E21)</f>
@@ -2808,11 +2811,11 @@
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">C22*Narxlar!$C$83</f>
-        <v>7498.12150420168</v>
+        <v>7517.39560084034</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">C23*Narxlar!$C$19</f>
-        <v>89227645.9</v>
+        <v>89457007.65</v>
       </c>
       <c r="E23" s="16"/>
     </row>
@@ -2823,11 +2826,11 @@
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">C22+C23</f>
-        <v>82479.3365462185</v>
+        <v>82691.3516092437</v>
       </c>
       <c r="D24" s="22" t="n">
         <f aca="false">C24*Narxlar!$C$19</f>
-        <v>981504104.9</v>
+        <v>984027084.15</v>
       </c>
       <c r="E24" s="20"/>
     </row>
@@ -2837,7 +2840,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="25" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")+SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")+SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,"1-qavat — kirish zali (resepshn, turniket)",'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")+SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")+SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,"1-qavat — kirish zali (resepshn, turniket)",'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>11020</v>
       </c>
       <c r="D25" s="26" t="n">
@@ -2885,7 +2888,7 @@
       </c>
       <c r="E29" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C29/$C$34)</f>
-        <v>0.0457447908529883</v>
+        <v>0.0456275042864124</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2905,7 +2908,7 @@
       </c>
       <c r="E30" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C30/$C$34)</f>
-        <v>0.36641844206718</v>
+        <v>0.36547896983004</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2917,15 +2920,15 @@
       </c>
       <c r="C31" s="7" t="n">
         <f aca="false">'Xonalar bo''yicha'!$W$25</f>
-        <v>11712.98</v>
+        <v>11696.705</v>
       </c>
       <c r="D31" s="8" t="n">
         <f aca="false">C31*Narxlar!$C$19</f>
-        <v>139384462</v>
+        <v>139190789.5</v>
       </c>
       <c r="E31" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C31/$C$34)</f>
-        <v>0.156212192526308</v>
+        <v>0.155595177120817</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2937,15 +2940,15 @@
       </c>
       <c r="C32" s="7" t="n">
         <f aca="false">'Xonalar bo''yicha'!$W$34</f>
-        <v>25044.0605042017</v>
+        <v>25253.0764705882</v>
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">C32*Narxlar!$C$19</f>
-        <v>298024320</v>
+        <v>300511610</v>
       </c>
       <c r="E32" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C32/$C$34)</f>
-        <v>0.334004463520201</v>
+        <v>0.335928529127366</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2965,7 +2968,7 @@
       </c>
       <c r="E33" s="9" t="n">
         <f aca="false">IF($C$34=0,0,C33/$C$34)</f>
-        <v>0.0976201110333227</v>
+        <v>0.0973698196353654</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2975,11 +2978,11 @@
       </c>
       <c r="C34" s="12" t="n">
         <f aca="false">SUM(C29:C33)</f>
-        <v>74981.2150420168</v>
+        <v>75173.9560084034</v>
       </c>
       <c r="D34" s="13" t="n">
         <f aca="false">C34*Narxlar!$C$19</f>
-        <v>892276459</v>
+        <v>894570076.5</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">SUM(E29:E33)</f>
@@ -3154,7 +3157,7 @@
       </c>
       <c r="K9" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I9/$I$15)</f>
-        <v>0.0943295086977073</v>
+        <v>0.0940876541827855</v>
       </c>
       <c r="L9" s="37" t="n">
         <f aca="false">SUM($I$9:I9)</f>
@@ -3184,27 +3187,27 @@
       </c>
       <c r="G10" s="36" t="n">
         <f aca="false">M99</f>
-        <v>286.86974789916</v>
+        <v>340.546218487395</v>
       </c>
       <c r="H10" s="37" t="n">
         <f aca="false">G10*Narxlar!$C$83</f>
-        <v>28.686974789916</v>
+        <v>34.0546218487395</v>
       </c>
       <c r="I10" s="37" t="n">
         <f aca="false">G10+H10</f>
-        <v>315.556722689076</v>
+        <v>374.600840336134</v>
       </c>
       <c r="J10" s="38" t="n">
         <f aca="false">I10*Narxlar!$C$19</f>
-        <v>3755125</v>
+        <v>4457750</v>
       </c>
       <c r="K10" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I10/$I$15)</f>
-        <v>0.00382588822731678</v>
+        <v>0.00453010905065748</v>
       </c>
       <c r="L10" s="37" t="n">
         <f aca="false">SUM($I$9:I10)</f>
-        <v>8095.79201680672</v>
+        <v>8154.83613445378</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3230,27 +3233,27 @@
       </c>
       <c r="G11" s="36" t="n">
         <f aca="false">N99</f>
-        <v>12020.9613445378</v>
+        <v>11869.7008403361</v>
       </c>
       <c r="H11" s="37" t="n">
         <f aca="false">G11*Narxlar!$C$83</f>
-        <v>1202.09613445378</v>
+        <v>1186.97008403361</v>
       </c>
       <c r="I11" s="37" t="n">
         <f aca="false">G11+H11</f>
-        <v>13223.0574789916</v>
+        <v>13056.6709243697</v>
       </c>
       <c r="J11" s="38" t="n">
         <f aca="false">I11*Narxlar!$C$19</f>
-        <v>157354384</v>
+        <v>155374384</v>
       </c>
       <c r="K11" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I11/$I$15)</f>
-        <v>0.160319639229662</v>
+        <v>0.15789645072037</v>
       </c>
       <c r="L11" s="37" t="n">
         <f aca="false">SUM($I$9:I11)</f>
-        <v>21318.8494957983</v>
+        <v>21211.5070588235</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3276,27 +3279,27 @@
       </c>
       <c r="G12" s="36" t="n">
         <f aca="false">O99</f>
-        <v>25750.2074789916</v>
+        <v>25733.9324789916</v>
       </c>
       <c r="H12" s="37" t="n">
         <f aca="false">G12*Narxlar!$C$83</f>
-        <v>2575.02074789916</v>
+        <v>2573.39324789916</v>
       </c>
       <c r="I12" s="37" t="n">
         <f aca="false">G12+H12</f>
-        <v>28325.2282268908</v>
+        <v>28307.3257268908</v>
       </c>
       <c r="J12" s="38" t="n">
         <f aca="false">I12*Narxlar!$C$19</f>
-        <v>337070215.9</v>
+        <v>336857176.15</v>
       </c>
       <c r="K12" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I12/$I$15)</f>
-        <v>0.343422115319978</v>
+        <v>0.342325106265725</v>
       </c>
       <c r="L12" s="37" t="n">
         <f aca="false">SUM($I$9:I12)</f>
-        <v>49644.0777226891</v>
+        <v>49518.8327857143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3322,27 +3325,27 @@
       </c>
       <c r="G13" s="36" t="n">
         <f aca="false">P99</f>
-        <v>22510.2352941176</v>
+        <v>22816.8352941176</v>
       </c>
       <c r="H13" s="37" t="n">
         <f aca="false">G13*Narxlar!$C$83</f>
-        <v>2251.02352941176</v>
+        <v>2281.68352941176</v>
       </c>
       <c r="I13" s="37" t="n">
         <f aca="false">G13+H13</f>
-        <v>24761.2588235294</v>
+        <v>25098.5188235294</v>
       </c>
       <c r="J13" s="38" t="n">
         <f aca="false">I13*Narxlar!$C$19</f>
-        <v>294658980</v>
+        <v>298672374</v>
       </c>
       <c r="K13" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I13/$I$15)</f>
-        <v>0.300211663434684</v>
+        <v>0.303520481103416</v>
       </c>
       <c r="L13" s="37" t="n">
         <f aca="false">SUM($I$9:I13)</f>
-        <v>74405.3365462185</v>
+        <v>74617.3516092437</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3384,11 +3387,11 @@
       </c>
       <c r="K14" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I14/$I$15)</f>
-        <v>0.0978911850906514</v>
+        <v>0.0976401986770457</v>
       </c>
       <c r="L14" s="37" t="n">
         <f aca="false">SUM($I$9:I14)</f>
-        <v>82479.3365462185</v>
+        <v>82691.3516092437</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3411,19 +3414,19 @@
       </c>
       <c r="G15" s="41" t="n">
         <f aca="false">SUM(G9:G14)</f>
-        <v>74981.2150420168</v>
+        <v>75173.9560084034</v>
       </c>
       <c r="H15" s="41" t="n">
         <f aca="false">SUM(H9:H14)</f>
-        <v>7498.12150420168</v>
+        <v>7517.39560084034</v>
       </c>
       <c r="I15" s="41" t="n">
         <f aca="false">SUM(I9:I14)</f>
-        <v>82479.3365462185</v>
+        <v>82691.3516092437</v>
       </c>
       <c r="J15" s="42" t="n">
         <f aca="false">I15*Narxlar!$C$19</f>
-        <v>981504104.9</v>
+        <v>984027084.15</v>
       </c>
       <c r="K15" s="14" t="n">
         <f aca="false">SUM(K9:K14)</f>
@@ -3852,7 +3855,7 @@
       </c>
       <c r="C31" s="48" t="n">
         <f aca="false">$I$10*MAX(0,MIN($F$10,EOMONTH(C$29,0))-MAX($E$10,C$29)+1)/($F$10-$E$10+1)</f>
-        <v>315.556722689076</v>
+        <v>374.600840336134</v>
       </c>
       <c r="D31" s="48" t="n">
         <f aca="false">$I$10*MAX(0,MIN($F$10,EOMONTH(D$29,0))-MAX($E$10,D$29)+1)/($F$10-$E$10+1)</f>
@@ -3876,11 +3879,11 @@
       </c>
       <c r="C32" s="48" t="n">
         <f aca="false">$I$11*MAX(0,MIN($F$11,EOMONTH(C$29,0))-MAX($E$11,C$29)+1)/($F$11-$E$11+1)</f>
-        <v>1889.00821128451</v>
+        <v>1865.23870348139</v>
       </c>
       <c r="D32" s="48" t="n">
         <f aca="false">$I$11*MAX(0,MIN($F$11,EOMONTH(D$29,0))-MAX($E$11,D$29)+1)/($F$11-$E$11+1)</f>
-        <v>11334.0492677071</v>
+        <v>11191.4322208884</v>
       </c>
       <c r="E32" s="48" t="n">
         <f aca="false">$I$11*MAX(0,MIN($F$11,EOMONTH(E$29,0))-MAX($E$11,E$29)+1)/($F$11-$E$11+1)</f>
@@ -3904,7 +3907,7 @@
       </c>
       <c r="D33" s="48" t="n">
         <f aca="false">$I$12*MAX(0,MIN($F$12,EOMONTH(D$29,0))-MAX($E$12,D$29)+1)/($F$12-$E$12+1)</f>
-        <v>28325.2282268908</v>
+        <v>28307.3257268908</v>
       </c>
       <c r="E33" s="48" t="n">
         <f aca="false">$I$12*MAX(0,MIN($F$12,EOMONTH(E$29,0))-MAX($E$12,E$29)+1)/($F$12-$E$12+1)</f>
@@ -3928,11 +3931,11 @@
       </c>
       <c r="D34" s="48" t="n">
         <f aca="false">$I$13*MAX(0,MIN($F$13,EOMONTH(D$29,0))-MAX($E$13,D$29)+1)/($F$13-$E$13+1)</f>
-        <v>13506.1411764706</v>
+        <v>13690.1011764706</v>
       </c>
       <c r="E34" s="48" t="n">
         <f aca="false">$I$13*MAX(0,MIN($F$13,EOMONTH(E$29,0))-MAX($E$13,E$29)+1)/($F$13-$E$13+1)</f>
-        <v>11255.1176470588</v>
+        <v>11408.4176470588</v>
       </c>
       <c r="F34" s="48" t="n">
         <f aca="false">$I$13*MAX(0,MIN($F$13,EOMONTH(F$29,0))-MAX($E$13,F$29)+1)/($F$13-$E$13+1)</f>
@@ -3969,15 +3972,15 @@
       </c>
       <c r="C36" s="41" t="n">
         <f aca="false">SUM(C30:C35)</f>
-        <v>9984.80022809124</v>
+        <v>10020.0748379352</v>
       </c>
       <c r="D36" s="41" t="n">
         <f aca="false">SUM(D30:D35)</f>
-        <v>53165.4186710684</v>
+        <v>53188.8591242497</v>
       </c>
       <c r="E36" s="41" t="n">
         <f aca="false">SUM(E30:E35)</f>
-        <v>19329.1176470588</v>
+        <v>19482.4176470588</v>
       </c>
       <c r="F36" s="41" t="n">
         <f aca="false">SUM(F30:F35)</f>
@@ -3990,15 +3993,15 @@
       </c>
       <c r="C37" s="42" t="n">
         <f aca="false">C36*Narxlar!$C$19</f>
-        <v>118819122.714286</v>
+        <v>119238890.571429</v>
       </c>
       <c r="D37" s="42" t="n">
         <f aca="false">D36*Narxlar!$C$19</f>
-        <v>632668482.185714</v>
+        <v>632947423.578571</v>
       </c>
       <c r="E37" s="42" t="n">
         <f aca="false">E36*Narxlar!$C$19</f>
-        <v>230016500</v>
+        <v>231840770</v>
       </c>
       <c r="F37" s="42" t="n">
         <f aca="false">F36*Narxlar!$C$19</f>
@@ -4074,7 +4077,7 @@
         <v>15</v>
       </c>
       <c r="D41" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A41)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A41)</f>
         <v>500</v>
       </c>
       <c r="E41" s="51" t="n">
@@ -4135,7 +4138,7 @@
         <v>15</v>
       </c>
       <c r="D42" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A42)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A42)</f>
         <v>250</v>
       </c>
       <c r="E42" s="51" t="n">
@@ -4196,7 +4199,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A43)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A43)</f>
         <v>2500</v>
       </c>
       <c r="E43" s="51" t="n">
@@ -4257,7 +4260,7 @@
         <v>21</v>
       </c>
       <c r="D44" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A44)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A44)</f>
         <v>4705.88235294118</v>
       </c>
       <c r="E44" s="51" t="n">
@@ -4318,7 +4321,7 @@
         <v>22</v>
       </c>
       <c r="D45" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A45)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A45)</f>
         <v>1500</v>
       </c>
       <c r="E45" s="51" t="n">
@@ -4379,7 +4382,7 @@
         <v>22</v>
       </c>
       <c r="D46" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A46)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A46)</f>
         <v>500</v>
       </c>
       <c r="E46" s="51" t="n">
@@ -4440,7 +4443,7 @@
         <v>22</v>
       </c>
       <c r="D47" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A47)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A47)</f>
         <v>650</v>
       </c>
       <c r="E47" s="51" t="n">
@@ -4501,7 +4504,7 @@
         <v>22</v>
       </c>
       <c r="D48" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A48)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A48)</f>
         <v>900</v>
       </c>
       <c r="E48" s="51" t="n">
@@ -4562,7 +4565,7 @@
         <v>22</v>
       </c>
       <c r="D49" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A49)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A49)</f>
         <v>100</v>
       </c>
       <c r="E49" s="51" t="n">
@@ -4623,7 +4626,7 @@
         <v>22</v>
       </c>
       <c r="D50" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A50)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A50)</f>
         <v>880</v>
       </c>
       <c r="E50" s="51" t="n">
@@ -4684,7 +4687,7 @@
         <v>22</v>
       </c>
       <c r="D51" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A51)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A51)</f>
         <v>360</v>
       </c>
       <c r="E51" s="51" t="n">
@@ -4745,7 +4748,7 @@
         <v>22</v>
       </c>
       <c r="D52" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A52)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A52)</f>
         <v>700</v>
       </c>
       <c r="E52" s="51" t="n">
@@ -4806,7 +4809,7 @@
         <v>22</v>
       </c>
       <c r="D53" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A53)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A53)</f>
         <v>600</v>
       </c>
       <c r="E53" s="51" t="n">
@@ -4867,8 +4870,8 @@
         <v>18</v>
       </c>
       <c r="D54" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A54)</f>
-        <v>186.029411764706</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A54)</f>
+        <v>239.705882352941</v>
       </c>
       <c r="E54" s="51" t="n">
         <v>0</v>
@@ -4898,7 +4901,7 @@
       </c>
       <c r="M54" s="53" t="n">
         <f aca="false">$D54*F54</f>
-        <v>186.029411764706</v>
+        <v>239.705882352941</v>
       </c>
       <c r="N54" s="53" t="n">
         <f aca="false">$D54*G54</f>
@@ -4928,7 +4931,7 @@
         <v>18</v>
       </c>
       <c r="D55" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A55)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A55)</f>
         <v>100.840336134454</v>
       </c>
       <c r="E55" s="51" t="n">
@@ -4989,7 +4992,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A56)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A56)</f>
         <v>3529.2</v>
       </c>
       <c r="E56" s="51" t="n">
@@ -5050,7 +5053,7 @@
         <v>14</v>
       </c>
       <c r="D57" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A57)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A57)</f>
         <v>303</v>
       </c>
       <c r="E57" s="51" t="n">
@@ -5111,7 +5114,7 @@
         <v>17</v>
       </c>
       <c r="D58" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A58)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A58)</f>
         <v>1512.60504201681</v>
       </c>
       <c r="E58" s="51" t="n">
@@ -5172,7 +5175,7 @@
         <v>19</v>
       </c>
       <c r="D59" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A59)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A59)</f>
         <v>1344.53781512605</v>
       </c>
       <c r="E59" s="51" t="n">
@@ -5233,7 +5236,7 @@
         <v>19</v>
       </c>
       <c r="D60" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A60)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A60)</f>
         <v>84.0336134453782</v>
       </c>
       <c r="E60" s="51" t="n">
@@ -5294,7 +5297,7 @@
         <v>19</v>
       </c>
       <c r="D61" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A61)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A61)</f>
         <v>40.3361344537815</v>
       </c>
       <c r="E61" s="51" t="n">
@@ -5355,7 +5358,7 @@
         <v>19</v>
       </c>
       <c r="D62" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A62)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A62)</f>
         <v>42.0168067226891</v>
       </c>
       <c r="E62" s="51" t="n">
@@ -5416,7 +5419,7 @@
         <v>19</v>
       </c>
       <c r="D63" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A63)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A63)</f>
         <v>336.134453781513</v>
       </c>
       <c r="E63" s="51" t="n">
@@ -5477,8 +5480,8 @@
         <v>21</v>
       </c>
       <c r="D64" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A64)</f>
-        <v>5470.58823529412</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A64)</f>
+        <v>5319.32773109244</v>
       </c>
       <c r="E64" s="51" t="n">
         <v>0</v>
@@ -5512,7 +5515,7 @@
       </c>
       <c r="N64" s="53" t="n">
         <f aca="false">$D64*G64</f>
-        <v>5470.58823529412</v>
+        <v>5319.32773109244</v>
       </c>
       <c r="O64" s="53" t="n">
         <f aca="false">$D64*H64</f>
@@ -5538,7 +5541,7 @@
         <v>22</v>
       </c>
       <c r="D65" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A65)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A65)</f>
         <v>700</v>
       </c>
       <c r="E65" s="51" t="n">
@@ -5599,7 +5602,7 @@
         <v>8</v>
       </c>
       <c r="D66" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A66)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A66)</f>
         <v>6600</v>
       </c>
       <c r="E66" s="51" t="n">
@@ -5660,8 +5663,8 @@
         <v>10</v>
       </c>
       <c r="D67" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A67)</f>
-        <v>8481.91</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A67)</f>
+        <v>8465.635</v>
       </c>
       <c r="E67" s="51" t="n">
         <v>0</v>
@@ -5699,7 +5702,7 @@
       </c>
       <c r="O67" s="53" t="n">
         <f aca="false">$D67*H67</f>
-        <v>8481.91</v>
+        <v>8465.635</v>
       </c>
       <c r="P67" s="53" t="n">
         <f aca="false">$D67*I67</f>
@@ -5721,7 +5724,7 @@
         <v>20</v>
       </c>
       <c r="D68" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A68)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A68)</f>
         <v>621.848739495798</v>
       </c>
       <c r="E68" s="51" t="n">
@@ -5782,7 +5785,7 @@
         <v>20</v>
       </c>
       <c r="D69" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A69)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A69)</f>
         <v>621.848739495798</v>
       </c>
       <c r="E69" s="51" t="n">
@@ -5843,7 +5846,7 @@
         <v>21</v>
       </c>
       <c r="D70" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A70)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A70)</f>
         <v>7840</v>
       </c>
       <c r="E70" s="51" t="n">
@@ -5904,7 +5907,7 @@
         <v>21</v>
       </c>
       <c r="D71" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A71)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A71)</f>
         <v>1520</v>
       </c>
       <c r="E71" s="51" t="n">
@@ -5965,7 +5968,7 @@
         <v>21</v>
       </c>
       <c r="D72" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A72)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A72)</f>
         <v>1000</v>
       </c>
       <c r="E72" s="51" t="n">
@@ -6026,7 +6029,7 @@
         <v>22</v>
       </c>
       <c r="D73" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A73)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A73)</f>
         <v>250</v>
       </c>
       <c r="E73" s="51" t="n">
@@ -6087,7 +6090,7 @@
         <v>11</v>
       </c>
       <c r="D74" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A74)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A74)</f>
         <v>8256</v>
       </c>
       <c r="E74" s="51" t="n">
@@ -6148,8 +6151,8 @@
         <v>12</v>
       </c>
       <c r="D75" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A75)</f>
-        <v>2016</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A75)</f>
+        <v>2322.6</v>
       </c>
       <c r="E75" s="51" t="n">
         <v>0</v>
@@ -6191,7 +6194,7 @@
       </c>
       <c r="P75" s="53" t="n">
         <f aca="false">$D75*I75</f>
-        <v>2016</v>
+        <v>2322.6</v>
       </c>
       <c r="Q75" s="53" t="n">
         <f aca="false">$D75*J75</f>
@@ -6209,7 +6212,7 @@
         <v>13</v>
       </c>
       <c r="D76" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A76)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A76)</f>
         <v>2016</v>
       </c>
       <c r="E76" s="51" t="n">
@@ -6270,7 +6273,7 @@
         <v>13</v>
       </c>
       <c r="D77" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A77)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A77)</f>
         <v>1008</v>
       </c>
       <c r="E77" s="51" t="n">
@@ -6331,7 +6334,7 @@
         <v>14</v>
       </c>
       <c r="D78" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A78)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A78)</f>
         <v>640</v>
       </c>
       <c r="E78" s="51" t="n">
@@ -6392,7 +6395,7 @@
         <v>14</v>
       </c>
       <c r="D79" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A79)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A79)</f>
         <v>336</v>
       </c>
       <c r="E79" s="51" t="n">
@@ -6453,7 +6456,7 @@
         <v>14</v>
       </c>
       <c r="D80" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A80)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A80)</f>
         <v>840</v>
       </c>
       <c r="E80" s="51" t="n">
@@ -6514,7 +6517,7 @@
         <v>16</v>
       </c>
       <c r="D81" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A81)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A81)</f>
         <v>537.81512605042</v>
       </c>
       <c r="E81" s="51" t="n">
@@ -6575,7 +6578,7 @@
         <v>19</v>
       </c>
       <c r="D82" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A82)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A82)</f>
         <v>176.470588235294</v>
       </c>
       <c r="E82" s="51" t="n">
@@ -6636,7 +6639,7 @@
         <v>19</v>
       </c>
       <c r="D83" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A83)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A83)</f>
         <v>302.521008403361</v>
       </c>
       <c r="E83" s="51" t="n">
@@ -6697,7 +6700,7 @@
         <v>19</v>
       </c>
       <c r="D84" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A84)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A84)</f>
         <v>218.487394957983</v>
       </c>
       <c r="E84" s="51" t="n">
@@ -6758,7 +6761,7 @@
         <v>19</v>
       </c>
       <c r="D85" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A85)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A85)</f>
         <v>100.840336134454</v>
       </c>
       <c r="E85" s="51" t="n">
@@ -6819,7 +6822,7 @@
         <v>19</v>
       </c>
       <c r="D86" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A86)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A86)</f>
         <v>134.453781512605</v>
       </c>
       <c r="E86" s="51" t="n">
@@ -6880,7 +6883,7 @@
         <v>19</v>
       </c>
       <c r="D87" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A87)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A87)</f>
         <v>134.453781512605</v>
       </c>
       <c r="E87" s="51" t="n">
@@ -6941,7 +6944,7 @@
         <v>19</v>
       </c>
       <c r="D88" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A88)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A88)</f>
         <v>403.361344537815</v>
       </c>
       <c r="E88" s="51" t="n">
@@ -7002,7 +7005,7 @@
         <v>22</v>
       </c>
       <c r="D89" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A89)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A89)</f>
         <v>450</v>
       </c>
       <c r="E89" s="51" t="n">
@@ -7063,7 +7066,7 @@
         <v>22</v>
       </c>
       <c r="D90" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A90)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A90)</f>
         <v>60</v>
       </c>
       <c r="E90" s="51" t="n">
@@ -7124,7 +7127,7 @@
         <v>22</v>
       </c>
       <c r="D91" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A91)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A91)</f>
         <v>600</v>
       </c>
       <c r="E91" s="51" t="n">
@@ -7185,7 +7188,7 @@
         <v>22</v>
       </c>
       <c r="D92" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A92)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A92)</f>
         <v>300</v>
       </c>
       <c r="E92" s="51" t="n">
@@ -7246,7 +7249,7 @@
         <v>22</v>
       </c>
       <c r="D93" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A93)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A93)</f>
         <v>450</v>
       </c>
       <c r="E93" s="51" t="n">
@@ -7307,7 +7310,7 @@
         <v>22</v>
       </c>
       <c r="D94" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A94)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A94)</f>
         <v>500</v>
       </c>
       <c r="E94" s="51" t="n">
@@ -7368,7 +7371,7 @@
         <v>22</v>
       </c>
       <c r="D95" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A95)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A95)</f>
         <v>300</v>
       </c>
       <c r="E95" s="51" t="n">
@@ -7429,7 +7432,7 @@
         <v>22</v>
       </c>
       <c r="D96" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A96)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A96)</f>
         <v>100</v>
       </c>
       <c r="E96" s="51" t="n">
@@ -7490,7 +7493,7 @@
         <v>23</v>
       </c>
       <c r="D97" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A97)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A97)</f>
         <v>120</v>
       </c>
       <c r="E97" s="51" t="n">
@@ -7551,7 +7554,7 @@
         <v>23</v>
       </c>
       <c r="D98" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$K$5:$K$310,$A98)</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$K$5:$K$312,$A98)</f>
         <v>250</v>
       </c>
       <c r="E98" s="51" t="n">
@@ -7609,7 +7612,7 @@
       <c r="C99" s="11"/>
       <c r="D99" s="41" t="n">
         <f aca="false">SUM(D41:D98)</f>
-        <v>74981.2150420168</v>
+        <v>75173.9560084034</v>
       </c>
       <c r="E99" s="11"/>
       <c r="F99" s="11"/>
@@ -7624,19 +7627,19 @@
       </c>
       <c r="M99" s="41" t="n">
         <f aca="false">SUM(M41:M98)</f>
-        <v>286.86974789916</v>
+        <v>340.546218487395</v>
       </c>
       <c r="N99" s="41" t="n">
         <f aca="false">SUM(N41:N98)</f>
-        <v>12020.9613445378</v>
+        <v>11869.7008403361</v>
       </c>
       <c r="O99" s="41" t="n">
         <f aca="false">SUM(O41:O98)</f>
-        <v>25750.2074789916</v>
+        <v>25733.9324789916</v>
       </c>
       <c r="P99" s="41" t="n">
         <f aca="false">SUM(P41:P98)</f>
-        <v>22510.2352941176</v>
+        <v>22816.8352941176</v>
       </c>
       <c r="Q99" s="41" t="n">
         <f aca="false">SUM(Q41:Q98)</f>
@@ -7824,87 +7827,87 @@
         <v>235</v>
       </c>
       <c r="B6" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D6" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F6" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H6" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J6" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>750</v>
       </c>
       <c r="O6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>2680</v>
       </c>
       <c r="V6" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A6,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A6,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W6" s="58" t="n">
@@ -8037,87 +8040,87 @@
         <v>237</v>
       </c>
       <c r="B10" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>13.75</v>
       </c>
       <c r="C10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>756.25</v>
       </c>
       <c r="D10" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>7.25</v>
       </c>
       <c r="E10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>87</v>
       </c>
       <c r="F10" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H10" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J10" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>1120</v>
       </c>
       <c r="U10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V10" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A10,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A10,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W10" s="58" t="n">
@@ -8130,87 +8133,87 @@
         <v>238</v>
       </c>
       <c r="B11" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>14</v>
       </c>
       <c r="C11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>770</v>
       </c>
       <c r="D11" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>6.3</v>
       </c>
       <c r="E11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>75.6</v>
       </c>
       <c r="F11" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H11" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J11" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>1120</v>
       </c>
       <c r="U11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V11" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A11,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A11,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W11" s="58" t="n">
@@ -8223,87 +8226,87 @@
         <v>239</v>
       </c>
       <c r="B12" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>2.25</v>
       </c>
       <c r="C12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>123.75</v>
       </c>
       <c r="D12" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>17.875</v>
       </c>
       <c r="E12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>214.5</v>
       </c>
       <c r="F12" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H12" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J12" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>1120</v>
       </c>
       <c r="U12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V12" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A12,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A12,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W12" s="58" t="n">
@@ -8316,87 +8319,87 @@
         <v>240</v>
       </c>
       <c r="B13" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>2.25</v>
       </c>
       <c r="C13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>123.75</v>
       </c>
       <c r="D13" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>52</v>
       </c>
       <c r="E13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>624</v>
       </c>
       <c r="F13" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>50.4</v>
       </c>
       <c r="G13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>781.2</v>
       </c>
       <c r="H13" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J13" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>1120</v>
       </c>
       <c r="U13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V13" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A13,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A13,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W13" s="58" t="n">
@@ -8409,87 +8412,87 @@
         <v>241</v>
       </c>
       <c r="B14" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>2.25</v>
       </c>
       <c r="C14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>123.75</v>
       </c>
       <c r="D14" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>27.5</v>
       </c>
       <c r="E14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>330</v>
       </c>
       <c r="F14" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H14" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J14" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>1120</v>
       </c>
       <c r="U14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V14" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A14,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A14,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W14" s="58" t="n">
@@ -8502,87 +8505,87 @@
         <v>242</v>
       </c>
       <c r="B15" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>14</v>
       </c>
       <c r="C15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>770</v>
       </c>
       <c r="D15" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>25.55</v>
       </c>
       <c r="E15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>306.6</v>
       </c>
       <c r="F15" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H15" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J15" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>1120</v>
       </c>
       <c r="U15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V15" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A15,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A15,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W15" s="58" t="n">
@@ -8595,87 +8598,87 @@
         <v>243</v>
       </c>
       <c r="B16" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>14</v>
       </c>
       <c r="C16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>770</v>
       </c>
       <c r="D16" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>30.45</v>
       </c>
       <c r="E16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>365.4</v>
       </c>
       <c r="F16" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>53.9</v>
       </c>
       <c r="G16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>835.45</v>
       </c>
       <c r="H16" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J16" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>1120</v>
       </c>
       <c r="U16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V16" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A16,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A16,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W16" s="58" t="n">
@@ -8808,87 +8811,87 @@
         <v>245</v>
       </c>
       <c r="B20" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>14.25</v>
       </c>
       <c r="C20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>783.75</v>
       </c>
       <c r="D20" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>5.7</v>
       </c>
       <c r="E20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>68.4</v>
       </c>
       <c r="F20" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>18.2</v>
       </c>
       <c r="G20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>282.1</v>
       </c>
       <c r="H20" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J20" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>380</v>
       </c>
       <c r="U20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>2340</v>
       </c>
       <c r="V20" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A20,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A20,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W20" s="58" t="n">
@@ -8901,92 +8904,92 @@
         <v>246</v>
       </c>
       <c r="B21" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
-        <v>14.25</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
+        <v>14.5</v>
       </c>
       <c r="C21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
-        <v>783.75</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
+        <v>797.5</v>
       </c>
       <c r="D21" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
-        <v>10.95</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
+        <v>5.8</v>
       </c>
       <c r="E21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
-        <v>131.4</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
+        <v>69.6</v>
       </c>
       <c r="F21" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
-        <v>19.6</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
+        <v>18.2</v>
       </c>
       <c r="G21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
-        <v>303.8</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
+        <v>282.1</v>
       </c>
       <c r="H21" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J21" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>380</v>
       </c>
       <c r="U21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>1470</v>
       </c>
       <c r="V21" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A21,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A21,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W21" s="58" t="n">
         <f aca="false">C21+E21+G21+I21+K21+L21+M21+N21+O21+P21+Q21+R21+S21+T21+U21+V21</f>
-        <v>3236.95</v>
+        <v>3167.2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8994,87 +8997,87 @@
         <v>247</v>
       </c>
       <c r="B22" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>14.5</v>
       </c>
       <c r="C22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>797.5</v>
       </c>
       <c r="D22" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>12.45</v>
       </c>
       <c r="E22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>149.4</v>
       </c>
       <c r="F22" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>30.1</v>
       </c>
       <c r="G22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>466.55</v>
       </c>
       <c r="H22" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J22" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>380</v>
       </c>
       <c r="U22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V22" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A22,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A22,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W22" s="58" t="n">
@@ -9087,92 +9090,92 @@
         <v>248</v>
       </c>
       <c r="B23" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
-        <v>14.5</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
+        <v>14.25</v>
       </c>
       <c r="C23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
-        <v>797.5</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
+        <v>783.75</v>
       </c>
       <c r="D23" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
-        <v>5.8</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
+        <v>10.95</v>
       </c>
       <c r="E23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
-        <v>69.6</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
+        <v>131.4</v>
       </c>
       <c r="F23" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
-        <v>29.4</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
+        <v>29.75</v>
       </c>
       <c r="G23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
-        <v>455.7</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
+        <v>461.125</v>
       </c>
       <c r="H23" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J23" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>380</v>
       </c>
       <c r="U23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V23" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A23,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A23,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W23" s="58" t="n">
         <f aca="false">C23+E23+G23+I23+K23+L23+M23+N23+O23+P23+Q23+R23+S23+T23+U23+V23</f>
-        <v>1870.8</v>
+        <v>1924.275</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9180,87 +9183,87 @@
         <v>249</v>
       </c>
       <c r="B24" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D24" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F24" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>29.26</v>
       </c>
       <c r="G24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>453.53</v>
       </c>
       <c r="H24" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J24" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>168</v>
       </c>
       <c r="M24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V24" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A24,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A24,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W24" s="58" t="n">
@@ -9290,11 +9293,11 @@
       </c>
       <c r="F25" s="59" t="n">
         <f aca="false">SUM(F20:F24)</f>
-        <v>126.56</v>
+        <v>125.51</v>
       </c>
       <c r="G25" s="41" t="n">
         <f aca="false">SUM(G20:G24)</f>
-        <v>1961.68</v>
+        <v>1945.405</v>
       </c>
       <c r="H25" s="60" t="n">
         <f aca="false">SUM(H20:H24)</f>
@@ -9358,7 +9361,7 @@
       </c>
       <c r="W25" s="41" t="n">
         <f aca="false">SUM(W20:W24)</f>
-        <v>11712.98</v>
+        <v>11696.705</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9393,87 +9396,87 @@
         <v>251</v>
       </c>
       <c r="B28" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D28" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>37.85</v>
       </c>
       <c r="E28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>454.2</v>
       </c>
       <c r="F28" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H28" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J28" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>336</v>
       </c>
       <c r="M28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V28" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A28,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A28,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W28" s="58" t="n">
@@ -9486,87 +9489,87 @@
         <v>252</v>
       </c>
       <c r="B29" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D29" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>35.7</v>
       </c>
       <c r="E29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>428.4</v>
       </c>
       <c r="F29" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H29" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J29" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>336</v>
       </c>
       <c r="M29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V29" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A29,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A29,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W29" s="58" t="n">
@@ -9579,87 +9582,87 @@
         <v>253</v>
       </c>
       <c r="B30" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D30" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>9.625</v>
       </c>
       <c r="E30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>115.5</v>
       </c>
       <c r="F30" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H30" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J30" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>336</v>
       </c>
       <c r="M30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>3410</v>
       </c>
       <c r="V30" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A30,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A30,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>370</v>
       </c>
       <c r="W30" s="58" t="n">
@@ -9672,87 +9675,87 @@
         <v>254</v>
       </c>
       <c r="B31" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D31" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>9.1</v>
       </c>
       <c r="E31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>109.2</v>
       </c>
       <c r="F31" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H31" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J31" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V31" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A31,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A31,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W31" s="58" t="n">
@@ -9765,92 +9768,92 @@
         <v>255</v>
       </c>
       <c r="B32" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D32" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F32" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H32" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J32" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
-        <v>24</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
+        <v>27.65</v>
       </c>
       <c r="K32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
-        <v>2016</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
+        <v>2322.6</v>
       </c>
       <c r="L32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V32" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A32,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A32,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W32" s="58" t="n">
         <f aca="false">C32+E32+G32+I32+K32+L32+M32+N32+O32+P32+Q32+R32+S32+T32+U32+V32</f>
-        <v>2016</v>
+        <v>2322.6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9858,92 +9861,92 @@
         <v>256</v>
       </c>
       <c r="B33" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D33" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F33" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H33" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J33" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>2119</v>
       </c>
       <c r="N33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>2500</v>
       </c>
       <c r="O33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>537.81512605042</v>
       </c>
       <c r="P33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>1512.60504201681</v>
       </c>
       <c r="Q33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
-        <v>286.86974789916</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
+        <v>340.546218487395</v>
       </c>
       <c r="R33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
-        <v>10176.4705882353</v>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
+        <v>10025.2100840336</v>
       </c>
       <c r="U33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V33" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A33,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A33,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W33" s="58" t="n">
         <f aca="false">C33+E33+G33+I33+K33+L33+M33+N33+O33+P33+Q33+R33+S33+T33+U33+V33</f>
-        <v>17132.7605042017</v>
+        <v>17035.1764705882</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9984,11 +9987,11 @@
       </c>
       <c r="J34" s="59" t="n">
         <f aca="false">SUM(J28:J33)</f>
-        <v>24</v>
+        <v>27.65</v>
       </c>
       <c r="K34" s="41" t="n">
         <f aca="false">SUM(K28:K33)</f>
-        <v>2016</v>
+        <v>2322.6</v>
       </c>
       <c r="L34" s="41" t="n">
         <f aca="false">SUM(L28:L33)</f>
@@ -10012,7 +10015,7 @@
       </c>
       <c r="Q34" s="41" t="n">
         <f aca="false">SUM(Q28:Q33)</f>
-        <v>286.86974789916</v>
+        <v>340.546218487395</v>
       </c>
       <c r="R34" s="41" t="n">
         <f aca="false">SUM(R28:R33)</f>
@@ -10024,7 +10027,7 @@
       </c>
       <c r="T34" s="41" t="n">
         <f aca="false">SUM(T28:T33)</f>
-        <v>10176.4705882353</v>
+        <v>10025.2100840336</v>
       </c>
       <c r="U34" s="41" t="n">
         <f aca="false">SUM(U28:U33)</f>
@@ -10036,7 +10039,7 @@
       </c>
       <c r="W34" s="41" t="n">
         <f aca="false">SUM(W28:W33)</f>
-        <v>25044.0605042017</v>
+        <v>25253.0764705882</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10071,87 +10074,87 @@
         <v>258</v>
       </c>
       <c r="B37" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D37" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F37" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>46.86</v>
       </c>
       <c r="G37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>726.33</v>
       </c>
       <c r="H37" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1</v>
       </c>
       <c r="I37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>1032</v>
       </c>
       <c r="J37" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>0</v>
       </c>
       <c r="S37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>0</v>
       </c>
       <c r="T37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>1000</v>
       </c>
       <c r="U37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V37" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A37,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A37,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W37" s="58" t="n">
@@ -10164,87 +10167,87 @@
         <v>259</v>
       </c>
       <c r="B38" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="C38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Shisha devor")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Shisha devor")</f>
         <v>0</v>
       </c>
       <c r="D38" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="E38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Gips karton (GKL)")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Gips karton (GKL)")</f>
         <v>0</v>
       </c>
       <c r="F38" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="G38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Bambuk panel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Bambuk panel")</f>
         <v>0</v>
       </c>
       <c r="H38" s="57" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="I38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Interaktiv doska")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Interaktiv doska")</f>
         <v>0</v>
       </c>
       <c r="J38" s="56" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$G$5:$G$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="K38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Perila")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Perila")</f>
         <v>0</v>
       </c>
       <c r="L38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Yoritish")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Yoritish")</f>
         <v>0</v>
       </c>
       <c r="M38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Kamera tizimi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Kamera tizimi")</f>
         <v>0</v>
       </c>
       <c r="N38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Logotip")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Logotip")</f>
         <v>0</v>
       </c>
       <c r="O38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Matli plyonka")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Matli plyonka")</f>
         <v>0</v>
       </c>
       <c r="P38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Yong'in xavfsizligi")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Yong'in xavfsizligi")</f>
         <v>0</v>
       </c>
       <c r="Q38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Buzish ishlari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Buzish ishlari")</f>
         <v>0</v>
       </c>
       <c r="R38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Santexnika")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Santexnika")</f>
         <v>3317.64705882353</v>
       </c>
       <c r="S38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Kafel")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Kafel")</f>
         <v>1243.6974789916</v>
       </c>
       <c r="T38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Konditsioner va ventilyatsiya")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Konditsioner va ventilyatsiya")</f>
         <v>0</v>
       </c>
       <c r="U38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"Mebel va interyer")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"Mebel va interyer")</f>
         <v>0</v>
       </c>
       <c r="V38" s="50" t="n">
-        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$310,'Hisob (batafsil)'!$B$5:$B$310,$A38,'Hisob (batafsil)'!$C$5:$C$310,"E'lon va e'tirof doskalari")</f>
+        <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$312,'Hisob (batafsil)'!$B$5:$B$312,$A38,'Hisob (batafsil)'!$C$5:$C$312,"E'lon va e'tirof doskalari")</f>
         <v>0</v>
       </c>
       <c r="W38" s="58" t="n">
@@ -10367,11 +10370,11 @@
       </c>
       <c r="F41" s="61" t="n">
         <f aca="false">F7+F17+F25+F34+F39</f>
-        <v>547.22</v>
+        <v>546.17</v>
       </c>
       <c r="G41" s="62" t="n">
         <f aca="false">G7+G17+G25+G34+G39</f>
-        <v>8481.91</v>
+        <v>8465.635</v>
       </c>
       <c r="H41" s="63" t="n">
         <f aca="false">H7+H17+H25+H34+H39</f>
@@ -10383,11 +10386,11 @@
       </c>
       <c r="J41" s="61" t="n">
         <f aca="false">J7+J17+J25+J34+J39</f>
-        <v>24</v>
+        <v>27.65</v>
       </c>
       <c r="K41" s="62" t="n">
         <f aca="false">K7+K17+K25+K34+K39</f>
-        <v>2016</v>
+        <v>2322.6</v>
       </c>
       <c r="L41" s="62" t="n">
         <f aca="false">L7+L17+L25+L34+L39</f>
@@ -10411,7 +10414,7 @@
       </c>
       <c r="Q41" s="62" t="n">
         <f aca="false">Q7+Q17+Q25+Q34+Q39</f>
-        <v>286.86974789916</v>
+        <v>340.546218487395</v>
       </c>
       <c r="R41" s="62" t="n">
         <f aca="false">R7+R17+R25+R34+R39</f>
@@ -10423,7 +10426,7 @@
       </c>
       <c r="T41" s="62" t="n">
         <f aca="false">T7+T17+T25+T34+T39</f>
-        <v>20536.4705882353</v>
+        <v>20385.2100840336</v>
       </c>
       <c r="U41" s="62" t="n">
         <f aca="false">U7+U17+U25+U34+U39</f>
@@ -10435,7 +10438,7 @@
       </c>
       <c r="W41" s="62" t="n">
         <f aca="false">W7+W17+W25+W34+W39</f>
-        <v>74981.2150420168</v>
+        <v>75173.9560084034</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10466,7 +10469,7 @@
       <c r="V42" s="16"/>
       <c r="W42" s="64" t="n">
         <f aca="false">W41*Narxlar!$C$83</f>
-        <v>7498.12150420168</v>
+        <v>7517.39560084034</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10496,7 +10499,7 @@
       <c r="V43" s="20"/>
       <c r="W43" s="62" t="n">
         <f aca="false">W41+W42</f>
-        <v>82479.3365462185</v>
+        <v>82691.3516092437</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10526,7 +10529,7 @@
       <c r="V44" s="20"/>
       <c r="W44" s="22" t="n">
         <f aca="false">W43*Narxlar!$C$19</f>
-        <v>981504104.9</v>
+        <v>984027084.15</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10534,7 +10537,7 @@
         <v>263</v>
       </c>
       <c r="W46" s="27" t="n">
-        <f aca="false">W41-'Hisob (batafsil)'!J311</f>
+        <f aca="false">W41-'Hisob (batafsil)'!J313</f>
         <v>0</v>
       </c>
     </row>
@@ -11454,7 +11457,7 @@
         <v>324</v>
       </c>
       <c r="C55" s="66" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>277</v>
@@ -12199,7 +12202,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K311"/>
+  <dimension ref="A1:K313"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -16419,10 +16422,10 @@
         <v>8</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="E137" s="73" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="F137" s="56" t="n">
         <f aca="false">Narxlar!$C$85</f>
@@ -16430,7 +16433,7 @@
       </c>
       <c r="G137" s="74" t="n">
         <f aca="false">E137*F137</f>
-        <v>6</v>
+        <v>6.125</v>
       </c>
       <c r="H137" s="5" t="s">
         <v>310</v>
@@ -16441,7 +16444,7 @@
       </c>
       <c r="J137" s="76" t="n">
         <f aca="false">G137*I137</f>
-        <v>330</v>
+        <v>336.875</v>
       </c>
       <c r="K137" s="24" t="s">
         <v>143</v>
@@ -16458,10 +16461,10 @@
         <v>8</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="E138" s="73" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="F138" s="56" t="n">
         <f aca="false">Narxlar!$C$85</f>
@@ -16469,7 +16472,7 @@
       </c>
       <c r="G138" s="74" t="n">
         <f aca="false">E138*F138</f>
-        <v>6</v>
+        <v>6.125</v>
       </c>
       <c r="H138" s="5" t="s">
         <v>310</v>
@@ -16480,7 +16483,7 @@
       </c>
       <c r="J138" s="76" t="n">
         <f aca="false">G138*I138</f>
-        <v>330</v>
+        <v>336.875</v>
       </c>
       <c r="K138" s="24" t="s">
         <v>143</v>
@@ -16497,7 +16500,7 @@
         <v>8</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="E139" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -16537,18 +16540,18 @@
         <v>9</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="E140" s="73" t="n">
-        <v>0.6</v>
+        <v>2.45</v>
       </c>
       <c r="F140" s="56" t="n">
-        <f aca="false">Narxlar!$C$84</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$86</f>
+        <v>1</v>
       </c>
       <c r="G140" s="74" t="n">
         <f aca="false">E140*F140</f>
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="H140" s="5" t="s">
         <v>310</v>
@@ -16559,7 +16562,7 @@
       </c>
       <c r="J140" s="76" t="n">
         <f aca="false">G140*I140</f>
-        <v>25.2</v>
+        <v>29.4</v>
       </c>
       <c r="K140" s="24" t="s">
         <v>123</v>
@@ -16576,18 +16579,18 @@
         <v>9</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="E141" s="73" t="n">
-        <v>0.9</v>
+        <v>2.45</v>
       </c>
       <c r="F141" s="56" t="n">
-        <f aca="false">Narxlar!$C$84</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$86</f>
+        <v>1</v>
       </c>
       <c r="G141" s="74" t="n">
         <f aca="false">E141*F141</f>
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="H141" s="5" t="s">
         <v>310</v>
@@ -16598,7 +16601,7 @@
       </c>
       <c r="J141" s="76" t="n">
         <f aca="false">G141*I141</f>
-        <v>37.8</v>
+        <v>29.4</v>
       </c>
       <c r="K141" s="24" t="s">
         <v>123</v>
@@ -16615,10 +16618,11 @@
         <v>9</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="E142" s="73" t="n">
-        <v>2.4</v>
+        <v>413</v>
+      </c>
+      <c r="E142" s="56" t="n">
+        <f aca="false">Narxlar!$C$89</f>
+        <v>0.9</v>
       </c>
       <c r="F142" s="56" t="n">
         <f aca="false">Narxlar!$C$86</f>
@@ -16626,7 +16630,7 @@
       </c>
       <c r="G142" s="74" t="n">
         <f aca="false">E142*F142</f>
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="H142" s="5" t="s">
         <v>310</v>
@@ -16637,7 +16641,7 @@
       </c>
       <c r="J142" s="76" t="n">
         <f aca="false">G142*I142</f>
-        <v>28.8</v>
+        <v>10.8</v>
       </c>
       <c r="K142" s="24" t="s">
         <v>123</v>
@@ -16651,35 +16655,35 @@
         <v>246</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>393</v>
+        <v>435</v>
       </c>
       <c r="E143" s="73" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="F143" s="56" t="n">
-        <f aca="false">Narxlar!$C$86</f>
-        <v>1</v>
+        <f aca="false">Narxlar!$C$90</f>
+        <v>3.5</v>
       </c>
       <c r="G143" s="74" t="n">
         <f aca="false">E143*F143</f>
-        <v>2.4</v>
+        <v>9.1</v>
       </c>
       <c r="H143" s="5" t="s">
         <v>310</v>
       </c>
       <c r="I143" s="7" t="n">
-        <f aca="false">Narxlar!$C$6</f>
-        <v>12</v>
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
       </c>
       <c r="J143" s="76" t="n">
         <f aca="false">G143*I143</f>
-        <v>28.8</v>
+        <v>141.05</v>
       </c>
       <c r="K143" s="24" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16690,36 +16694,35 @@
         <v>246</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="E144" s="56" t="n">
-        <f aca="false">Narxlar!$C$89</f>
-        <v>0.9</v>
+        <v>436</v>
+      </c>
+      <c r="E144" s="73" t="n">
+        <v>2.6</v>
       </c>
       <c r="F144" s="56" t="n">
-        <f aca="false">Narxlar!$C$86</f>
-        <v>1</v>
+        <f aca="false">Narxlar!$C$90</f>
+        <v>3.5</v>
       </c>
       <c r="G144" s="74" t="n">
         <f aca="false">E144*F144</f>
-        <v>0.9</v>
+        <v>9.1</v>
       </c>
       <c r="H144" s="5" t="s">
         <v>310</v>
       </c>
       <c r="I144" s="7" t="n">
-        <f aca="false">Narxlar!$C$6</f>
-        <v>12</v>
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
       </c>
       <c r="J144" s="76" t="n">
         <f aca="false">G144*I144</f>
-        <v>10.8</v>
+        <v>141.05</v>
       </c>
       <c r="K144" s="24" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16730,35 +16733,29 @@
         <v>246</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="E145" s="73" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F145" s="56" t="n">
-        <f aca="false">Narxlar!$C$90</f>
-        <v>3.5</v>
-      </c>
-      <c r="G145" s="74" t="n">
-        <f aca="false">E145*F145</f>
-        <v>9.8</v>
+        <v>399</v>
+      </c>
+      <c r="E145" s="73"/>
+      <c r="F145" s="74"/>
+      <c r="G145" s="75" t="n">
+        <v>1</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>310</v>
+        <v>386</v>
       </c>
       <c r="I145" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
+        <f aca="false">Narxlar!$C$12</f>
+        <v>168</v>
       </c>
       <c r="J145" s="76" t="n">
         <f aca="false">G145*I145</f>
-        <v>151.9</v>
+        <v>168</v>
       </c>
       <c r="K145" s="24" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16769,35 +16766,29 @@
         <v>246</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="E146" s="73" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F146" s="56" t="n">
-        <f aca="false">Narxlar!$C$90</f>
-        <v>3.5</v>
-      </c>
-      <c r="G146" s="74" t="n">
-        <f aca="false">E146*F146</f>
-        <v>9.8</v>
+        <v>152</v>
+      </c>
+      <c r="E146" s="73"/>
+      <c r="F146" s="74"/>
+      <c r="G146" s="75" t="n">
+        <v>1</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="I146" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
+        <f aca="false">Narxlar!$C$57</f>
+        <v>380</v>
       </c>
       <c r="J146" s="76" t="n">
         <f aca="false">G146*I146</f>
-        <v>151.9</v>
+        <v>380</v>
       </c>
       <c r="K146" s="24" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16808,29 +16799,29 @@
         <v>246</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>399</v>
+        <v>437</v>
       </c>
       <c r="E147" s="73"/>
       <c r="F147" s="74"/>
       <c r="G147" s="75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>386</v>
+        <v>283</v>
       </c>
       <c r="I147" s="7" t="n">
-        <f aca="false">Narxlar!$C$12</f>
-        <v>168</v>
+        <f aca="false">Narxlar!$C$59</f>
+        <v>220</v>
       </c>
       <c r="J147" s="76" t="n">
         <f aca="false">G147*I147</f>
-        <v>168</v>
+        <v>440</v>
       </c>
       <c r="K147" s="24" t="s">
-        <v>159</v>
+        <v>111</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16841,29 +16832,29 @@
         <v>246</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>152</v>
+        <v>438</v>
       </c>
       <c r="E148" s="73"/>
       <c r="F148" s="74"/>
       <c r="G148" s="75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H148" s="5" t="s">
         <v>283</v>
       </c>
       <c r="I148" s="7" t="n">
-        <f aca="false">Narxlar!$C$57</f>
-        <v>380</v>
+        <f aca="false">Narxlar!$C$60</f>
+        <v>130</v>
       </c>
       <c r="J148" s="76" t="n">
         <f aca="false">G148*I148</f>
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="K148" s="24" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16877,7 +16868,7 @@
         <v>22</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E149" s="73"/>
       <c r="F149" s="74"/>
@@ -16888,15 +16879,15 @@
         <v>283</v>
       </c>
       <c r="I149" s="7" t="n">
-        <f aca="false">Narxlar!$C$59</f>
-        <v>220</v>
+        <f aca="false">Narxlar!$C$61</f>
+        <v>60</v>
       </c>
       <c r="J149" s="76" t="n">
         <f aca="false">G149*I149</f>
-        <v>440</v>
+        <v>120</v>
       </c>
       <c r="K149" s="24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16910,26 +16901,26 @@
         <v>22</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E150" s="73"/>
       <c r="F150" s="74"/>
       <c r="G150" s="75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H150" s="5" t="s">
         <v>283</v>
       </c>
       <c r="I150" s="7" t="n">
-        <f aca="false">Narxlar!$C$60</f>
-        <v>130</v>
+        <f aca="false">Narxlar!$C$63</f>
+        <v>350</v>
       </c>
       <c r="J150" s="76" t="n">
         <f aca="false">G150*I150</f>
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="K150" s="24" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16943,124 +16934,136 @@
         <v>22</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E151" s="73"/>
       <c r="F151" s="74"/>
       <c r="G151" s="75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>283</v>
+        <v>386</v>
       </c>
       <c r="I151" s="7" t="n">
-        <f aca="false">Narxlar!$C$61</f>
-        <v>60</v>
+        <f aca="false">Narxlar!$C$66</f>
+        <v>300</v>
       </c>
       <c r="J151" s="76" t="n">
         <f aca="false">G151*I151</f>
+        <v>300</v>
+      </c>
+      <c r="K151" s="24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="77"/>
+      <c r="B152" s="77"/>
+      <c r="C152" s="77"/>
+      <c r="D152" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="E152" s="77"/>
+      <c r="F152" s="77"/>
+      <c r="G152" s="77"/>
+      <c r="H152" s="77"/>
+      <c r="I152" s="77"/>
+      <c r="J152" s="12" t="n">
+        <f aca="false">SUM(J137:J151)</f>
+        <v>3167.2</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="54" t="s">
+        <v>247</v>
+      </c>
+      <c r="B154" s="55"/>
+      <c r="C154" s="55"/>
+      <c r="D154" s="55"/>
+      <c r="E154" s="55"/>
+      <c r="F154" s="55"/>
+      <c r="G154" s="55"/>
+      <c r="H154" s="55"/>
+      <c r="I154" s="55"/>
+      <c r="J154" s="55"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="K151" s="24" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D152" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="E152" s="73"/>
-      <c r="F152" s="74"/>
-      <c r="G152" s="75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I152" s="7" t="n">
-        <f aca="false">Narxlar!$C$63</f>
-        <v>350</v>
-      </c>
-      <c r="J152" s="76" t="n">
-        <f aca="false">G152*I152</f>
-        <v>350</v>
-      </c>
-      <c r="K152" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="5" t="n">
+      <c r="B155" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E155" s="73" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F155" s="56" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>2.5</v>
+      </c>
+      <c r="G155" s="74" t="n">
+        <f aca="false">E155*F155</f>
+        <v>0.375</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I155" s="7" t="n">
+        <f aca="false">Narxlar!$C$5</f>
+        <v>55</v>
+      </c>
+      <c r="J155" s="76" t="n">
+        <f aca="false">G155*I155</f>
+        <v>20.625</v>
+      </c>
+      <c r="K155" s="24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="B153" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="E153" s="73"/>
-      <c r="F153" s="74"/>
-      <c r="G153" s="75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="I153" s="7" t="n">
-        <f aca="false">Narxlar!$C$66</f>
-        <v>300</v>
-      </c>
-      <c r="J153" s="76" t="n">
-        <f aca="false">G153*I153</f>
-        <v>300</v>
-      </c>
-      <c r="K153" s="24" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="77"/>
-      <c r="B154" s="77"/>
-      <c r="C154" s="77"/>
-      <c r="D154" s="11" t="s">
-        <v>440</v>
-      </c>
-      <c r="E154" s="77"/>
-      <c r="F154" s="77"/>
-      <c r="G154" s="77"/>
-      <c r="H154" s="77"/>
-      <c r="I154" s="77"/>
-      <c r="J154" s="12" t="n">
-        <f aca="false">SUM(J137:J153)</f>
-        <v>3236.95</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="54" t="s">
+      <c r="B156" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="B156" s="55"/>
-      <c r="C156" s="55"/>
-      <c r="D156" s="55"/>
-      <c r="E156" s="55"/>
-      <c r="F156" s="55"/>
-      <c r="G156" s="55"/>
-      <c r="H156" s="55"/>
-      <c r="I156" s="55"/>
-      <c r="J156" s="55"/>
+      <c r="C156" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E156" s="73" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F156" s="56" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>2.5</v>
+      </c>
+      <c r="G156" s="74" t="n">
+        <f aca="false">E156*F156</f>
+        <v>11.875</v>
+      </c>
+      <c r="H156" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I156" s="7" t="n">
+        <f aca="false">Narxlar!$C$5</f>
+        <v>55</v>
+      </c>
+      <c r="J156" s="76" t="n">
+        <f aca="false">G156*I156</f>
+        <v>653.125</v>
+      </c>
+      <c r="K156" s="24" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="5" t="n">
@@ -17073,10 +17076,11 @@
         <v>8</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="E157" s="73" t="n">
-        <v>0.15</v>
+        <v>391</v>
+      </c>
+      <c r="E157" s="56" t="n">
+        <f aca="false">Narxlar!$C$89</f>
+        <v>0.9</v>
       </c>
       <c r="F157" s="56" t="n">
         <f aca="false">Narxlar!$C$85</f>
@@ -17084,7 +17088,7 @@
       </c>
       <c r="G157" s="74" t="n">
         <f aca="false">E157*F157</f>
-        <v>0.375</v>
+        <v>2.25</v>
       </c>
       <c r="H157" s="5" t="s">
         <v>310</v>
@@ -17095,7 +17099,7 @@
       </c>
       <c r="J157" s="76" t="n">
         <f aca="false">G157*I157</f>
-        <v>20.625</v>
+        <v>123.75</v>
       </c>
       <c r="K157" s="24" t="s">
         <v>143</v>
@@ -17109,35 +17113,35 @@
         <v>247</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>390</v>
+        <v>442</v>
       </c>
       <c r="E158" s="73" t="n">
-        <v>4.75</v>
+        <v>0.9</v>
       </c>
       <c r="F158" s="56" t="n">
-        <f aca="false">Narxlar!$C$85</f>
-        <v>2.5</v>
+        <f aca="false">Narxlar!$C$84</f>
+        <v>3.5</v>
       </c>
       <c r="G158" s="74" t="n">
         <f aca="false">E158*F158</f>
-        <v>11.875</v>
+        <v>3.15</v>
       </c>
       <c r="H158" s="5" t="s">
         <v>310</v>
       </c>
       <c r="I158" s="7" t="n">
-        <f aca="false">Narxlar!$C$5</f>
-        <v>55</v>
+        <f aca="false">Narxlar!$C$6</f>
+        <v>12</v>
       </c>
       <c r="J158" s="76" t="n">
         <f aca="false">G158*I158</f>
-        <v>653.125</v>
+        <v>37.8</v>
       </c>
       <c r="K158" s="24" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17148,36 +17152,35 @@
         <v>247</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="E159" s="56" t="n">
-        <f aca="false">Narxlar!$C$89</f>
-        <v>0.9</v>
+        <v>443</v>
+      </c>
+      <c r="E159" s="73" t="n">
+        <v>1</v>
       </c>
       <c r="F159" s="56" t="n">
-        <f aca="false">Narxlar!$C$85</f>
-        <v>2.5</v>
+        <f aca="false">Narxlar!$C$84</f>
+        <v>3.5</v>
       </c>
       <c r="G159" s="74" t="n">
         <f aca="false">E159*F159</f>
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="H159" s="5" t="s">
         <v>310</v>
       </c>
       <c r="I159" s="7" t="n">
-        <f aca="false">Narxlar!$C$5</f>
-        <v>55</v>
+        <f aca="false">Narxlar!$C$6</f>
+        <v>12</v>
       </c>
       <c r="J159" s="76" t="n">
         <f aca="false">G159*I159</f>
-        <v>123.75</v>
+        <v>42</v>
       </c>
       <c r="K159" s="24" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17191,18 +17194,18 @@
         <v>9</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>441</v>
+        <v>393</v>
       </c>
       <c r="E160" s="73" t="n">
-        <v>0.9</v>
+        <v>0.15</v>
       </c>
       <c r="F160" s="56" t="n">
-        <f aca="false">Narxlar!$C$84</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$86</f>
+        <v>1</v>
       </c>
       <c r="G160" s="74" t="n">
         <f aca="false">E160*F160</f>
-        <v>3.15</v>
+        <v>0.15</v>
       </c>
       <c r="H160" s="5" t="s">
         <v>310</v>
@@ -17213,7 +17216,7 @@
       </c>
       <c r="J160" s="76" t="n">
         <f aca="false">G160*I160</f>
-        <v>37.8</v>
+        <v>1.8</v>
       </c>
       <c r="K160" s="24" t="s">
         <v>123</v>
@@ -17230,18 +17233,18 @@
         <v>9</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>442</v>
+        <v>393</v>
       </c>
       <c r="E161" s="73" t="n">
-        <v>1</v>
+        <v>4.75</v>
       </c>
       <c r="F161" s="56" t="n">
-        <f aca="false">Narxlar!$C$84</f>
-        <v>3.5</v>
+        <f aca="false">Narxlar!$C$86</f>
+        <v>1</v>
       </c>
       <c r="G161" s="74" t="n">
         <f aca="false">E161*F161</f>
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="H161" s="5" t="s">
         <v>310</v>
@@ -17252,7 +17255,7 @@
       </c>
       <c r="J161" s="76" t="n">
         <f aca="false">G161*I161</f>
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="K161" s="24" t="s">
         <v>123</v>
@@ -17269,10 +17272,11 @@
         <v>9</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="E162" s="73" t="n">
-        <v>0.15</v>
+        <v>395</v>
+      </c>
+      <c r="E162" s="56" t="n">
+        <f aca="false">Narxlar!$C$89</f>
+        <v>0.9</v>
       </c>
       <c r="F162" s="56" t="n">
         <f aca="false">Narxlar!$C$86</f>
@@ -17280,7 +17284,7 @@
       </c>
       <c r="G162" s="74" t="n">
         <f aca="false">E162*F162</f>
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="H162" s="5" t="s">
         <v>310</v>
@@ -17291,7 +17295,7 @@
       </c>
       <c r="J162" s="76" t="n">
         <f aca="false">G162*I162</f>
-        <v>1.8</v>
+        <v>10.8</v>
       </c>
       <c r="K162" s="24" t="s">
         <v>123</v>
@@ -17305,35 +17309,35 @@
         <v>247</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>393</v>
+        <v>444</v>
       </c>
       <c r="E163" s="73" t="n">
-        <v>4.75</v>
+        <v>5.8</v>
       </c>
       <c r="F163" s="56" t="n">
-        <f aca="false">Narxlar!$C$86</f>
-        <v>1</v>
+        <f aca="false">Narxlar!$C$90</f>
+        <v>3.5</v>
       </c>
       <c r="G163" s="74" t="n">
         <f aca="false">E163*F163</f>
-        <v>4.75</v>
+        <v>20.3</v>
       </c>
       <c r="H163" s="5" t="s">
         <v>310</v>
       </c>
       <c r="I163" s="7" t="n">
-        <f aca="false">Narxlar!$C$6</f>
-        <v>12</v>
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
       </c>
       <c r="J163" s="76" t="n">
         <f aca="false">G163*I163</f>
-        <v>57</v>
+        <v>314.65</v>
       </c>
       <c r="K163" s="24" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17344,36 +17348,35 @@
         <v>247</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="E164" s="56" t="n">
-        <f aca="false">Narxlar!$C$89</f>
-        <v>0.9</v>
+        <v>445</v>
+      </c>
+      <c r="E164" s="73" t="n">
+        <v>2.8</v>
       </c>
       <c r="F164" s="56" t="n">
-        <f aca="false">Narxlar!$C$86</f>
-        <v>1</v>
+        <f aca="false">Narxlar!$C$90</f>
+        <v>3.5</v>
       </c>
       <c r="G164" s="74" t="n">
         <f aca="false">E164*F164</f>
-        <v>0.9</v>
+        <v>9.8</v>
       </c>
       <c r="H164" s="5" t="s">
         <v>310</v>
       </c>
       <c r="I164" s="7" t="n">
-        <f aca="false">Narxlar!$C$6</f>
-        <v>12</v>
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
       </c>
       <c r="J164" s="76" t="n">
         <f aca="false">G164*I164</f>
-        <v>10.8</v>
+        <v>151.9</v>
       </c>
       <c r="K164" s="24" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17384,35 +17387,29 @@
         <v>247</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="E165" s="73" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F165" s="56" t="n">
-        <f aca="false">Narxlar!$C$90</f>
-        <v>3.5</v>
-      </c>
-      <c r="G165" s="74" t="n">
-        <f aca="false">E165*F165</f>
-        <v>20.3</v>
+        <v>399</v>
+      </c>
+      <c r="E165" s="73"/>
+      <c r="F165" s="74"/>
+      <c r="G165" s="75" t="n">
+        <v>1</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>310</v>
+        <v>386</v>
       </c>
       <c r="I165" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
+        <f aca="false">Narxlar!$C$12</f>
+        <v>168</v>
       </c>
       <c r="J165" s="76" t="n">
         <f aca="false">G165*I165</f>
-        <v>314.65</v>
+        <v>168</v>
       </c>
       <c r="K165" s="24" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17423,133 +17420,139 @@
         <v>247</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="E166" s="73" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F166" s="56" t="n">
-        <f aca="false">Narxlar!$C$90</f>
-        <v>3.5</v>
-      </c>
-      <c r="G166" s="74" t="n">
-        <f aca="false">E166*F166</f>
-        <v>9.8</v>
+        <v>152</v>
+      </c>
+      <c r="E166" s="73"/>
+      <c r="F166" s="74"/>
+      <c r="G166" s="75" t="n">
+        <v>1</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="I166" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
+        <f aca="false">Narxlar!$C$57</f>
+        <v>380</v>
       </c>
       <c r="J166" s="76" t="n">
         <f aca="false">G166*I166</f>
-        <v>151.9</v>
+        <v>380</v>
       </c>
       <c r="K166" s="24" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="5" t="n">
+      <c r="A167" s="77"/>
+      <c r="B167" s="77"/>
+      <c r="C167" s="77"/>
+      <c r="D167" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="E167" s="77"/>
+      <c r="F167" s="77"/>
+      <c r="G167" s="77"/>
+      <c r="H167" s="77"/>
+      <c r="I167" s="77"/>
+      <c r="J167" s="12" t="n">
+        <f aca="false">SUM(J155:J166)</f>
+        <v>1961.45</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="54" t="s">
+        <v>248</v>
+      </c>
+      <c r="B169" s="55"/>
+      <c r="C169" s="55"/>
+      <c r="D169" s="55"/>
+      <c r="E169" s="55"/>
+      <c r="F169" s="55"/>
+      <c r="G169" s="55"/>
+      <c r="H169" s="55"/>
+      <c r="I169" s="55"/>
+      <c r="J169" s="55"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="B167" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D167" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="E167" s="73"/>
-      <c r="F167" s="74"/>
-      <c r="G167" s="75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H167" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="I167" s="7" t="n">
-        <f aca="false">Narxlar!$C$12</f>
-        <v>168</v>
-      </c>
-      <c r="J167" s="76" t="n">
-        <f aca="false">G167*I167</f>
-        <v>168</v>
-      </c>
-      <c r="K167" s="24" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="5" t="n">
+      <c r="B170" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E170" s="73" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F170" s="56" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>2.5</v>
+      </c>
+      <c r="G170" s="74" t="n">
+        <f aca="false">E170*F170</f>
+        <v>6</v>
+      </c>
+      <c r="H170" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I170" s="7" t="n">
+        <f aca="false">Narxlar!$C$5</f>
+        <v>55</v>
+      </c>
+      <c r="J170" s="76" t="n">
+        <f aca="false">G170*I170</f>
+        <v>330</v>
+      </c>
+      <c r="K170" s="24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="5" t="n">
         <v>133</v>
       </c>
-      <c r="B168" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D168" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E168" s="73"/>
-      <c r="F168" s="74"/>
-      <c r="G168" s="75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H168" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I168" s="7" t="n">
-        <f aca="false">Narxlar!$C$57</f>
-        <v>380</v>
-      </c>
-      <c r="J168" s="76" t="n">
-        <f aca="false">G168*I168</f>
-        <v>380</v>
-      </c>
-      <c r="K168" s="24" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="77"/>
-      <c r="B169" s="77"/>
-      <c r="C169" s="77"/>
-      <c r="D169" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="E169" s="77"/>
-      <c r="F169" s="77"/>
-      <c r="G169" s="77"/>
-      <c r="H169" s="77"/>
-      <c r="I169" s="77"/>
-      <c r="J169" s="12" t="n">
-        <f aca="false">SUM(J157:J168)</f>
-        <v>1961.45</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="54" t="s">
+      <c r="B171" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B171" s="55"/>
-      <c r="C171" s="55"/>
-      <c r="D171" s="55"/>
-      <c r="E171" s="55"/>
-      <c r="F171" s="55"/>
-      <c r="G171" s="55"/>
-      <c r="H171" s="55"/>
-      <c r="I171" s="55"/>
-      <c r="J171" s="55"/>
+      <c r="C171" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E171" s="73" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F171" s="56" t="n">
+        <f aca="false">Narxlar!$C$85</f>
+        <v>2.5</v>
+      </c>
+      <c r="G171" s="74" t="n">
+        <f aca="false">E171*F171</f>
+        <v>6</v>
+      </c>
+      <c r="H171" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I171" s="7" t="n">
+        <f aca="false">Narxlar!$C$5</f>
+        <v>55</v>
+      </c>
+      <c r="J171" s="76" t="n">
+        <f aca="false">G171*I171</f>
+        <v>330</v>
+      </c>
+      <c r="K171" s="24" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="5" t="n">
@@ -17562,10 +17565,11 @@
         <v>8</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="E172" s="73" t="n">
-        <v>3.1</v>
+        <v>391</v>
+      </c>
+      <c r="E172" s="56" t="n">
+        <f aca="false">Narxlar!$C$89</f>
+        <v>0.9</v>
       </c>
       <c r="F172" s="56" t="n">
         <f aca="false">Narxlar!$C$85</f>
@@ -17573,7 +17577,7 @@
       </c>
       <c r="G172" s="74" t="n">
         <f aca="false">E172*F172</f>
-        <v>7.75</v>
+        <v>2.25</v>
       </c>
       <c r="H172" s="5" t="s">
         <v>310</v>
@@ -17584,7 +17588,7 @@
       </c>
       <c r="J172" s="76" t="n">
         <f aca="false">G172*I172</f>
-        <v>426.25</v>
+        <v>123.75</v>
       </c>
       <c r="K172" s="24" t="s">
         <v>143</v>
@@ -17598,35 +17602,35 @@
         <v>248</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="E173" s="73" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="F173" s="56" t="n">
-        <f aca="false">Narxlar!$C$85</f>
-        <v>2.5</v>
+        <f aca="false">Narxlar!$C$84</f>
+        <v>3.5</v>
       </c>
       <c r="G173" s="74" t="n">
         <f aca="false">E173*F173</f>
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="H173" s="5" t="s">
         <v>310</v>
       </c>
       <c r="I173" s="7" t="n">
-        <f aca="false">Narxlar!$C$5</f>
-        <v>55</v>
+        <f aca="false">Narxlar!$C$6</f>
+        <v>12</v>
       </c>
       <c r="J173" s="76" t="n">
         <f aca="false">G173*I173</f>
-        <v>247.5</v>
+        <v>25.2</v>
       </c>
       <c r="K173" s="24" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17637,36 +17641,35 @@
         <v>248</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="E174" s="56" t="n">
-        <f aca="false">Narxlar!$C$89</f>
+        <v>405</v>
+      </c>
+      <c r="E174" s="73" t="n">
         <v>0.9</v>
       </c>
       <c r="F174" s="56" t="n">
-        <f aca="false">Narxlar!$C$85</f>
-        <v>2.5</v>
+        <f aca="false">Narxlar!$C$84</f>
+        <v>3.5</v>
       </c>
       <c r="G174" s="74" t="n">
         <f aca="false">E174*F174</f>
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="H174" s="5" t="s">
         <v>310</v>
       </c>
       <c r="I174" s="7" t="n">
-        <f aca="false">Narxlar!$C$5</f>
-        <v>55</v>
+        <f aca="false">Narxlar!$C$6</f>
+        <v>12</v>
       </c>
       <c r="J174" s="76" t="n">
         <f aca="false">G174*I174</f>
-        <v>123.75</v>
+        <v>37.8</v>
       </c>
       <c r="K174" s="24" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17680,10 +17683,10 @@
         <v>9</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>422</v>
+        <v>393</v>
       </c>
       <c r="E175" s="73" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="F175" s="56" t="n">
         <f aca="false">Narxlar!$C$86</f>
@@ -17691,7 +17694,7 @@
       </c>
       <c r="G175" s="74" t="n">
         <f aca="false">E175*F175</f>
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="H175" s="5" t="s">
         <v>310</v>
@@ -17702,7 +17705,7 @@
       </c>
       <c r="J175" s="76" t="n">
         <f aca="false">G175*I175</f>
-        <v>37.2</v>
+        <v>28.8</v>
       </c>
       <c r="K175" s="24" t="s">
         <v>123</v>
@@ -17719,10 +17722,10 @@
         <v>9</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>422</v>
+        <v>393</v>
       </c>
       <c r="E176" s="73" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="F176" s="56" t="n">
         <f aca="false">Narxlar!$C$86</f>
@@ -17730,7 +17733,7 @@
       </c>
       <c r="G176" s="74" t="n">
         <f aca="false">E176*F176</f>
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="H176" s="5" t="s">
         <v>310</v>
@@ -17741,7 +17744,7 @@
       </c>
       <c r="J176" s="76" t="n">
         <f aca="false">G176*I176</f>
-        <v>21.6</v>
+        <v>28.8</v>
       </c>
       <c r="K176" s="24" t="s">
         <v>123</v>
@@ -17758,7 +17761,7 @@
         <v>9</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="E177" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -17798,10 +17801,10 @@
         <v>10</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E178" s="73" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F178" s="56" t="n">
         <f aca="false">Narxlar!$C$90</f>
@@ -17809,7 +17812,7 @@
       </c>
       <c r="G178" s="74" t="n">
         <f aca="false">E178*F178</f>
-        <v>20.3</v>
+        <v>19.95</v>
       </c>
       <c r="H178" s="5" t="s">
         <v>310</v>
@@ -17820,7 +17823,7 @@
       </c>
       <c r="J178" s="76" t="n">
         <f aca="false">G178*I178</f>
-        <v>314.65</v>
+        <v>309.225</v>
       </c>
       <c r="K178" s="24" t="s">
         <v>144</v>
@@ -17837,10 +17840,10 @@
         <v>10</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>447</v>
+        <v>426</v>
       </c>
       <c r="E179" s="73" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="F179" s="56" t="n">
         <f aca="false">Narxlar!$C$90</f>
@@ -17848,7 +17851,7 @@
       </c>
       <c r="G179" s="74" t="n">
         <f aca="false">E179*F179</f>
-        <v>9.1</v>
+        <v>9.8</v>
       </c>
       <c r="H179" s="5" t="s">
         <v>310</v>
@@ -17859,7 +17862,7 @@
       </c>
       <c r="J179" s="76" t="n">
         <f aca="false">G179*I179</f>
-        <v>141.05</v>
+        <v>151.9</v>
       </c>
       <c r="K179" s="24" t="s">
         <v>144</v>
@@ -17944,8 +17947,8 @@
       <c r="H182" s="77"/>
       <c r="I182" s="77"/>
       <c r="J182" s="12" t="n">
-        <f aca="false">SUM(J172:J181)</f>
-        <v>1870.8</v>
+        <f aca="false">SUM(J170:J181)</f>
+        <v>1924.275</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18623,7 +18626,7 @@
         <v>9</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>461</v>
+        <v>436</v>
       </c>
       <c r="E204" s="73" t="n">
         <v>1.15</v>
@@ -18662,7 +18665,7 @@
         <v>9</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E205" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -18702,7 +18705,7 @@
         <v>9</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E206" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -18742,7 +18745,7 @@
         <v>9</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E207" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -18782,7 +18785,7 @@
         <v>9</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E208" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -18822,7 +18825,7 @@
         <v>9</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E209" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -18862,7 +18865,7 @@
         <v>13</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E210" s="73"/>
       <c r="F210" s="74"/>
@@ -18889,7 +18892,7 @@
       <c r="B211" s="77"/>
       <c r="C211" s="77"/>
       <c r="D211" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E211" s="77"/>
       <c r="F211" s="77"/>
@@ -18926,7 +18929,7 @@
         <v>9</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E214" s="73" t="n">
         <v>2.4</v>
@@ -18965,7 +18968,7 @@
         <v>9</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E215" s="73" t="n">
         <v>2.4</v>
@@ -19043,10 +19046,10 @@
         <v>9</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E217" s="73" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="F217" s="56" t="n">
         <f aca="false">Narxlar!$C$86</f>
@@ -19054,7 +19057,7 @@
       </c>
       <c r="G217" s="74" t="n">
         <f aca="false">E217*F217</f>
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="H217" s="5" t="s">
         <v>310</v>
@@ -19065,7 +19068,7 @@
       </c>
       <c r="J217" s="76" t="n">
         <f aca="false">G217*I217</f>
-        <v>37.2</v>
+        <v>29.4</v>
       </c>
       <c r="K217" s="24" t="s">
         <v>123</v>
@@ -19082,10 +19085,10 @@
         <v>9</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E218" s="73" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="F218" s="56" t="n">
         <f aca="false">Narxlar!$C$86</f>
@@ -19093,7 +19096,7 @@
       </c>
       <c r="G218" s="74" t="n">
         <f aca="false">E218*F218</f>
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="H218" s="5" t="s">
         <v>310</v>
@@ -19104,7 +19107,7 @@
       </c>
       <c r="J218" s="76" t="n">
         <f aca="false">G218*I218</f>
-        <v>21.6</v>
+        <v>29.4</v>
       </c>
       <c r="K218" s="24" t="s">
         <v>123</v>
@@ -19121,7 +19124,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E219" s="73" t="n">
         <v>0.3</v>
@@ -19160,7 +19163,7 @@
         <v>9</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E220" s="73" t="n">
         <v>0.15</v>
@@ -19238,7 +19241,7 @@
         <v>9</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E222" s="73" t="n">
         <v>0.2</v>
@@ -19277,7 +19280,7 @@
         <v>9</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E223" s="73" t="n">
         <v>4.7</v>
@@ -19316,7 +19319,7 @@
         <v>9</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E224" s="73" t="n">
         <v>0.4</v>
@@ -19355,7 +19358,7 @@
         <v>9</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E225" s="73" t="n">
         <v>4.7</v>
@@ -19394,7 +19397,7 @@
         <v>9</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E226" s="73" t="n">
         <v>0.35</v>
@@ -19433,7 +19436,7 @@
         <v>9</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E227" s="73" t="n">
         <v>0.1</v>
@@ -19472,7 +19475,7 @@
         <v>9</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E228" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -19512,7 +19515,7 @@
         <v>9</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E229" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -19552,7 +19555,7 @@
         <v>9</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E230" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -19592,7 +19595,7 @@
         <v>9</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E231" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -19632,7 +19635,7 @@
         <v>9</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E232" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -19672,7 +19675,7 @@
         <v>9</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E233" s="56" t="n">
         <f aca="false">Narxlar!$C$89</f>
@@ -19712,7 +19715,7 @@
         <v>13</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E234" s="73"/>
       <c r="F234" s="74"/>
@@ -19739,7 +19742,7 @@
       <c r="B235" s="77"/>
       <c r="C235" s="77"/>
       <c r="D235" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E235" s="77"/>
       <c r="F235" s="77"/>
@@ -19776,7 +19779,7 @@
         <v>9</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E238" s="73" t="n">
         <v>0.4</v>
@@ -19815,7 +19818,7 @@
         <v>9</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E239" s="73" t="n">
         <v>0.7</v>
@@ -19893,7 +19896,7 @@
         <v>13</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E241" s="73"/>
       <c r="F241" s="74"/>
@@ -19926,7 +19929,7 @@
         <v>22</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E242" s="73"/>
       <c r="F242" s="74"/>
@@ -19959,7 +19962,7 @@
         <v>22</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E243" s="73"/>
       <c r="F243" s="74"/>
@@ -19992,7 +19995,7 @@
         <v>22</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E244" s="73"/>
       <c r="F244" s="74"/>
@@ -20025,7 +20028,7 @@
         <v>22</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E245" s="73"/>
       <c r="F245" s="74"/>
@@ -20058,7 +20061,7 @@
         <v>22</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E246" s="73"/>
       <c r="F246" s="74"/>
@@ -20091,7 +20094,7 @@
         <v>22</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E247" s="73"/>
       <c r="F247" s="74"/>
@@ -20124,7 +20127,7 @@
         <v>22</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E248" s="73"/>
       <c r="F248" s="74"/>
@@ -20157,7 +20160,7 @@
         <v>22</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E249" s="73"/>
       <c r="F249" s="74"/>
@@ -20190,7 +20193,7 @@
         <v>22</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E250" s="73"/>
       <c r="F250" s="74"/>
@@ -20223,7 +20226,7 @@
         <v>23</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E251" s="73"/>
       <c r="F251" s="74"/>
@@ -20256,7 +20259,7 @@
         <v>23</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E252" s="73"/>
       <c r="F252" s="74"/>
@@ -20283,7 +20286,7 @@
       <c r="B253" s="77"/>
       <c r="C253" s="77"/>
       <c r="D253" s="11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E253" s="77"/>
       <c r="F253" s="77"/>
@@ -20353,7 +20356,7 @@
       <c r="B257" s="77"/>
       <c r="C257" s="77"/>
       <c r="D257" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E257" s="77"/>
       <c r="F257" s="77"/>
@@ -20390,7 +20393,7 @@
         <v>12</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E260" s="56" t="n">
         <f aca="false">Narxlar!$C$10</f>
@@ -20417,69 +20420,71 @@
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="77"/>
-      <c r="B261" s="77"/>
-      <c r="C261" s="77"/>
-      <c r="D261" s="11" t="s">
+      <c r="A261" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D261" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="E261" s="73" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F261" s="74"/>
+      <c r="G261" s="74" t="n">
+        <f aca="false">E261</f>
+        <v>3.65</v>
+      </c>
+      <c r="H261" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="I261" s="7" t="n">
+        <f aca="false">Narxlar!$C$9</f>
+        <v>84</v>
+      </c>
+      <c r="J261" s="76" t="n">
+        <f aca="false">G261*I261</f>
+        <v>306.6</v>
+      </c>
+      <c r="K261" s="24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="77"/>
+      <c r="B262" s="77"/>
+      <c r="C262" s="77"/>
+      <c r="D262" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="E261" s="77"/>
-      <c r="F261" s="77"/>
-      <c r="G261" s="77"/>
-      <c r="H261" s="77"/>
-      <c r="I261" s="77"/>
-      <c r="J261" s="12" t="n">
-        <f aca="false">SUM(J260:J260)</f>
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="54" t="s">
+      <c r="E262" s="77"/>
+      <c r="F262" s="77"/>
+      <c r="G262" s="77"/>
+      <c r="H262" s="77"/>
+      <c r="I262" s="77"/>
+      <c r="J262" s="12" t="n">
+        <f aca="false">SUM(J260:J261)</f>
+        <v>2322.6</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="54" t="s">
         <v>256</v>
       </c>
-      <c r="B263" s="55"/>
-      <c r="C263" s="55"/>
-      <c r="D263" s="55"/>
-      <c r="E263" s="55"/>
-      <c r="F263" s="55"/>
-      <c r="G263" s="55"/>
-      <c r="H263" s="55"/>
-      <c r="I263" s="55"/>
-      <c r="J263" s="55"/>
-    </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="5" t="n">
-        <v>205</v>
-      </c>
-      <c r="B264" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="C264" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D264" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E264" s="73"/>
-      <c r="F264" s="74"/>
-      <c r="G264" s="57" t="n">
-        <f aca="false">Narxlar!$C$14</f>
-        <v>16</v>
-      </c>
-      <c r="H264" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I264" s="7" t="n">
-        <f aca="false">Narxlar!$C$13</f>
-        <v>40</v>
-      </c>
-      <c r="J264" s="76" t="n">
-        <f aca="false">G264*I264</f>
-        <v>640</v>
-      </c>
-      <c r="K264" s="24" t="s">
-        <v>163</v>
-      </c>
+      <c r="B264" s="55"/>
+      <c r="C264" s="55"/>
+      <c r="D264" s="55"/>
+      <c r="E264" s="55"/>
+      <c r="F264" s="55"/>
+      <c r="G264" s="55"/>
+      <c r="H264" s="55"/>
+      <c r="I264" s="55"/>
+      <c r="J264" s="55"/>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="5" t="n">
@@ -20492,7 +20497,7 @@
         <v>14</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>500</v>
+        <v>164</v>
       </c>
       <c r="E265" s="73"/>
       <c r="F265" s="74"/>
@@ -20504,15 +20509,15 @@
         <v>283</v>
       </c>
       <c r="I265" s="7" t="n">
-        <f aca="false">Narxlar!$C$15</f>
-        <v>21</v>
+        <f aca="false">Narxlar!$C$13</f>
+        <v>40</v>
       </c>
       <c r="J265" s="76" t="n">
         <f aca="false">G265*I265</f>
-        <v>336</v>
+        <v>640</v>
       </c>
       <c r="K265" s="24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20526,26 +20531,27 @@
         <v>14</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>168</v>
+        <v>500</v>
       </c>
       <c r="E266" s="73"/>
       <c r="F266" s="74"/>
-      <c r="G266" s="75" t="n">
-        <v>1</v>
+      <c r="G266" s="57" t="n">
+        <f aca="false">Narxlar!$C$14</f>
+        <v>16</v>
       </c>
       <c r="H266" s="5" t="s">
         <v>283</v>
       </c>
       <c r="I266" s="7" t="n">
-        <f aca="false">Narxlar!$C$16</f>
-        <v>840</v>
+        <f aca="false">Narxlar!$C$15</f>
+        <v>21</v>
       </c>
       <c r="J266" s="76" t="n">
         <f aca="false">G266*I266</f>
-        <v>840</v>
+        <v>336</v>
       </c>
       <c r="K266" s="24" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20559,7 +20565,7 @@
         <v>14</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>501</v>
+        <v>168</v>
       </c>
       <c r="E267" s="73"/>
       <c r="F267" s="74"/>
@@ -20567,18 +20573,18 @@
         <v>1</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>386</v>
+        <v>283</v>
       </c>
       <c r="I267" s="7" t="n">
-        <f aca="false">Narxlar!$C$17</f>
-        <v>303</v>
+        <f aca="false">Narxlar!$C$16</f>
+        <v>840</v>
       </c>
       <c r="J267" s="76" t="n">
         <f aca="false">G267*I267</f>
-        <v>303</v>
+        <v>840</v>
       </c>
       <c r="K267" s="24" t="s">
-        <v>125</v>
+        <v>167</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20589,10 +20595,10 @@
         <v>256</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E268" s="73"/>
       <c r="F268" s="74"/>
@@ -20603,15 +20609,15 @@
         <v>386</v>
       </c>
       <c r="I268" s="7" t="n">
-        <f aca="false">Narxlar!$C$18</f>
-        <v>2500</v>
+        <f aca="false">Narxlar!$C$17</f>
+        <v>303</v>
       </c>
       <c r="J268" s="76" t="n">
         <f aca="false">G268*I268</f>
-        <v>2500</v>
+        <v>303</v>
       </c>
       <c r="K268" s="24" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20622,30 +20628,29 @@
         <v>256</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E269" s="73"/>
       <c r="F269" s="74"/>
-      <c r="G269" s="57" t="n">
-        <f aca="false">Narxlar!$C$21</f>
-        <v>8</v>
+      <c r="G269" s="75" t="n">
+        <v>1</v>
       </c>
       <c r="H269" s="5" t="s">
-        <v>283</v>
+        <v>386</v>
       </c>
       <c r="I269" s="7" t="n">
-        <f aca="false">Narxlar!$C$20/Narxlar!$C$19</f>
-        <v>67.2268907563025</v>
+        <f aca="false">Narxlar!$C$18</f>
+        <v>2500</v>
       </c>
       <c r="J269" s="76" t="n">
         <f aca="false">G269*I269</f>
-        <v>537.81512605042</v>
+        <v>2500</v>
       </c>
       <c r="K269" s="24" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20656,29 +20661,30 @@
         <v>256</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E270" s="73"/>
       <c r="F270" s="74"/>
-      <c r="G270" s="75" t="n">
-        <v>1</v>
+      <c r="G270" s="57" t="n">
+        <f aca="false">Narxlar!$C$21</f>
+        <v>8</v>
       </c>
       <c r="H270" s="5" t="s">
-        <v>386</v>
+        <v>283</v>
       </c>
       <c r="I270" s="7" t="n">
-        <f aca="false">Narxlar!$C$22/Narxlar!$C$19</f>
-        <v>1512.60504201681</v>
+        <f aca="false">Narxlar!$C$20/Narxlar!$C$19</f>
+        <v>67.2268907563025</v>
       </c>
       <c r="J270" s="76" t="n">
         <f aca="false">G270*I270</f>
-        <v>1512.60504201681</v>
+        <v>537.81512605042</v>
       </c>
       <c r="K270" s="24" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20689,35 +20695,29 @@
         <v>256</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="E271" s="73" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F271" s="56" t="n">
-        <f aca="false">Narxlar!$C$84</f>
-        <v>3.5</v>
-      </c>
-      <c r="G271" s="74" t="n">
-        <f aca="false">E271*F271</f>
-        <v>3.85</v>
+        <v>504</v>
+      </c>
+      <c r="E271" s="73"/>
+      <c r="F271" s="74"/>
+      <c r="G271" s="75" t="n">
+        <v>1</v>
       </c>
       <c r="H271" s="5" t="s">
-        <v>310</v>
+        <v>386</v>
       </c>
       <c r="I271" s="7" t="n">
-        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
-        <v>4.20168067226891</v>
+        <f aca="false">Narxlar!$C$22/Narxlar!$C$19</f>
+        <v>1512.60504201681</v>
       </c>
       <c r="J271" s="76" t="n">
         <f aca="false">G271*I271</f>
-        <v>16.1764705882353</v>
+        <v>1512.60504201681</v>
       </c>
       <c r="K271" s="24" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20731,10 +20731,10 @@
         <v>18</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E272" s="73" t="n">
-        <v>0.75</v>
+        <v>3.65</v>
       </c>
       <c r="F272" s="56" t="n">
         <f aca="false">Narxlar!$C$84</f>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="G272" s="74" t="n">
         <f aca="false">E272*F272</f>
-        <v>2.625</v>
+        <v>12.775</v>
       </c>
       <c r="H272" s="5" t="s">
         <v>310</v>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="J272" s="76" t="n">
         <f aca="false">G272*I272</f>
-        <v>11.0294117647059</v>
+        <v>53.6764705882353</v>
       </c>
       <c r="K272" s="24" t="s">
         <v>119</v>
@@ -20773,7 +20773,7 @@
         <v>506</v>
       </c>
       <c r="E273" s="73" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="F273" s="56" t="n">
         <f aca="false">Narxlar!$C$84</f>
@@ -20781,7 +20781,7 @@
       </c>
       <c r="G273" s="74" t="n">
         <f aca="false">E273*F273</f>
-        <v>11.9</v>
+        <v>3.85</v>
       </c>
       <c r="H273" s="5" t="s">
         <v>310</v>
@@ -20792,7 +20792,7 @@
       </c>
       <c r="J273" s="76" t="n">
         <f aca="false">G273*I273</f>
-        <v>50</v>
+        <v>16.1764705882353</v>
       </c>
       <c r="K273" s="24" t="s">
         <v>119</v>
@@ -20812,7 +20812,7 @@
         <v>507</v>
       </c>
       <c r="E274" s="73" t="n">
-        <v>4.2</v>
+        <v>0.75</v>
       </c>
       <c r="F274" s="56" t="n">
         <f aca="false">Narxlar!$C$84</f>
@@ -20820,7 +20820,7 @@
       </c>
       <c r="G274" s="74" t="n">
         <f aca="false">E274*F274</f>
-        <v>14.7</v>
+        <v>2.625</v>
       </c>
       <c r="H274" s="5" t="s">
         <v>310</v>
@@ -20831,7 +20831,7 @@
       </c>
       <c r="J274" s="76" t="n">
         <f aca="false">G274*I274</f>
-        <v>61.764705882353</v>
+        <v>11.0294117647059</v>
       </c>
       <c r="K274" s="24" t="s">
         <v>119</v>
@@ -20848,10 +20848,10 @@
         <v>18</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E275" s="73" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="F275" s="56" t="n">
         <f aca="false">Narxlar!$C$84</f>
@@ -20859,7 +20859,7 @@
       </c>
       <c r="G275" s="74" t="n">
         <f aca="false">E275*F275</f>
-        <v>5.25</v>
+        <v>11.9</v>
       </c>
       <c r="H275" s="5" t="s">
         <v>310</v>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="J275" s="76" t="n">
         <f aca="false">G275*I275</f>
-        <v>22.0588235294118</v>
+        <v>50</v>
       </c>
       <c r="K275" s="24" t="s">
         <v>119</v>
@@ -20890,7 +20890,7 @@
         <v>508</v>
       </c>
       <c r="E276" s="73" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="F276" s="56" t="n">
         <f aca="false">Narxlar!$C$84</f>
@@ -20898,7 +20898,7 @@
       </c>
       <c r="G276" s="74" t="n">
         <f aca="false">E276*F276</f>
-        <v>0.7</v>
+        <v>14.7</v>
       </c>
       <c r="H276" s="5" t="s">
         <v>310</v>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="J276" s="76" t="n">
         <f aca="false">G276*I276</f>
-        <v>2.94117647058824</v>
+        <v>61.764705882353</v>
       </c>
       <c r="K276" s="24" t="s">
         <v>119</v>
@@ -20926,7 +20926,7 @@
         <v>18</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E277" s="73" t="n">
         <v>1.5</v>
@@ -20967,24 +20967,30 @@
       <c r="D278" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="E278" s="73"/>
-      <c r="F278" s="74"/>
-      <c r="G278" s="75" t="n">
-        <v>1</v>
+      <c r="E278" s="73" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F278" s="56" t="n">
+        <f aca="false">Narxlar!$C$84</f>
+        <v>3.5</v>
+      </c>
+      <c r="G278" s="74" t="n">
+        <f aca="false">E278*F278</f>
+        <v>0.7</v>
       </c>
       <c r="H278" s="5" t="s">
-        <v>386</v>
+        <v>310</v>
       </c>
       <c r="I278" s="7" t="n">
-        <f aca="false">Narxlar!$C$24/Narxlar!$C$19</f>
-        <v>100.840336134454</v>
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
       </c>
       <c r="J278" s="76" t="n">
         <f aca="false">G278*I278</f>
-        <v>100.840336134454</v>
+        <v>2.94117647058824</v>
       </c>
       <c r="K278" s="24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20995,30 +21001,35 @@
         <v>256</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="E279" s="73"/>
-      <c r="F279" s="74"/>
-      <c r="G279" s="57" t="n">
-        <f aca="false">Narxlar!$C$53</f>
-        <v>2</v>
+        <v>506</v>
+      </c>
+      <c r="E279" s="73" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F279" s="56" t="n">
+        <f aca="false">Narxlar!$C$84</f>
+        <v>3.5</v>
+      </c>
+      <c r="G279" s="74" t="n">
+        <f aca="false">E279*F279</f>
+        <v>5.25</v>
       </c>
       <c r="H279" s="5" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="I279" s="7" t="n">
-        <f aca="false">Narxlar!$C$52/Narxlar!$C$19</f>
-        <v>2352.94117647059</v>
+        <f aca="false">Narxlar!$C$23/Narxlar!$C$19</f>
+        <v>4.20168067226891</v>
       </c>
       <c r="J279" s="76" t="n">
         <f aca="false">G279*I279</f>
-        <v>4705.88235294118</v>
+        <v>22.0588235294118</v>
       </c>
       <c r="K279" s="24" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21029,140 +21040,129 @@
         <v>256</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E280" s="73"/>
       <c r="F280" s="74"/>
-      <c r="G280" s="56" t="n">
+      <c r="G280" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H280" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="I280" s="7" t="n">
+        <f aca="false">Narxlar!$C$24/Narxlar!$C$19</f>
+        <v>100.840336134454</v>
+      </c>
+      <c r="J280" s="76" t="n">
+        <f aca="false">G280*I280</f>
+        <v>100.840336134454</v>
+      </c>
+      <c r="K280" s="24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D281" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="E281" s="73"/>
+      <c r="F281" s="74"/>
+      <c r="G281" s="57" t="n">
+        <f aca="false">Narxlar!$C$53</f>
+        <v>2</v>
+      </c>
+      <c r="H281" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="I281" s="7" t="n">
+        <f aca="false">Narxlar!$C$52/Narxlar!$C$19</f>
+        <v>2352.94117647059</v>
+      </c>
+      <c r="J281" s="76" t="n">
+        <f aca="false">G281*I281</f>
+        <v>4705.88235294118</v>
+      </c>
+      <c r="K281" s="24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D282" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="E282" s="73"/>
+      <c r="F282" s="74"/>
+      <c r="G282" s="56" t="n">
         <f aca="false">Narxlar!$C$55</f>
-        <v>217</v>
-      </c>
-      <c r="H280" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="H282" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="I280" s="7" t="n">
+      <c r="I282" s="7" t="n">
         <f aca="false">Narxlar!$C$54/Narxlar!$C$19</f>
         <v>25.2100840336134</v>
       </c>
-      <c r="J280" s="76" t="n">
-        <f aca="false">G280*I280</f>
-        <v>5470.58823529412</v>
-      </c>
-      <c r="K280" s="24" t="s">
+      <c r="J282" s="76" t="n">
+        <f aca="false">G282*I282</f>
+        <v>5319.32773109244</v>
+      </c>
+      <c r="K282" s="24" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="77"/>
-      <c r="B281" s="77"/>
-      <c r="C281" s="77"/>
-      <c r="D281" s="11" t="s">
-        <v>512</v>
-      </c>
-      <c r="E281" s="77"/>
-      <c r="F281" s="77"/>
-      <c r="G281" s="77"/>
-      <c r="H281" s="77"/>
-      <c r="I281" s="77"/>
-      <c r="J281" s="12" t="n">
-        <f aca="false">SUM(J264:J280)</f>
-        <v>17132.7605042017</v>
-      </c>
-    </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="54" t="s">
+      <c r="A283" s="77"/>
+      <c r="B283" s="77"/>
+      <c r="C283" s="77"/>
+      <c r="D283" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="E283" s="77"/>
+      <c r="F283" s="77"/>
+      <c r="G283" s="77"/>
+      <c r="H283" s="77"/>
+      <c r="I283" s="77"/>
+      <c r="J283" s="12" t="n">
+        <f aca="false">SUM(J265:J282)</f>
+        <v>17035.1764705882</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="54" t="s">
         <v>258</v>
       </c>
-      <c r="B283" s="55"/>
-      <c r="C283" s="55"/>
-      <c r="D283" s="55"/>
-      <c r="E283" s="55"/>
-      <c r="F283" s="55"/>
-      <c r="G283" s="55"/>
-      <c r="H283" s="55"/>
-      <c r="I283" s="55"/>
-      <c r="J283" s="55"/>
-    </row>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="5" t="n">
-        <v>222</v>
-      </c>
-      <c r="B284" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C284" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D284" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="E284" s="73" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="F284" s="56" t="n">
-        <f aca="false">Narxlar!$C$91</f>
-        <v>2.5</v>
-      </c>
-      <c r="G284" s="74" t="n">
-        <f aca="false">E284*F284</f>
-        <v>13.625</v>
-      </c>
-      <c r="H284" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="I284" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
-      </c>
-      <c r="J284" s="76" t="n">
-        <f aca="false">G284*I284</f>
-        <v>211.1875</v>
-      </c>
-      <c r="K284" s="24" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="5" t="n">
-        <v>223</v>
-      </c>
-      <c r="B285" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C285" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D285" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="E285" s="73" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="F285" s="56" t="n">
-        <f aca="false">Narxlar!$C$91</f>
-        <v>2.5</v>
-      </c>
-      <c r="G285" s="74" t="n">
-        <f aca="false">E285*F285</f>
-        <v>13.625</v>
-      </c>
-      <c r="H285" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="I285" s="7" t="n">
-        <f aca="false">Narxlar!$C$7</f>
-        <v>15.5</v>
-      </c>
-      <c r="J285" s="76" t="n">
-        <f aca="false">G285*I285</f>
-        <v>211.1875</v>
-      </c>
-      <c r="K285" s="24" t="s">
-        <v>144</v>
-      </c>
+      <c r="B285" s="55"/>
+      <c r="C285" s="55"/>
+      <c r="D285" s="55"/>
+      <c r="E285" s="55"/>
+      <c r="F285" s="55"/>
+      <c r="G285" s="55"/>
+      <c r="H285" s="55"/>
+      <c r="I285" s="55"/>
+      <c r="J285" s="55"/>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="5" t="n">
@@ -21175,10 +21175,10 @@
         <v>10</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E286" s="73" t="n">
-        <v>8.6</v>
+        <v>5.45</v>
       </c>
       <c r="F286" s="56" t="n">
         <f aca="false">Narxlar!$C$91</f>
@@ -21186,7 +21186,7 @@
       </c>
       <c r="G286" s="74" t="n">
         <f aca="false">E286*F286</f>
-        <v>21.5</v>
+        <v>13.625</v>
       </c>
       <c r="H286" s="5" t="s">
         <v>310</v>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="J286" s="76" t="n">
         <f aca="false">G286*I286</f>
-        <v>333.25</v>
+        <v>211.1875</v>
       </c>
       <c r="K286" s="24" t="s">
         <v>144</v>
@@ -21214,19 +21214,18 @@
         <v>10</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="E287" s="56" t="n">
-        <f aca="false">Narxlar!$C$89</f>
-        <v>0.9</v>
+        <v>515</v>
+      </c>
+      <c r="E287" s="73" t="n">
+        <v>5.45</v>
       </c>
       <c r="F287" s="56" t="n">
-        <f aca="false">Narxlar!$C$87</f>
-        <v>2.1</v>
+        <f aca="false">Narxlar!$C$91</f>
+        <v>2.5</v>
       </c>
       <c r="G287" s="74" t="n">
-        <f aca="false">-E287*F287</f>
-        <v>-1.89</v>
+        <f aca="false">E287*F287</f>
+        <v>13.625</v>
       </c>
       <c r="H287" s="5" t="s">
         <v>310</v>
@@ -21237,7 +21236,7 @@
       </c>
       <c r="J287" s="76" t="n">
         <f aca="false">G287*I287</f>
-        <v>-29.295</v>
+        <v>211.1875</v>
       </c>
       <c r="K287" s="24" t="s">
         <v>144</v>
@@ -21251,29 +21250,35 @@
         <v>258</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D288" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="E288" s="73"/>
-      <c r="F288" s="74"/>
-      <c r="G288" s="75" t="n">
-        <v>1</v>
+      <c r="E288" s="73" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F288" s="56" t="n">
+        <f aca="false">Narxlar!$C$91</f>
+        <v>2.5</v>
+      </c>
+      <c r="G288" s="74" t="n">
+        <f aca="false">E288*F288</f>
+        <v>21.5</v>
       </c>
       <c r="H288" s="5" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="I288" s="7" t="n">
-        <f aca="false">Narxlar!$C$8</f>
-        <v>1032</v>
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
       </c>
       <c r="J288" s="76" t="n">
         <f aca="false">G288*I288</f>
-        <v>1032</v>
+        <v>333.25</v>
       </c>
       <c r="K288" s="24" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21284,129 +21289,134 @@
         <v>258</v>
       </c>
       <c r="C289" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="E289" s="56" t="n">
+        <f aca="false">Narxlar!$C$89</f>
+        <v>0.9</v>
+      </c>
+      <c r="F289" s="56" t="n">
+        <f aca="false">Narxlar!$C$87</f>
+        <v>2.1</v>
+      </c>
+      <c r="G289" s="74" t="n">
+        <f aca="false">-E289*F289</f>
+        <v>-1.89</v>
+      </c>
+      <c r="H289" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I289" s="7" t="n">
+        <f aca="false">Narxlar!$C$7</f>
+        <v>15.5</v>
+      </c>
+      <c r="J289" s="76" t="n">
+        <f aca="false">G289*I289</f>
+        <v>-29.295</v>
+      </c>
+      <c r="K289" s="24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="E290" s="73"/>
+      <c r="F290" s="74"/>
+      <c r="G290" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H290" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="I290" s="7" t="n">
+        <f aca="false">Narxlar!$C$8</f>
+        <v>1032</v>
+      </c>
+      <c r="J290" s="76" t="n">
+        <f aca="false">G290*I290</f>
+        <v>1032</v>
+      </c>
+      <c r="K290" s="24" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C291" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D289" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="E289" s="73"/>
-      <c r="F289" s="74"/>
-      <c r="G289" s="75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H289" s="5" t="s">
+      <c r="D291" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="E291" s="73"/>
+      <c r="F291" s="74"/>
+      <c r="G291" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H291" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="I289" s="7" t="n">
+      <c r="I291" s="7" t="n">
         <f aca="false">Narxlar!$C$58</f>
         <v>1000</v>
       </c>
-      <c r="J289" s="76" t="n">
-        <f aca="false">G289*I289</f>
+      <c r="J291" s="76" t="n">
+        <f aca="false">G291*I291</f>
         <v>1000</v>
       </c>
-      <c r="K289" s="24" t="s">
+      <c r="K291" s="24" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="77"/>
-      <c r="B290" s="77"/>
-      <c r="C290" s="77"/>
-      <c r="D290" s="11" t="s">
-        <v>518</v>
-      </c>
-      <c r="E290" s="77"/>
-      <c r="F290" s="77"/>
-      <c r="G290" s="77"/>
-      <c r="H290" s="77"/>
-      <c r="I290" s="77"/>
-      <c r="J290" s="12" t="n">
-        <f aca="false">SUM(J284:J289)</f>
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="77"/>
+      <c r="B292" s="77"/>
+      <c r="C292" s="77"/>
+      <c r="D292" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="E292" s="77"/>
+      <c r="F292" s="77"/>
+      <c r="G292" s="77"/>
+      <c r="H292" s="77"/>
+      <c r="I292" s="77"/>
+      <c r="J292" s="12" t="n">
+        <f aca="false">SUM(J286:J291)</f>
         <v>2758.33</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="54" t="s">
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="54" t="s">
         <v>259</v>
       </c>
-      <c r="B292" s="55"/>
-      <c r="C292" s="55"/>
-      <c r="D292" s="55"/>
-      <c r="E292" s="55"/>
-      <c r="F292" s="55"/>
-      <c r="G292" s="55"/>
-      <c r="H292" s="55"/>
-      <c r="I292" s="55"/>
-      <c r="J292" s="55"/>
-    </row>
-    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="5" t="n">
-        <v>228</v>
-      </c>
-      <c r="B293" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C293" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D293" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="E293" s="73"/>
-      <c r="F293" s="74"/>
-      <c r="G293" s="57" t="n">
-        <f aca="false">Narxlar!$C$26</f>
-        <v>3</v>
-      </c>
-      <c r="H293" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I293" s="7" t="n">
-        <f aca="false">Narxlar!$C$25/Narxlar!$C$19</f>
-        <v>58.8235294117647</v>
-      </c>
-      <c r="J293" s="76" t="n">
-        <f aca="false">G293*I293</f>
-        <v>176.470588235294</v>
-      </c>
-      <c r="K293" s="24" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="5" t="n">
-        <v>229</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C294" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D294" s="6" t="s">
-        <v>520</v>
-      </c>
-      <c r="E294" s="73"/>
-      <c r="F294" s="74"/>
-      <c r="G294" s="57" t="n">
-        <f aca="false">Narxlar!$C$28</f>
-        <v>3</v>
-      </c>
-      <c r="H294" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I294" s="7" t="n">
-        <f aca="false">Narxlar!$C$27/Narxlar!$C$19</f>
-        <v>100.840336134454</v>
-      </c>
-      <c r="J294" s="76" t="n">
-        <f aca="false">G294*I294</f>
-        <v>302.521008403361</v>
-      </c>
-      <c r="K294" s="24" t="s">
-        <v>173</v>
-      </c>
+      <c r="B294" s="55"/>
+      <c r="C294" s="55"/>
+      <c r="D294" s="55"/>
+      <c r="E294" s="55"/>
+      <c r="F294" s="55"/>
+      <c r="G294" s="55"/>
+      <c r="H294" s="55"/>
+      <c r="I294" s="55"/>
+      <c r="J294" s="55"/>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="5" t="n">
@@ -21419,27 +21429,27 @@
         <v>19</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E295" s="73"/>
       <c r="F295" s="74"/>
       <c r="G295" s="57" t="n">
-        <f aca="false">Narxlar!$C$30</f>
-        <v>4</v>
+        <f aca="false">Narxlar!$C$26</f>
+        <v>3</v>
       </c>
       <c r="H295" s="5" t="s">
         <v>283</v>
       </c>
       <c r="I295" s="7" t="n">
-        <f aca="false">Narxlar!$C$29/Narxlar!$C$19</f>
-        <v>54.6218487394958</v>
+        <f aca="false">Narxlar!$C$25/Narxlar!$C$19</f>
+        <v>58.8235294117647</v>
       </c>
       <c r="J295" s="76" t="n">
         <f aca="false">G295*I295</f>
-        <v>218.487394957983</v>
+        <v>176.470588235294</v>
       </c>
       <c r="K295" s="24" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21453,27 +21463,27 @@
         <v>19</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E296" s="73"/>
       <c r="F296" s="74"/>
       <c r="G296" s="57" t="n">
-        <f aca="false">Narxlar!$C$32</f>
-        <v>6</v>
+        <f aca="false">Narxlar!$C$28</f>
+        <v>3</v>
       </c>
       <c r="H296" s="5" t="s">
         <v>283</v>
       </c>
       <c r="I296" s="7" t="n">
-        <f aca="false">Narxlar!$C$31/Narxlar!$C$19</f>
-        <v>16.8067226890756</v>
+        <f aca="false">Narxlar!$C$27/Narxlar!$C$19</f>
+        <v>100.840336134454</v>
       </c>
       <c r="J296" s="76" t="n">
         <f aca="false">G296*I296</f>
-        <v>100.840336134454</v>
+        <v>302.521008403361</v>
       </c>
       <c r="K296" s="24" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21487,27 +21497,27 @@
         <v>19</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E297" s="73"/>
       <c r="F297" s="74"/>
       <c r="G297" s="57" t="n">
-        <f aca="false">Narxlar!$C$34</f>
+        <f aca="false">Narxlar!$C$30</f>
         <v>4</v>
       </c>
       <c r="H297" s="5" t="s">
         <v>283</v>
       </c>
       <c r="I297" s="7" t="n">
-        <f aca="false">Narxlar!$C$33/Narxlar!$C$19</f>
-        <v>33.6134453781513</v>
+        <f aca="false">Narxlar!$C$29/Narxlar!$C$19</f>
+        <v>54.6218487394958</v>
       </c>
       <c r="J297" s="76" t="n">
         <f aca="false">G297*I297</f>
-        <v>134.453781512605</v>
+        <v>218.487394957983</v>
       </c>
       <c r="K297" s="24" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21521,27 +21531,27 @@
         <v>19</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E298" s="73"/>
       <c r="F298" s="74"/>
       <c r="G298" s="57" t="n">
-        <f aca="false">Narxlar!$C$36</f>
-        <v>4</v>
+        <f aca="false">Narxlar!$C$32</f>
+        <v>6</v>
       </c>
       <c r="H298" s="5" t="s">
         <v>283</v>
       </c>
       <c r="I298" s="7" t="n">
-        <f aca="false">Narxlar!$C$35/Narxlar!$C$19</f>
-        <v>33.6134453781513</v>
+        <f aca="false">Narxlar!$C$31/Narxlar!$C$19</f>
+        <v>16.8067226890756</v>
       </c>
       <c r="J298" s="76" t="n">
         <f aca="false">G298*I298</f>
-        <v>134.453781512605</v>
+        <v>100.840336134454</v>
       </c>
       <c r="K298" s="24" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21555,27 +21565,27 @@
         <v>19</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E299" s="73"/>
       <c r="F299" s="74"/>
       <c r="G299" s="57" t="n">
-        <f aca="false">Narxlar!$C$38</f>
-        <v>16</v>
+        <f aca="false">Narxlar!$C$34</f>
+        <v>4</v>
       </c>
       <c r="H299" s="5" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="I299" s="7" t="n">
-        <f aca="false">Narxlar!$C$37/Narxlar!$C$19</f>
-        <v>84.0336134453782</v>
+        <f aca="false">Narxlar!$C$33/Narxlar!$C$19</f>
+        <v>33.6134453781513</v>
       </c>
       <c r="J299" s="76" t="n">
         <f aca="false">G299*I299</f>
-        <v>1344.53781512605</v>
+        <v>134.453781512605</v>
       </c>
       <c r="K299" s="24" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21589,27 +21599,27 @@
         <v>19</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E300" s="73"/>
       <c r="F300" s="74"/>
       <c r="G300" s="57" t="n">
-        <f aca="false">Narxlar!$C$44</f>
+        <f aca="false">Narxlar!$C$36</f>
         <v>4</v>
       </c>
       <c r="H300" s="5" t="s">
         <v>283</v>
       </c>
       <c r="I300" s="7" t="n">
-        <f aca="false">Narxlar!$C$43/Narxlar!$C$19</f>
-        <v>100.840336134454</v>
+        <f aca="false">Narxlar!$C$35/Narxlar!$C$19</f>
+        <v>33.6134453781513</v>
       </c>
       <c r="J300" s="76" t="n">
         <f aca="false">G300*I300</f>
-        <v>403.361344537815</v>
+        <v>134.453781512605</v>
       </c>
       <c r="K300" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21623,27 +21633,27 @@
         <v>19</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>132</v>
+        <v>526</v>
       </c>
       <c r="E301" s="73"/>
       <c r="F301" s="74"/>
-      <c r="G301" s="56" t="n">
-        <f aca="false">Narxlar!$C$46</f>
-        <v>40</v>
+      <c r="G301" s="57" t="n">
+        <f aca="false">Narxlar!$C$38</f>
+        <v>16</v>
       </c>
       <c r="H301" s="5" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="I301" s="7" t="n">
-        <f aca="false">Narxlar!$C$45/Narxlar!$C$19</f>
-        <v>2.10084033613445</v>
+        <f aca="false">Narxlar!$C$37/Narxlar!$C$19</f>
+        <v>84.0336134453782</v>
       </c>
       <c r="J301" s="76" t="n">
         <f aca="false">G301*I301</f>
-        <v>84.0336134453782</v>
+        <v>1344.53781512605</v>
       </c>
       <c r="K301" s="24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21657,27 +21667,27 @@
         <v>19</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>134</v>
+        <v>527</v>
       </c>
       <c r="E302" s="73"/>
       <c r="F302" s="74"/>
-      <c r="G302" s="56" t="n">
-        <f aca="false">Narxlar!$C$48</f>
-        <v>40</v>
+      <c r="G302" s="57" t="n">
+        <f aca="false">Narxlar!$C$44</f>
+        <v>4</v>
       </c>
       <c r="H302" s="5" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="I302" s="7" t="n">
-        <f aca="false">Narxlar!$C$47/Narxlar!$C$19</f>
-        <v>1.00840336134454</v>
+        <f aca="false">Narxlar!$C$43/Narxlar!$C$19</f>
+        <v>100.840336134454</v>
       </c>
       <c r="J302" s="76" t="n">
         <f aca="false">G302*I302</f>
-        <v>40.3361344537815</v>
+        <v>403.361344537815</v>
       </c>
       <c r="K302" s="24" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21691,27 +21701,27 @@
         <v>19</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E303" s="73"/>
       <c r="F303" s="74"/>
-      <c r="G303" s="57" t="n">
-        <f aca="false">Narxlar!$C$50</f>
-        <v>100</v>
+      <c r="G303" s="56" t="n">
+        <f aca="false">Narxlar!$C$46</f>
+        <v>40</v>
       </c>
       <c r="H303" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="I303" s="7" t="n">
-        <f aca="false">Narxlar!$C$49/Narxlar!$C$19</f>
-        <v>0.420168067226891</v>
+        <f aca="false">Narxlar!$C$45/Narxlar!$C$19</f>
+        <v>2.10084033613445</v>
       </c>
       <c r="J303" s="76" t="n">
         <f aca="false">G303*I303</f>
-        <v>42.0168067226891</v>
+        <v>84.0336134453782</v>
       </c>
       <c r="K303" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21725,26 +21735,27 @@
         <v>19</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>527</v>
+        <v>134</v>
       </c>
       <c r="E304" s="73"/>
       <c r="F304" s="74"/>
-      <c r="G304" s="75" t="n">
-        <v>1</v>
+      <c r="G304" s="56" t="n">
+        <f aca="false">Narxlar!$C$48</f>
+        <v>40</v>
       </c>
       <c r="H304" s="5" t="s">
-        <v>386</v>
+        <v>277</v>
       </c>
       <c r="I304" s="7" t="n">
-        <f aca="false">Narxlar!$C$51/Narxlar!$C$19</f>
-        <v>336.134453781513</v>
+        <f aca="false">Narxlar!$C$47/Narxlar!$C$19</f>
+        <v>1.00840336134454</v>
       </c>
       <c r="J304" s="76" t="n">
         <f aca="false">G304*I304</f>
-        <v>336.134453781513</v>
+        <v>40.3361344537815</v>
       </c>
       <c r="K304" s="24" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21755,30 +21766,30 @@
         <v>259</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>528</v>
+        <v>136</v>
       </c>
       <c r="E305" s="73"/>
       <c r="F305" s="74"/>
-      <c r="G305" s="56" t="n">
-        <f aca="false">Narxlar!$C$41</f>
-        <v>58</v>
+      <c r="G305" s="57" t="n">
+        <f aca="false">Narxlar!$C$50</f>
+        <v>100</v>
       </c>
       <c r="H305" s="5" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="I305" s="7" t="n">
-        <f aca="false">Narxlar!$C$39/Narxlar!$C$19</f>
-        <v>8.40336134453782</v>
+        <f aca="false">Narxlar!$C$49/Narxlar!$C$19</f>
+        <v>0.420168067226891</v>
       </c>
       <c r="J305" s="76" t="n">
         <f aca="false">G305*I305</f>
-        <v>487.394957983193</v>
+        <v>42.0168067226891</v>
       </c>
       <c r="K305" s="24" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21789,30 +21800,29 @@
         <v>259</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E306" s="73"/>
       <c r="F306" s="74"/>
-      <c r="G306" s="56" t="n">
-        <f aca="false">Narxlar!$C$41</f>
-        <v>58</v>
+      <c r="G306" s="75" t="n">
+        <v>1</v>
       </c>
       <c r="H306" s="5" t="s">
-        <v>310</v>
+        <v>386</v>
       </c>
       <c r="I306" s="7" t="n">
-        <f aca="false">Narxlar!$C$40/Narxlar!$C$19</f>
-        <v>8.40336134453782</v>
+        <f aca="false">Narxlar!$C$51/Narxlar!$C$19</f>
+        <v>336.134453781513</v>
       </c>
       <c r="J306" s="76" t="n">
         <f aca="false">G306*I306</f>
-        <v>487.394957983193</v>
+        <v>336.134453781513</v>
       </c>
       <c r="K306" s="24" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21826,13 +21836,13 @@
         <v>20</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E307" s="73"/>
       <c r="F307" s="74"/>
       <c r="G307" s="56" t="n">
-        <f aca="false">Narxlar!$C$42</f>
-        <v>16</v>
+        <f aca="false">Narxlar!$C$41</f>
+        <v>58</v>
       </c>
       <c r="H307" s="5" t="s">
         <v>310</v>
@@ -21843,7 +21853,7 @@
       </c>
       <c r="J307" s="76" t="n">
         <f aca="false">G307*I307</f>
-        <v>134.453781512605</v>
+        <v>487.394957983193</v>
       </c>
       <c r="K307" s="24" t="s">
         <v>145</v>
@@ -21860,13 +21870,13 @@
         <v>20</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E308" s="73"/>
       <c r="F308" s="74"/>
       <c r="G308" s="56" t="n">
-        <f aca="false">Narxlar!$C$42</f>
-        <v>16</v>
+        <f aca="false">Narxlar!$C$41</f>
+        <v>58</v>
       </c>
       <c r="H308" s="5" t="s">
         <v>310</v>
@@ -21877,27 +21887,78 @@
       </c>
       <c r="J308" s="76" t="n">
         <f aca="false">G308*I308</f>
-        <v>134.453781512605</v>
+        <v>487.394957983193</v>
       </c>
       <c r="K308" s="24" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="77"/>
-      <c r="B309" s="77"/>
-      <c r="C309" s="77"/>
-      <c r="D309" s="11" t="s">
+      <c r="A309" s="5" t="n">
+        <v>244</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="E309" s="73"/>
+      <c r="F309" s="74"/>
+      <c r="G309" s="56" t="n">
+        <f aca="false">Narxlar!$C$42</f>
+        <v>16</v>
+      </c>
+      <c r="H309" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I309" s="7" t="n">
+        <f aca="false">Narxlar!$C$39/Narxlar!$C$19</f>
+        <v>8.40336134453782</v>
+      </c>
+      <c r="J309" s="76" t="n">
+        <f aca="false">G309*I309</f>
+        <v>134.453781512605</v>
+      </c>
+      <c r="K309" s="24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D310" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="E309" s="77"/>
-      <c r="F309" s="77"/>
-      <c r="G309" s="77"/>
-      <c r="H309" s="77"/>
-      <c r="I309" s="77"/>
-      <c r="J309" s="12" t="n">
-        <f aca="false">SUM(J293:J308)</f>
-        <v>4561.34453781513</v>
+      <c r="E310" s="73"/>
+      <c r="F310" s="74"/>
+      <c r="G310" s="56" t="n">
+        <f aca="false">Narxlar!$C$42</f>
+        <v>16</v>
+      </c>
+      <c r="H310" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="I310" s="7" t="n">
+        <f aca="false">Narxlar!$C$40/Narxlar!$C$19</f>
+        <v>8.40336134453782</v>
+      </c>
+      <c r="J310" s="76" t="n">
+        <f aca="false">G310*I310</f>
+        <v>134.453781512605</v>
+      </c>
+      <c r="K310" s="24" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21913,8 +21974,25 @@
       <c r="H311" s="77"/>
       <c r="I311" s="77"/>
       <c r="J311" s="12" t="n">
-        <f aca="false">J13+J27+J40+J52+J71+J84+J99+J115+J134+J154+J169+J182+J189+J211+J235+J253+J257+J261+J281+J290+J309</f>
-        <v>74981.2150420168</v>
+        <f aca="false">SUM(J295:J310)</f>
+        <v>4561.34453781513</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="77"/>
+      <c r="B313" s="77"/>
+      <c r="C313" s="77"/>
+      <c r="D313" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="E313" s="77"/>
+      <c r="F313" s="77"/>
+      <c r="G313" s="77"/>
+      <c r="H313" s="77"/>
+      <c r="I313" s="77"/>
+      <c r="J313" s="12" t="n">
+        <f aca="false">J13+J27+J40+J52+J71+J84+J99+J115+J134+J152+J167+J182+J189+J211+J235+J253+J257+J262+J283+J292+J311</f>
+        <v>75173.9560084034</v>
       </c>
     </row>
   </sheetData>

--- a/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
+++ b/xadra-filiali/hisob/Xadra_xarajatlar_v1.2.xlsx
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">Havo kanallari uzunligi</t>
   </si>
   <si>
-    <t xml:space="preserve">Kanallar rejasidan: 165 m (berish ~72, tashqi havo ~24, vitechka ~69) + 10% burilish va ulanishlar</t>
+    <t xml:space="preserve">Kanallar rejasidan: 167 m (berish ~75, tashqi havo ~24, vitechka ~69) + 10% burilish va ulanishlar</t>
   </si>
   <si>
     <t xml:space="preserve">TAXMIN</t>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C6/$C$23)</f>
-        <v>0.0971685938246814</v>
+        <v>0.0971071369793098</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C7/$C$23)</f>
-        <v>0.0458501455866683</v>
+        <v>0.0458211464502532</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C8/$C$23)</f>
-        <v>0.104082077299537</v>
+        <v>0.104016247838816</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C9/$C$23)</f>
-        <v>0.103629764006662</v>
+        <v>0.103564220623437</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C10/$C$23)</f>
-        <v>0.0291534023597229</v>
+        <v>0.0291349635198637</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C11/$C$23)</f>
-        <v>0.0379574135605796</v>
+        <v>0.0379334063911426</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C12/$C$23)</f>
-        <v>0.0265978040128532</v>
+        <v>0.026580981528714</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C13/$C$23)</f>
-        <v>0.0407941779338239</v>
+        <v>0.0407683765777822</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C14/$C$23)</f>
-        <v>0.0067506849069547</v>
+        <v>0.00674641525786183</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C15/$C$23)</f>
-        <v>0.0189863013008101</v>
+        <v>0.0189742929127364</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C16/$C$23)</f>
-        <v>0.00427455477897405</v>
+        <v>0.00427185122382579</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C17/$C$23)</f>
-        <v>0.0416432875197768</v>
+        <v>0.0416169491219352</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C18/$C$23)</f>
-        <v>0.0156109588473327</v>
+        <v>0.0156010852838055</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2848,15 +2848,15 @@
       </c>
       <c r="C19" s="7" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$345,'Hisob (batafsil)'!$C$5:$C$345,"Konditsioner va ventilyatsiya")</f>
-        <v>18238.2352941176</v>
+        <v>18288.6554621849</v>
       </c>
       <c r="D19" s="8" t="n">
         <f aca="false">C19*Narxlar!$C$19</f>
-        <v>217035000</v>
+        <v>217635000</v>
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C19/$C$23)</f>
-        <v>0.228927327934518</v>
+        <v>0.229415013225744</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="E20" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C20/$C$23)</f>
-        <v>0.164431917210183</v>
+        <v>0.164327917898138</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="E21" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C21/$C$23)</f>
-        <v>0.00464426025708149</v>
+        <v>0.00464132287193213</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E22" s="9" t="n">
         <f aca="false">IF($C$23=0,0,C22/$C$23)</f>
-        <v>0.0294973286598419</v>
+        <v>0.0294786722947041</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2926,11 +2926,11 @@
       </c>
       <c r="C23" s="12" t="n">
         <f aca="false">SUM(C6:C22)</f>
-        <v>79668.2312184874</v>
+        <v>79718.6513865546</v>
       </c>
       <c r="D23" s="13" t="n">
         <f aca="false">C23*Narxlar!$C$19</f>
-        <v>948051951.5</v>
+        <v>948651951.5</v>
       </c>
       <c r="E23" s="14" t="n">
         <f aca="false">SUM(E6:E22)</f>
@@ -2945,11 +2945,11 @@
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">C23*Narxlar!$C$93</f>
-        <v>7966.82312184874</v>
+        <v>7971.86513865546</v>
       </c>
       <c r="D24" s="18" t="n">
         <f aca="false">C24*Narxlar!$C$19</f>
-        <v>94805195.15</v>
+        <v>94865195.15</v>
       </c>
       <c r="E24" s="16"/>
     </row>
@@ -2960,11 +2960,11 @@
       </c>
       <c r="C25" s="21" t="n">
         <f aca="false">C23+C24</f>
-        <v>87635.0543403361</v>
+        <v>87690.5165252101</v>
       </c>
       <c r="D25" s="22" t="n">
         <f aca="false">C25*Narxlar!$C$19</f>
-        <v>1042857146.65</v>
+        <v>1043517146.65</v>
       </c>
       <c r="E25" s="20"/>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E30" s="9" t="n">
         <f aca="false">IF($C$35=0,0,C30/$C$35)</f>
-        <v>0.0430535477886203</v>
+        <v>0.0430263174343979</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E31" s="9" t="n">
         <f aca="false">IF($C$35=0,0,C31/$C$35)</f>
-        <v>0.267071951699896</v>
+        <v>0.266903034985218</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="E32" s="9" t="n">
         <f aca="false">IF($C$35=0,0,C32/$C$35)</f>
-        <v>0.135269791172409</v>
+        <v>0.135184236217744</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3074,15 +3074,15 @@
       </c>
       <c r="C33" s="7" t="n">
         <f aca="false">'Xonalar bo''yicha'!$X$36</f>
-        <v>36864.7016806723</v>
+        <v>36915.1218487395</v>
       </c>
       <c r="D33" s="8" t="n">
         <f aca="false">C33*Narxlar!$C$19</f>
-        <v>438689950</v>
+        <v>439289950</v>
       </c>
       <c r="E33" s="9" t="n">
         <f aca="false">IF($C$35=0,0,C33/$C$35)</f>
-        <v>0.462727753796518</v>
+        <v>0.463067565828963</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="E34" s="9" t="n">
         <f aca="false">IF($C$35=0,0,C34/$C$35)</f>
-        <v>0.0918769555425571</v>
+        <v>0.0918188455336773</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3112,11 +3112,11 @@
       </c>
       <c r="C35" s="12" t="n">
         <f aca="false">SUM(C30:C34)</f>
-        <v>79668.2312184874</v>
+        <v>79718.6513865546</v>
       </c>
       <c r="D35" s="13" t="n">
         <f aca="false">C35*Narxlar!$C$19</f>
-        <v>948051951.5</v>
+        <v>948651951.5</v>
       </c>
       <c r="E35" s="14" t="n">
         <f aca="false">SUM(E30:E34)</f>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="K9" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I9/$I$15)</f>
-        <v>0.132047615958101</v>
+        <v>0.131964098953314</v>
       </c>
       <c r="L9" s="37" t="n">
         <f aca="false">SUM($I$9:I9)</f>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="K10" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I10/$I$15)</f>
-        <v>0.00427455477897405</v>
+        <v>0.00427185122382579</v>
       </c>
       <c r="L10" s="37" t="n">
         <f aca="false">SUM($I$9:I10)</f>
@@ -3367,27 +3367,27 @@
       </c>
       <c r="G11" s="36" t="n">
         <f aca="false">N107</f>
-        <v>14747.4672268908</v>
+        <v>14797.887394958</v>
       </c>
       <c r="H11" s="37" t="n">
         <f aca="false">G11*Narxlar!$C$93</f>
-        <v>1474.74672268908</v>
+        <v>1479.7887394958</v>
       </c>
       <c r="I11" s="37" t="n">
         <f aca="false">G11+H11</f>
-        <v>16222.2139495798</v>
+        <v>16277.6761344538</v>
       </c>
       <c r="J11" s="38" t="n">
         <f aca="false">I11*Narxlar!$C$19</f>
-        <v>193044346</v>
+        <v>193704346</v>
       </c>
       <c r="K11" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I11/$I$15)</f>
-        <v>0.185111016039083</v>
+        <v>0.18562641411485</v>
       </c>
       <c r="L11" s="37" t="n">
         <f aca="false">SUM($I$9:I11)</f>
-        <v>28168.814789916</v>
+        <v>28224.2769747899</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3429,11 +3429,11 @@
       </c>
       <c r="K12" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I12/$I$15)</f>
-        <v>0.211285693450735</v>
+        <v>0.211152060229541</v>
       </c>
       <c r="L12" s="37" t="n">
         <f aca="false">SUM($I$9:I12)</f>
-        <v>46684.8480168067</v>
+        <v>46740.3102016807</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3475,11 +3475,11 @@
       </c>
       <c r="K13" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I13/$I$15)</f>
-        <v>0.357576161267994</v>
+        <v>0.35735000277391</v>
       </c>
       <c r="L13" s="37" t="n">
         <f aca="false">SUM($I$9:I13)</f>
-        <v>78021.0543403361</v>
+        <v>78076.5165252101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3521,11 +3521,11 @@
       </c>
       <c r="K14" s="39" t="n">
         <f aca="false">IF($I$15=0,0,I14/$I$15)</f>
-        <v>0.109704958505114</v>
+        <v>0.109635572704559</v>
       </c>
       <c r="L14" s="37" t="n">
         <f aca="false">SUM($I$9:I14)</f>
-        <v>87635.0543403361</v>
+        <v>87690.5165252101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3548,19 +3548,19 @@
       </c>
       <c r="G15" s="41" t="n">
         <f aca="false">SUM(G9:G14)</f>
-        <v>79668.2312184874</v>
+        <v>79718.6513865546</v>
       </c>
       <c r="H15" s="41" t="n">
         <f aca="false">SUM(H9:H14)</f>
-        <v>7966.82312184874</v>
+        <v>7971.86513865546</v>
       </c>
       <c r="I15" s="41" t="n">
         <f aca="false">SUM(I9:I14)</f>
-        <v>87635.0543403361</v>
+        <v>87690.5165252101</v>
       </c>
       <c r="J15" s="42" t="n">
         <f aca="false">I15*Narxlar!$C$19</f>
-        <v>1042857146.65</v>
+        <v>1043517146.65</v>
       </c>
       <c r="K15" s="14" t="n">
         <f aca="false">SUM(K9:K14)</f>
@@ -4013,11 +4013,11 @@
       </c>
       <c r="C32" s="48" t="n">
         <f aca="false">$I$11*MAX(0,MIN($F$11,EOMONTH(C$29,0))-MAX($E$11,C$29)+1)/($F$11-$E$11+1)</f>
-        <v>2317.45913565426</v>
+        <v>2325.38230492197</v>
       </c>
       <c r="D32" s="48" t="n">
         <f aca="false">$I$11*MAX(0,MIN($F$11,EOMONTH(D$29,0))-MAX($E$11,D$29)+1)/($F$11-$E$11+1)</f>
-        <v>13904.7548139256</v>
+        <v>13952.2938295318</v>
       </c>
       <c r="E32" s="48" t="n">
         <f aca="false">$I$11*MAX(0,MIN($F$11,EOMONTH(E$29,0))-MAX($E$11,E$29)+1)/($F$11-$E$11+1)</f>
@@ -4106,11 +4106,11 @@
       </c>
       <c r="C36" s="41" t="n">
         <f aca="false">SUM(C30:C35)</f>
-        <v>14264.0599759904</v>
+        <v>14271.9831452581</v>
       </c>
       <c r="D36" s="41" t="n">
         <f aca="false">SUM(D30:D35)</f>
-        <v>49513.2642172869</v>
+        <v>49560.8032328932</v>
       </c>
       <c r="E36" s="41" t="n">
         <f aca="false">SUM(E30:E35)</f>
@@ -4127,11 +4127,11 @@
       </c>
       <c r="C37" s="42" t="n">
         <f aca="false">C36*Narxlar!$C$19</f>
-        <v>169742313.714286</v>
+        <v>169836599.428571</v>
       </c>
       <c r="D37" s="42" t="n">
         <f aca="false">D36*Narxlar!$C$19</f>
-        <v>589207844.185714</v>
+        <v>589773558.471429</v>
       </c>
       <c r="E37" s="42" t="n">
         <f aca="false">E36*Narxlar!$C$19</f>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="D65" s="50" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$345,'Hisob (batafsil)'!$K$5:$K$345,$A65)</f>
-        <v>4588.23529411765</v>
+        <v>4638.65546218487</v>
       </c>
       <c r="E65" s="51" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="N65" s="53" t="n">
         <f aca="false">$D65*G65</f>
-        <v>4588.23529411765</v>
+        <v>4638.65546218487</v>
       </c>
       <c r="O65" s="53" t="n">
         <f aca="false">$D65*H65</f>
@@ -8234,7 +8234,7 @@
       <c r="C107" s="11"/>
       <c r="D107" s="41" t="n">
         <f aca="false">SUM(D41:D106)</f>
-        <v>79668.2312184874</v>
+        <v>79718.6513865546</v>
       </c>
       <c r="E107" s="11"/>
       <c r="F107" s="11"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="N107" s="41" t="n">
         <f aca="false">SUM(N41:N106)</f>
-        <v>14747.4672268908</v>
+        <v>14797.887394958</v>
       </c>
       <c r="O107" s="41" t="n">
         <f aca="false">SUM(O41:O106)</f>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="T35" s="50" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$345,'Hisob (batafsil)'!$B$5:$B$345,$A35,'Hisob (batafsil)'!$C$5:$C$345,"Konditsioner va ventilyatsiya")</f>
-        <v>17238.2352941176</v>
+        <v>17288.6554621849</v>
       </c>
       <c r="U35" s="50" t="n">
         <f aca="false">SUMIFS('Hisob (batafsil)'!$J$5:$J$345,'Hisob (batafsil)'!$B$5:$B$345,$A35,'Hisob (batafsil)'!$C$5:$C$345,"Mebel va interyer")</f>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="X35" s="58" t="n">
         <f aca="false">C35+E35+G35+I35+K35+L35+M35+N35+O35+P35+Q35+R35+S35+T35+U35+V35+W35</f>
-        <v>24248.2016806723</v>
+        <v>24298.6218487395</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="T36" s="41" t="n">
         <f aca="false">SUM(T28:T35)</f>
-        <v>17238.2352941176</v>
+        <v>17288.6554621849</v>
       </c>
       <c r="U36" s="41" t="n">
         <f aca="false">SUM(U28:U35)</f>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="X36" s="41" t="n">
         <f aca="false">SUM(X28:X35)</f>
-        <v>36864.7016806723</v>
+        <v>36915.1218487395</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="T43" s="62" t="n">
         <f aca="false">T7+T17+T25+T36+T41</f>
-        <v>18238.2352941176</v>
+        <v>18288.6554621849</v>
       </c>
       <c r="U43" s="62" t="n">
         <f aca="false">U7+U17+U25+U36+U41</f>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="X43" s="62" t="n">
         <f aca="false">X7+X17+X25+X36+X41</f>
-        <v>79668.2312184874</v>
+        <v>79718.6513865546</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11402,7 +11402,7 @@
       <c r="W44" s="16"/>
       <c r="X44" s="64" t="n">
         <f aca="false">X43*Narxlar!$C$93</f>
-        <v>7966.82312184874</v>
+        <v>7971.86513865546</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11433,7 +11433,7 @@
       <c r="W45" s="20"/>
       <c r="X45" s="62" t="n">
         <f aca="false">X43+X44</f>
-        <v>87635.0543403361</v>
+        <v>87690.5165252101</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11464,7 +11464,7 @@
       <c r="W46" s="20"/>
       <c r="X46" s="22" t="n">
         <f aca="false">X45*Narxlar!$C$19</f>
-        <v>1042857146.65</v>
+        <v>1043517146.65</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12392,7 +12392,7 @@
         <v>344</v>
       </c>
       <c r="C55" s="66" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>297</v>
@@ -23137,7 +23137,7 @@
       <c r="F311" s="74"/>
       <c r="G311" s="56" t="n">
         <f aca="false">Narxlar!$C$55</f>
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H311" s="5" t="s">
         <v>297</v>
@@ -23148,7 +23148,7 @@
       </c>
       <c r="J311" s="76" t="n">
         <f aca="false">G311*I311</f>
-        <v>4588.23529411765</v>
+        <v>4638.65546218487</v>
       </c>
       <c r="K311" s="24" t="s">
         <v>142</v>
@@ -23302,7 +23302,7 @@
       <c r="I316" s="77"/>
       <c r="J316" s="12" t="n">
         <f aca="false">SUM(J294:J315)</f>
-        <v>24248.2016806723</v>
+        <v>24298.6218487395</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24147,7 +24147,7 @@
       <c r="I346" s="77"/>
       <c r="J346" s="12" t="n">
         <f aca="false">J13+J27+J40+J54+J72+J87+J102+J118+J137+J155+J170+J185+J192+J219+J248+J256+J264+J282+J286+J291+J316+J325+J344</f>
-        <v>79668.2312184874</v>
+        <v>79718.6513865546</v>
       </c>
     </row>
   </sheetData>
